--- a/daily.xml.xlsx
+++ b/daily.xml.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sally03915\Desktop\2026-출석부\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hyojung2\2026-AI-FULLSTACK-LevelUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1634F5F9-0767-4D0A-BC4E-03B3255B36B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8988"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026. 3~4월" sheetId="1" r:id="rId1"/>
@@ -20,17 +21,29 @@
     <sheet name="2026.9" sheetId="6" r:id="rId6"/>
     <sheet name="2026.10" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1281" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1281" uniqueCount="36">
   <si>
     <t>출석일수 (Attendance Days)</t>
   </si>
@@ -140,17 +153,21 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>복습문제
-엔젤</t>
+    <t>전원 출석
+- 최윤정지각</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>복습문제 만점</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="180" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
+    <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -239,7 +256,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -262,8 +279,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="26">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -603,19 +626,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -674,13 +684,13 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="2" applyBorder="1" applyAlignment="1">
@@ -755,9 +765,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -771,6 +778,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1055,23 +1065,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:Q29"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="12.09765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.796875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" customWidth="1"/>
-    <col min="5" max="5" width="15.796875" customWidth="1"/>
-    <col min="6" max="6" width="14.19921875" customWidth="1"/>
-    <col min="7" max="8" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.09765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.75" style="3" customWidth="1"/>
+    <col min="4" max="4" width="14.625" customWidth="1"/>
+    <col min="5" max="5" width="15.75" customWidth="1"/>
+    <col min="6" max="6" width="14.25" customWidth="1"/>
+    <col min="7" max="8" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="2:17" ht="49.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:17" ht="49.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="13" t="s">
         <v>30</v>
       </c>
@@ -1115,17 +1125,17 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B3" s="14">
         <v>46107</v>
       </c>
       <c r="C3" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="42" t="s">
+      <c r="D3" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="43" t="s">
+      <c r="E3" s="42" t="s">
         <v>24</v>
       </c>
       <c r="F3" s="9">
@@ -1141,7 +1151,7 @@
         <v>5</v>
       </c>
       <c r="K3" s="30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L3" s="31">
         <v>1</v>
@@ -1150,20 +1160,20 @@
         <v>1</v>
       </c>
       <c r="N3" s="31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O3" s="32">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B4" s="15">
         <v>46108</v>
       </c>
       <c r="C4" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="46" t="s">
+      <c r="D4" s="45" t="s">
         <v>22</v>
       </c>
       <c r="E4" s="5" t="s">
@@ -1181,8 +1191,8 @@
       <c r="J4" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="K4" s="34">
-        <v>3</v>
+      <c r="K4" s="30">
+        <v>4</v>
       </c>
       <c r="L4" s="35">
         <v>1</v>
@@ -1191,20 +1201,20 @@
         <v>1</v>
       </c>
       <c r="N4" s="31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O4" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B5" s="15">
         <v>46111</v>
       </c>
       <c r="C5" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="45" t="s">
+      <c r="D5" s="44" t="s">
         <v>21</v>
       </c>
       <c r="E5" s="5" t="s">
@@ -1213,7 +1223,7 @@
       <c r="F5" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="44" t="s">
+      <c r="G5" s="43" t="s">
         <v>33</v>
       </c>
       <c r="H5" s="6" t="s">
@@ -1222,8 +1232,8 @@
       <c r="J5" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="34">
-        <v>3</v>
+      <c r="K5" s="30">
+        <v>4</v>
       </c>
       <c r="L5" s="35">
         <v>1</v>
@@ -1232,20 +1242,20 @@
         <v>1</v>
       </c>
       <c r="N5" s="31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O5" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B6" s="15">
         <v>46112</v>
       </c>
       <c r="C6" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="45" t="s">
+      <c r="D6" s="44" t="s">
         <v>21</v>
       </c>
       <c r="E6" s="5" t="s">
@@ -1254,8 +1264,8 @@
       <c r="F6" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>34</v>
+      <c r="G6" s="43" t="s">
+        <v>35</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>23</v>
@@ -1263,8 +1273,8 @@
       <c r="J6" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="K6" s="34">
-        <v>3</v>
+      <c r="K6" s="30">
+        <v>4</v>
       </c>
       <c r="L6" s="35">
         <v>1</v>
@@ -1273,21 +1283,21 @@
         <v>1</v>
       </c>
       <c r="N6" s="31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O6" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:17" ht="33" x14ac:dyDescent="0.3">
       <c r="B7" s="15">
         <v>46113</v>
       </c>
       <c r="C7" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>23</v>
+      <c r="D7" s="46" t="s">
+        <v>34</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>23</v>
@@ -1304,8 +1314,8 @@
       <c r="J7" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="34">
-        <v>3</v>
+      <c r="K7" s="30">
+        <v>4</v>
       </c>
       <c r="L7" s="35">
         <v>1</v>
@@ -1314,13 +1324,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O7" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B8" s="15">
         <v>46114</v>
       </c>
@@ -1345,23 +1355,23 @@
       <c r="J8" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="K8" s="34">
+      <c r="K8" s="30">
+        <v>3</v>
+      </c>
+      <c r="L8" s="35">
+        <v>1</v>
+      </c>
+      <c r="M8" s="35">
+        <v>1</v>
+      </c>
+      <c r="N8" s="31">
         <v>2</v>
       </c>
-      <c r="L8" s="35">
-        <v>1</v>
-      </c>
-      <c r="M8" s="35">
-        <v>1</v>
-      </c>
-      <c r="N8" s="31">
-        <v>1</v>
-      </c>
       <c r="O8" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B9" s="15">
         <v>46115</v>
       </c>
@@ -1386,8 +1396,8 @@
       <c r="J9" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="K9" s="34">
-        <v>3</v>
+      <c r="K9" s="30">
+        <v>4</v>
       </c>
       <c r="L9" s="35">
         <v>1</v>
@@ -1396,13 +1406,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O9" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B10" s="15">
         <v>46118</v>
       </c>
@@ -1427,8 +1437,8 @@
       <c r="J10" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="K10" s="34">
-        <v>3</v>
+      <c r="K10" s="30">
+        <v>4</v>
       </c>
       <c r="L10" s="35">
         <v>1</v>
@@ -1437,13 +1447,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O10" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B11" s="15">
         <v>46119</v>
       </c>
@@ -1468,8 +1478,8 @@
       <c r="J11" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="K11" s="34">
-        <v>3</v>
+      <c r="K11" s="30">
+        <v>4</v>
       </c>
       <c r="L11" s="35">
         <v>1</v>
@@ -1478,13 +1488,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O11" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B12" s="15">
         <v>46120</v>
       </c>
@@ -1509,8 +1519,8 @@
       <c r="J12" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="K12" s="34">
-        <v>3</v>
+      <c r="K12" s="30">
+        <v>4</v>
       </c>
       <c r="L12" s="35">
         <v>1</v>
@@ -1519,13 +1529,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O12" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B13" s="15">
         <v>46121</v>
       </c>
@@ -1550,8 +1560,8 @@
       <c r="J13" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="K13" s="34">
-        <v>3</v>
+      <c r="K13" s="30">
+        <v>4</v>
       </c>
       <c r="L13" s="35">
         <v>1</v>
@@ -1560,13 +1570,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O13" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B14" s="15">
         <v>46122</v>
       </c>
@@ -1591,8 +1601,8 @@
       <c r="J14" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="K14" s="34">
-        <v>3</v>
+      <c r="K14" s="30">
+        <v>4</v>
       </c>
       <c r="L14" s="35">
         <v>1</v>
@@ -1601,13 +1611,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O14" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B15" s="15">
         <v>46125</v>
       </c>
@@ -1632,8 +1642,8 @@
       <c r="J15" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="K15" s="34">
-        <v>3</v>
+      <c r="K15" s="30">
+        <v>4</v>
       </c>
       <c r="L15" s="35">
         <v>1</v>
@@ -1642,13 +1652,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O15" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="15">
         <v>46126</v>
       </c>
@@ -1673,8 +1683,8 @@
       <c r="J16" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="K16" s="38">
-        <v>3</v>
+      <c r="K16" s="30">
+        <v>4</v>
       </c>
       <c r="L16" s="39">
         <v>1</v>
@@ -1682,14 +1692,14 @@
       <c r="M16" s="39">
         <v>1</v>
       </c>
-      <c r="N16" s="41">
-        <v>1</v>
+      <c r="N16" s="31">
+        <v>2</v>
       </c>
       <c r="O16" s="40">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" s="15">
         <v>46127</v>
       </c>
@@ -1712,7 +1722,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B18" s="15">
         <v>46128</v>
       </c>
@@ -1735,7 +1745,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="15">
         <v>46129</v>
       </c>
@@ -1758,7 +1768,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="15">
         <v>46132</v>
       </c>
@@ -1781,7 +1791,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="15">
         <v>46133</v>
       </c>
@@ -1804,7 +1814,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B22" s="15">
         <v>46134</v>
       </c>
@@ -1827,7 +1837,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="15">
         <v>46135</v>
       </c>
@@ -1850,7 +1860,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="15">
         <v>46136</v>
       </c>
@@ -1873,7 +1883,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B25" s="15">
         <v>46139</v>
       </c>
@@ -1896,7 +1906,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B26" s="15">
         <v>46140</v>
       </c>
@@ -1919,7 +1929,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B27" s="15">
         <v>46141</v>
       </c>
@@ -1942,7 +1952,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B28" s="16">
         <v>46142</v>
       </c>
@@ -1965,7 +1975,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="2"/>
       <c r="C29" s="4"/>
       <c r="D29" s="2">
@@ -1985,19 +1995,19 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:Q31"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.8984375" customWidth="1"/>
+    <col min="2" max="2" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="2:17" ht="87.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:17" ht="83.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="13" t="s">
         <v>30</v>
       </c>
@@ -2041,7 +2051,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:17" ht="33" x14ac:dyDescent="0.3">
       <c r="B3" s="14">
         <v>46107</v>
       </c>
@@ -2072,7 +2082,7 @@
       <c r="N3" s="31"/>
       <c r="O3" s="32"/>
     </row>
-    <row r="4" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B4" s="15">
         <v>46108</v>
       </c>
@@ -2103,7 +2113,7 @@
       <c r="N4" s="35"/>
       <c r="O4" s="36"/>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B5" s="15">
         <v>46111</v>
       </c>
@@ -2134,7 +2144,7 @@
       <c r="N5" s="35"/>
       <c r="O5" s="36"/>
     </row>
-    <row r="6" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:17" ht="33" x14ac:dyDescent="0.3">
       <c r="B6" s="15">
         <v>46112</v>
       </c>
@@ -2165,7 +2175,7 @@
       <c r="N6" s="35"/>
       <c r="O6" s="36"/>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B7" s="15">
         <v>46113</v>
       </c>
@@ -2196,7 +2206,7 @@
       <c r="N7" s="35"/>
       <c r="O7" s="36"/>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B8" s="15">
         <v>46114</v>
       </c>
@@ -2227,7 +2237,7 @@
       <c r="N8" s="35"/>
       <c r="O8" s="36"/>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B9" s="15">
         <v>46115</v>
       </c>
@@ -2258,7 +2268,7 @@
       <c r="N9" s="35"/>
       <c r="O9" s="36"/>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B10" s="15">
         <v>46118</v>
       </c>
@@ -2289,7 +2299,7 @@
       <c r="N10" s="35"/>
       <c r="O10" s="36"/>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B11" s="15">
         <v>46119</v>
       </c>
@@ -2320,7 +2330,7 @@
       <c r="N11" s="35"/>
       <c r="O11" s="36"/>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B12" s="15">
         <v>46120</v>
       </c>
@@ -2351,7 +2361,7 @@
       <c r="N12" s="35"/>
       <c r="O12" s="36"/>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B13" s="15">
         <v>46121</v>
       </c>
@@ -2382,7 +2392,7 @@
       <c r="N13" s="35"/>
       <c r="O13" s="36"/>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B14" s="15">
         <v>46122</v>
       </c>
@@ -2413,7 +2423,7 @@
       <c r="N14" s="35"/>
       <c r="O14" s="36"/>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B15" s="15">
         <v>46125</v>
       </c>
@@ -2444,7 +2454,7 @@
       <c r="N15" s="35"/>
       <c r="O15" s="36"/>
     </row>
-    <row r="16" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="15">
         <v>46126</v>
       </c>
@@ -2475,7 +2485,7 @@
       <c r="N16" s="39"/>
       <c r="O16" s="40"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" s="15">
         <v>46127</v>
       </c>
@@ -2498,7 +2508,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B18" s="15">
         <v>46128</v>
       </c>
@@ -2521,7 +2531,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="15">
         <v>46129</v>
       </c>
@@ -2544,7 +2554,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="15">
         <v>46132</v>
       </c>
@@ -2567,7 +2577,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="15">
         <v>46133</v>
       </c>
@@ -2590,7 +2600,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B22" s="15">
         <v>46134</v>
       </c>
@@ -2613,7 +2623,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="15">
         <v>46135</v>
       </c>
@@ -2636,7 +2646,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="15">
         <v>46136</v>
       </c>
@@ -2659,7 +2669,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B25" s="15">
         <v>46139</v>
       </c>
@@ -2682,7 +2692,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B26" s="15">
         <v>46140</v>
       </c>
@@ -2705,7 +2715,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B27" s="15">
         <v>46141</v>
       </c>
@@ -2728,7 +2738,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B28" s="16">
         <v>46142</v>
       </c>
@@ -2751,7 +2761,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="2"/>
       <c r="C29" s="4"/>
       <c r="D29" s="2"/>
@@ -2760,10 +2770,10 @@
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C30" s="3"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C31" s="3"/>
     </row>
   </sheetData>
@@ -2773,15 +2783,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:Q31"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="2:17" ht="87.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:17" ht="83.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="13" t="s">
         <v>30</v>
       </c>
@@ -2825,7 +2835,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:17" ht="33" x14ac:dyDescent="0.3">
       <c r="B3" s="14">
         <v>46107</v>
       </c>
@@ -2866,7 +2876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:17" ht="33" x14ac:dyDescent="0.3">
       <c r="B4" s="15">
         <v>46108</v>
       </c>
@@ -2907,7 +2917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B5" s="15">
         <v>46111</v>
       </c>
@@ -2948,7 +2958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:17" ht="33" x14ac:dyDescent="0.3">
       <c r="B6" s="15">
         <v>46112</v>
       </c>
@@ -2989,7 +2999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B7" s="15">
         <v>46113</v>
       </c>
@@ -3030,7 +3040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B8" s="15">
         <v>46114</v>
       </c>
@@ -3071,7 +3081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B9" s="15">
         <v>46115</v>
       </c>
@@ -3112,7 +3122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B10" s="15">
         <v>46118</v>
       </c>
@@ -3153,7 +3163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B11" s="15">
         <v>46119</v>
       </c>
@@ -3194,7 +3204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B12" s="15">
         <v>46120</v>
       </c>
@@ -3235,7 +3245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B13" s="15">
         <v>46121</v>
       </c>
@@ -3276,7 +3286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B14" s="15">
         <v>46122</v>
       </c>
@@ -3317,7 +3327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B15" s="15">
         <v>46125</v>
       </c>
@@ -3358,7 +3368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="15">
         <v>46126</v>
       </c>
@@ -3399,7 +3409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" s="15">
         <v>46127</v>
       </c>
@@ -3422,7 +3432,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B18" s="15">
         <v>46128</v>
       </c>
@@ -3445,7 +3455,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="15">
         <v>46129</v>
       </c>
@@ -3468,7 +3478,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="15">
         <v>46132</v>
       </c>
@@ -3491,7 +3501,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="15">
         <v>46133</v>
       </c>
@@ -3514,7 +3524,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B22" s="15">
         <v>46134</v>
       </c>
@@ -3537,7 +3547,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="15">
         <v>46135</v>
       </c>
@@ -3560,7 +3570,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="15">
         <v>46136</v>
       </c>
@@ -3583,7 +3593,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B25" s="15">
         <v>46139</v>
       </c>
@@ -3606,7 +3616,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B26" s="15">
         <v>46140</v>
       </c>
@@ -3629,7 +3639,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B27" s="15">
         <v>46141</v>
       </c>
@@ -3652,7 +3662,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B28" s="16">
         <v>46142</v>
       </c>
@@ -3675,7 +3685,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="2"/>
       <c r="C29" s="4"/>
       <c r="D29" s="2"/>
@@ -3684,10 +3694,10 @@
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C30" s="3"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C31" s="3"/>
     </row>
   </sheetData>
@@ -3697,15 +3707,15 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B1:Q31"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="2:17" ht="87.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:17" ht="83.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="13" t="s">
         <v>30</v>
       </c>
@@ -3749,7 +3759,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:17" ht="33" x14ac:dyDescent="0.3">
       <c r="B3" s="14">
         <v>46107</v>
       </c>
@@ -3790,7 +3800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:17" ht="33" x14ac:dyDescent="0.3">
       <c r="B4" s="15">
         <v>46108</v>
       </c>
@@ -3831,7 +3841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B5" s="15">
         <v>46111</v>
       </c>
@@ -3872,7 +3882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:17" ht="33" x14ac:dyDescent="0.3">
       <c r="B6" s="15">
         <v>46112</v>
       </c>
@@ -3913,7 +3923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B7" s="15">
         <v>46113</v>
       </c>
@@ -3954,7 +3964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B8" s="15">
         <v>46114</v>
       </c>
@@ -3995,7 +4005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B9" s="15">
         <v>46115</v>
       </c>
@@ -4036,7 +4046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B10" s="15">
         <v>46118</v>
       </c>
@@ -4077,7 +4087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B11" s="15">
         <v>46119</v>
       </c>
@@ -4118,7 +4128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B12" s="15">
         <v>46120</v>
       </c>
@@ -4159,7 +4169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B13" s="15">
         <v>46121</v>
       </c>
@@ -4200,7 +4210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B14" s="15">
         <v>46122</v>
       </c>
@@ -4241,7 +4251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B15" s="15">
         <v>46125</v>
       </c>
@@ -4282,7 +4292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="15">
         <v>46126</v>
       </c>
@@ -4323,7 +4333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" s="15">
         <v>46127</v>
       </c>
@@ -4346,7 +4356,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B18" s="15">
         <v>46128</v>
       </c>
@@ -4369,7 +4379,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="15">
         <v>46129</v>
       </c>
@@ -4392,7 +4402,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="15">
         <v>46132</v>
       </c>
@@ -4415,7 +4425,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="15">
         <v>46133</v>
       </c>
@@ -4438,7 +4448,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B22" s="15">
         <v>46134</v>
       </c>
@@ -4461,7 +4471,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="15">
         <v>46135</v>
       </c>
@@ -4484,7 +4494,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="15">
         <v>46136</v>
       </c>
@@ -4507,7 +4517,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B25" s="15">
         <v>46139</v>
       </c>
@@ -4530,7 +4540,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B26" s="15">
         <v>46140</v>
       </c>
@@ -4553,7 +4563,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B27" s="15">
         <v>46141</v>
       </c>
@@ -4576,7 +4586,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B28" s="16">
         <v>46142</v>
       </c>
@@ -4599,7 +4609,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="2"/>
       <c r="C29" s="4"/>
       <c r="D29" s="2"/>
@@ -4608,10 +4618,10 @@
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C30" s="3"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C31" s="3"/>
     </row>
   </sheetData>
@@ -4621,15 +4631,15 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B1:Q31"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="2:17" ht="87.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:17" ht="83.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="13" t="s">
         <v>30</v>
       </c>
@@ -4673,7 +4683,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:17" ht="33" x14ac:dyDescent="0.3">
       <c r="B3" s="14">
         <v>46107</v>
       </c>
@@ -4714,7 +4724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:17" ht="33" x14ac:dyDescent="0.3">
       <c r="B4" s="15">
         <v>46108</v>
       </c>
@@ -4755,7 +4765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B5" s="15">
         <v>46111</v>
       </c>
@@ -4796,7 +4806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:17" ht="33" x14ac:dyDescent="0.3">
       <c r="B6" s="15">
         <v>46112</v>
       </c>
@@ -4837,7 +4847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B7" s="15">
         <v>46113</v>
       </c>
@@ -4878,7 +4888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B8" s="15">
         <v>46114</v>
       </c>
@@ -4919,7 +4929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B9" s="15">
         <v>46115</v>
       </c>
@@ -4960,7 +4970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B10" s="15">
         <v>46118</v>
       </c>
@@ -5001,7 +5011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B11" s="15">
         <v>46119</v>
       </c>
@@ -5042,7 +5052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B12" s="15">
         <v>46120</v>
       </c>
@@ -5083,7 +5093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B13" s="15">
         <v>46121</v>
       </c>
@@ -5124,7 +5134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B14" s="15">
         <v>46122</v>
       </c>
@@ -5165,7 +5175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B15" s="15">
         <v>46125</v>
       </c>
@@ -5206,7 +5216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="15">
         <v>46126</v>
       </c>
@@ -5247,7 +5257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" s="15">
         <v>46127</v>
       </c>
@@ -5270,7 +5280,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B18" s="15">
         <v>46128</v>
       </c>
@@ -5293,7 +5303,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="15">
         <v>46129</v>
       </c>
@@ -5316,7 +5326,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="15">
         <v>46132</v>
       </c>
@@ -5339,7 +5349,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="15">
         <v>46133</v>
       </c>
@@ -5362,7 +5372,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B22" s="15">
         <v>46134</v>
       </c>
@@ -5385,7 +5395,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="15">
         <v>46135</v>
       </c>
@@ -5408,7 +5418,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="15">
         <v>46136</v>
       </c>
@@ -5431,7 +5441,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B25" s="15">
         <v>46139</v>
       </c>
@@ -5454,7 +5464,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B26" s="15">
         <v>46140</v>
       </c>
@@ -5477,7 +5487,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B27" s="15">
         <v>46141</v>
       </c>
@@ -5500,7 +5510,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B28" s="16">
         <v>46142</v>
       </c>
@@ -5523,7 +5533,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="2"/>
       <c r="C29" s="4"/>
       <c r="D29" s="2"/>
@@ -5532,10 +5542,10 @@
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C30" s="3"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C31" s="3"/>
     </row>
   </sheetData>
@@ -5545,15 +5555,15 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B1:Q31"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="2:17" ht="87.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:17" ht="83.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="13" t="s">
         <v>30</v>
       </c>
@@ -5597,7 +5607,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:17" ht="33" x14ac:dyDescent="0.3">
       <c r="B3" s="14">
         <v>46107</v>
       </c>
@@ -5638,7 +5648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:17" ht="33" x14ac:dyDescent="0.3">
       <c r="B4" s="15">
         <v>46108</v>
       </c>
@@ -5679,7 +5689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B5" s="15">
         <v>46111</v>
       </c>
@@ -5720,7 +5730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:17" ht="33" x14ac:dyDescent="0.3">
       <c r="B6" s="15">
         <v>46112</v>
       </c>
@@ -5761,7 +5771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B7" s="15">
         <v>46113</v>
       </c>
@@ -5802,7 +5812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B8" s="15">
         <v>46114</v>
       </c>
@@ -5843,7 +5853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B9" s="15">
         <v>46115</v>
       </c>
@@ -5884,7 +5894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B10" s="15">
         <v>46118</v>
       </c>
@@ -5925,7 +5935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B11" s="15">
         <v>46119</v>
       </c>
@@ -5966,7 +5976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B12" s="15">
         <v>46120</v>
       </c>
@@ -6007,7 +6017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B13" s="15">
         <v>46121</v>
       </c>
@@ -6048,7 +6058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B14" s="15">
         <v>46122</v>
       </c>
@@ -6089,7 +6099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B15" s="15">
         <v>46125</v>
       </c>
@@ -6130,7 +6140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="15">
         <v>46126</v>
       </c>
@@ -6171,7 +6181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" s="15">
         <v>46127</v>
       </c>
@@ -6194,7 +6204,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B18" s="15">
         <v>46128</v>
       </c>
@@ -6217,7 +6227,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="15">
         <v>46129</v>
       </c>
@@ -6240,7 +6250,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="15">
         <v>46132</v>
       </c>
@@ -6263,7 +6273,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="15">
         <v>46133</v>
       </c>
@@ -6286,7 +6296,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B22" s="15">
         <v>46134</v>
       </c>
@@ -6309,7 +6319,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="15">
         <v>46135</v>
       </c>
@@ -6332,7 +6342,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="15">
         <v>46136</v>
       </c>
@@ -6355,7 +6365,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B25" s="15">
         <v>46139</v>
       </c>
@@ -6378,7 +6388,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B26" s="15">
         <v>46140</v>
       </c>
@@ -6401,7 +6411,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B27" s="15">
         <v>46141</v>
       </c>
@@ -6424,7 +6434,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B28" s="16">
         <v>46142</v>
       </c>
@@ -6447,7 +6457,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="2"/>
       <c r="C29" s="4"/>
       <c r="D29" s="2"/>
@@ -6456,10 +6466,10 @@
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C30" s="3"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C31" s="3"/>
     </row>
   </sheetData>
@@ -6469,15 +6479,15 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="B1:Q31"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="2:17" ht="87.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:17" ht="83.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="13" t="s">
         <v>30</v>
       </c>
@@ -6521,7 +6531,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:17" ht="33" x14ac:dyDescent="0.3">
       <c r="B3" s="14">
         <v>46107</v>
       </c>
@@ -6562,7 +6572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:17" ht="33" x14ac:dyDescent="0.3">
       <c r="B4" s="15">
         <v>46108</v>
       </c>
@@ -6603,7 +6613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B5" s="15">
         <v>46111</v>
       </c>
@@ -6644,7 +6654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:17" ht="33" x14ac:dyDescent="0.3">
       <c r="B6" s="15">
         <v>46112</v>
       </c>
@@ -6685,7 +6695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B7" s="15">
         <v>46113</v>
       </c>
@@ -6726,7 +6736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B8" s="15">
         <v>46114</v>
       </c>
@@ -6767,7 +6777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B9" s="15">
         <v>46115</v>
       </c>
@@ -6808,7 +6818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B10" s="15">
         <v>46118</v>
       </c>
@@ -6849,7 +6859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B11" s="15">
         <v>46119</v>
       </c>
@@ -6890,7 +6900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B12" s="15">
         <v>46120</v>
       </c>
@@ -6931,7 +6941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B13" s="15">
         <v>46121</v>
       </c>
@@ -6972,7 +6982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B14" s="15">
         <v>46122</v>
       </c>
@@ -7013,7 +7023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B15" s="15">
         <v>46125</v>
       </c>
@@ -7054,7 +7064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="15">
         <v>46126</v>
       </c>
@@ -7095,7 +7105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" s="15">
         <v>46127</v>
       </c>
@@ -7118,7 +7128,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B18" s="15">
         <v>46128</v>
       </c>
@@ -7141,7 +7151,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="15">
         <v>46129</v>
       </c>
@@ -7164,7 +7174,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="15">
         <v>46132</v>
       </c>
@@ -7187,7 +7197,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="15">
         <v>46133</v>
       </c>
@@ -7210,7 +7220,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B22" s="15">
         <v>46134</v>
       </c>
@@ -7233,7 +7243,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="15">
         <v>46135</v>
       </c>
@@ -7256,7 +7266,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="15">
         <v>46136</v>
       </c>
@@ -7279,7 +7289,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B25" s="15">
         <v>46139</v>
       </c>
@@ -7302,7 +7312,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B26" s="15">
         <v>46140</v>
       </c>
@@ -7325,7 +7335,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B27" s="15">
         <v>46141</v>
       </c>
@@ -7348,7 +7358,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B28" s="16">
         <v>46142</v>
       </c>
@@ -7371,7 +7381,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="2"/>
       <c r="C29" s="4"/>
       <c r="D29" s="2"/>
@@ -7380,10 +7390,10 @@
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C30" s="3"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C31" s="3"/>
     </row>
   </sheetData>

--- a/daily.xml.xlsx
+++ b/daily.xml.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hyojung2\2026-AI-FULLSTACK-LevelUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC8190BB-AC02-4BE3-AD2E-58ADF7E5D978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46B40B8C-E12C-4F0D-862C-B23B5FC613AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1282" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1283" uniqueCount="45">
   <si>
     <t>출석일수 (Attendance Days)</t>
   </si>
@@ -170,6 +170,23 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
+    <t>7일</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>12일</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>BANK-CONTROL</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>전원 출석
+- 김현미외출</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">복습문제
 협업마스터 
@@ -186,21 +203,20 @@
         <scheme val="minor"/>
       </rPr>
       <t>이일두님추천
-- 장영탁, 김현미
+- 장영탁, 임채연
 최다영추천 - 정수정</t>
     </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>7일</t>
+    <t xml:space="preserve"> </t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>12일</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>BANK-CONTROL</t>
+    <t xml:space="preserve"> 복습문제
+html - css-ckeck1
+java - 계산기1
+java - 성적처리</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -331,7 +347,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="38">
+  <borders count="37">
     <border>
       <left/>
       <right/>
@@ -685,17 +701,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -855,7 +860,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -985,31 +990,28 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="28" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="30" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="31" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="32" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="33" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1024,13 +1026,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1039,10 +1041,10 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1345,25 +1347,25 @@
       <c r="B1" s="1"/>
     </row>
     <row r="2" spans="2:17" ht="49.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="48" t="s">
+      <c r="C2" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="49" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="50" t="s">
+      <c r="D2" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="50" t="s">
-        <v>3</v>
-      </c>
-      <c r="H2" s="51" t="s">
+      <c r="G2" s="49" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="50" t="s">
         <v>4</v>
       </c>
       <c r="J2" s="28" t="s">
@@ -1389,32 +1391,32 @@
       </c>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B3" s="56">
+      <c r="B3" s="55">
         <v>46107</v>
       </c>
-      <c r="C3" s="57" t="s">
+      <c r="C3" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="44" t="s">
+      <c r="D3" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="44" t="s">
+      <c r="E3" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="45">
-        <v>1</v>
-      </c>
-      <c r="G3" s="45" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" s="46" t="s">
+      <c r="F3" s="44">
+        <v>1</v>
+      </c>
+      <c r="G3" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="45" t="s">
         <v>23</v>
       </c>
       <c r="J3" s="29" t="s">
         <v>5</v>
       </c>
       <c r="K3" s="30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L3" s="31">
         <v>1</v>
@@ -1423,20 +1425,20 @@
         <v>1</v>
       </c>
       <c r="N3" s="31">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O3" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="58">
+      <c r="B4" s="57">
         <v>46108</v>
       </c>
-      <c r="C4" s="59" t="s">
+      <c r="C4" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="60" t="s">
+      <c r="D4" s="59" t="s">
         <v>22</v>
       </c>
       <c r="E4" s="7" t="s">
@@ -1455,7 +1457,7 @@
         <v>6</v>
       </c>
       <c r="K4" s="30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L4" s="35">
         <v>1</v>
@@ -1464,39 +1466,39 @@
         <v>1</v>
       </c>
       <c r="N4" s="31">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O4" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B5" s="56">
+      <c r="B5" s="55">
         <v>46111</v>
       </c>
-      <c r="C5" s="57" t="s">
+      <c r="C5" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="44" t="s">
+      <c r="D5" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="45" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="45" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="44" t="s">
+      <c r="E5" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="46" t="s">
+      <c r="H5" s="45" t="s">
         <v>23</v>
       </c>
       <c r="J5" s="33" t="s">
         <v>7</v>
       </c>
       <c r="K5" s="30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L5" s="35">
         <v>1</v>
@@ -1505,17 +1507,17 @@
         <v>1</v>
       </c>
       <c r="N5" s="31">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O5" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B6" s="61">
+      <c r="B6" s="60">
         <v>46112</v>
       </c>
-      <c r="C6" s="53" t="s">
+      <c r="C6" s="52" t="s">
         <v>28</v>
       </c>
       <c r="D6" s="42" t="s">
@@ -1537,7 +1539,7 @@
         <v>8</v>
       </c>
       <c r="K6" s="30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L6" s="35">
         <v>1</v>
@@ -1546,17 +1548,17 @@
         <v>1</v>
       </c>
       <c r="N6" s="31">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O6" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:17" ht="69.75" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="61">
-        <v>46113</v>
-      </c>
-      <c r="C7" s="53" t="s">
+      <c r="B7" s="60">
+        <v>46266</v>
+      </c>
+      <c r="C7" s="52" t="s">
         <v>29</v>
       </c>
       <c r="D7" s="42" t="s">
@@ -1569,7 +1571,7 @@
         <v>23</v>
       </c>
       <c r="G7" s="42" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>23</v>
@@ -1578,7 +1580,7 @@
         <v>9</v>
       </c>
       <c r="K7" s="30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L7" s="35">
         <v>1</v>
@@ -1587,20 +1589,20 @@
         <v>1</v>
       </c>
       <c r="N7" s="31">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O7" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B8" s="61">
-        <v>46114</v>
-      </c>
-      <c r="C8" s="53" t="s">
+    <row r="8" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="60">
+        <v>46267</v>
+      </c>
+      <c r="C8" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="44" t="s">
+      <c r="D8" s="43" t="s">
         <v>21</v>
       </c>
       <c r="E8" s="5" t="s">
@@ -1619,7 +1621,7 @@
         <v>10</v>
       </c>
       <c r="K8" s="30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L8" s="35">
         <v>1</v>
@@ -1628,42 +1630,42 @@
         <v>1</v>
       </c>
       <c r="N8" s="31">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O8" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:17" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="58">
-        <v>46115</v>
-      </c>
-      <c r="C9" s="59" t="s">
+    <row r="9" spans="2:17" ht="66.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="57">
+        <v>46268</v>
+      </c>
+      <c r="C9" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>23</v>
+      <c r="D9" s="43" t="s">
+        <v>41</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F9" s="7">
         <v>1</v>
       </c>
-      <c r="G9" s="7" t="s">
-        <v>23</v>
+      <c r="G9" s="42" t="s">
+        <v>44</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I9" s="62" t="s">
-        <v>39</v>
+      <c r="I9" s="61" t="s">
+        <v>38</v>
       </c>
       <c r="J9" s="33" t="s">
         <v>11</v>
       </c>
       <c r="K9" s="30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L9" s="35">
         <v>1</v>
@@ -1672,39 +1674,39 @@
         <v>1</v>
       </c>
       <c r="N9" s="31">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O9" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B10" s="56">
-        <v>46118</v>
-      </c>
-      <c r="C10" s="57" t="s">
+      <c r="B10" s="55">
+        <v>46271</v>
+      </c>
+      <c r="C10" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="45" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="45" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="45" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" s="45" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" s="46" t="s">
+      <c r="D10" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="45" t="s">
         <v>23</v>
       </c>
       <c r="J10" s="33" t="s">
         <v>12</v>
       </c>
       <c r="K10" s="30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L10" s="35">
         <v>1</v>
@@ -1713,17 +1715,17 @@
         <v>1</v>
       </c>
       <c r="N10" s="31">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O10" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B11" s="61">
-        <v>46119</v>
-      </c>
-      <c r="C11" s="53" t="s">
+      <c r="B11" s="60">
+        <v>46272</v>
+      </c>
+      <c r="C11" s="52" t="s">
         <v>28</v>
       </c>
       <c r="D11" s="5" t="s">
@@ -1745,7 +1747,7 @@
         <v>13</v>
       </c>
       <c r="K11" s="30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L11" s="35">
         <v>1</v>
@@ -1754,17 +1756,17 @@
         <v>1</v>
       </c>
       <c r="N11" s="31">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O11" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B12" s="61">
-        <v>46120</v>
-      </c>
-      <c r="C12" s="53" t="s">
+      <c r="B12" s="60">
+        <v>46273</v>
+      </c>
+      <c r="C12" s="52" t="s">
         <v>29</v>
       </c>
       <c r="D12" s="5" t="s">
@@ -1786,7 +1788,7 @@
         <v>14</v>
       </c>
       <c r="K12" s="30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L12" s="35">
         <v>1</v>
@@ -1795,17 +1797,17 @@
         <v>1</v>
       </c>
       <c r="N12" s="31">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O12" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B13" s="61">
-        <v>46121</v>
-      </c>
-      <c r="C13" s="53" t="s">
+      <c r="B13" s="60">
+        <v>46274</v>
+      </c>
+      <c r="C13" s="52" t="s">
         <v>25</v>
       </c>
       <c r="D13" s="5" t="s">
@@ -1827,7 +1829,7 @@
         <v>15</v>
       </c>
       <c r="K13" s="30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L13" s="35">
         <v>1</v>
@@ -1836,17 +1838,17 @@
         <v>1</v>
       </c>
       <c r="N13" s="31">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O13" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="58">
-        <v>46122</v>
-      </c>
-      <c r="C14" s="59" t="s">
+      <c r="B14" s="57">
+        <v>46275</v>
+      </c>
+      <c r="C14" s="58" t="s">
         <v>26</v>
       </c>
       <c r="D14" s="7" t="s">
@@ -1864,14 +1866,14 @@
       <c r="H14" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I14" s="62" t="s">
-        <v>40</v>
+      <c r="I14" s="61" t="s">
+        <v>39</v>
       </c>
       <c r="J14" s="33" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L14" s="35">
         <v>1</v>
@@ -1880,39 +1882,39 @@
         <v>1</v>
       </c>
       <c r="N14" s="31">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O14" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B15" s="56">
-        <v>46125</v>
-      </c>
-      <c r="C15" s="57" t="s">
+      <c r="B15" s="55">
+        <v>46278</v>
+      </c>
+      <c r="C15" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="45" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" s="45" t="s">
-        <v>23</v>
-      </c>
-      <c r="F15" s="45" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15" s="45" t="s">
-        <v>23</v>
-      </c>
-      <c r="H15" s="46" t="s">
+      <c r="D15" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" s="45" t="s">
         <v>23</v>
       </c>
       <c r="J15" s="33" t="s">
         <v>17</v>
       </c>
       <c r="K15" s="30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L15" s="35">
         <v>1</v>
@@ -1921,17 +1923,17 @@
         <v>1</v>
       </c>
       <c r="N15" s="31">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O15" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="61">
-        <v>46126</v>
-      </c>
-      <c r="C16" s="53" t="s">
+      <c r="B16" s="60">
+        <v>46284</v>
+      </c>
+      <c r="C16" s="52" t="s">
         <v>28</v>
       </c>
       <c r="D16" s="5" t="s">
@@ -1952,8 +1954,8 @@
       <c r="J16" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="K16" s="43">
-        <v>6</v>
+      <c r="K16" s="30">
+        <v>7</v>
       </c>
       <c r="L16" s="39">
         <v>1</v>
@@ -1962,17 +1964,17 @@
         <v>1</v>
       </c>
       <c r="N16" s="41">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O16" s="40">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B17" s="61">
+      <c r="B17" s="60">
         <v>46127</v>
       </c>
-      <c r="C17" s="53" t="s">
+      <c r="C17" s="52" t="s">
         <v>29</v>
       </c>
       <c r="D17" s="5" t="s">
@@ -1992,10 +1994,10 @@
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B18" s="61">
+      <c r="B18" s="60">
         <v>46128</v>
       </c>
-      <c r="C18" s="53" t="s">
+      <c r="C18" s="52" t="s">
         <v>25</v>
       </c>
       <c r="D18" s="5" t="s">
@@ -2015,10 +2017,10 @@
       </c>
     </row>
     <row r="19" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="58">
+      <c r="B19" s="57">
         <v>46129</v>
       </c>
-      <c r="C19" s="59" t="s">
+      <c r="C19" s="58" t="s">
         <v>26</v>
       </c>
       <c r="D19" s="7" t="s">
@@ -2038,33 +2040,33 @@
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B20" s="56">
+      <c r="B20" s="55">
         <v>46132</v>
       </c>
-      <c r="C20" s="57" t="s">
+      <c r="C20" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="45" t="s">
-        <v>23</v>
-      </c>
-      <c r="E20" s="45" t="s">
-        <v>23</v>
-      </c>
-      <c r="F20" s="45" t="s">
-        <v>23</v>
-      </c>
-      <c r="G20" s="45" t="s">
-        <v>23</v>
-      </c>
-      <c r="H20" s="46" t="s">
+      <c r="D20" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="F20" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="45" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B21" s="61">
+      <c r="B21" s="60">
         <v>46133</v>
       </c>
-      <c r="C21" s="53" t="s">
+      <c r="C21" s="52" t="s">
         <v>28</v>
       </c>
       <c r="D21" s="5" t="s">
@@ -2084,10 +2086,10 @@
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B22" s="61">
+      <c r="B22" s="60">
         <v>46134</v>
       </c>
-      <c r="C22" s="53" t="s">
+      <c r="C22" s="52" t="s">
         <v>29</v>
       </c>
       <c r="D22" s="5" t="s">
@@ -2107,10 +2109,10 @@
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B23" s="61">
+      <c r="B23" s="60">
         <v>46135</v>
       </c>
-      <c r="C23" s="53" t="s">
+      <c r="C23" s="52" t="s">
         <v>25</v>
       </c>
       <c r="D23" s="5" t="s">
@@ -2130,10 +2132,10 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="58">
+      <c r="B24" s="57">
         <v>46136</v>
       </c>
-      <c r="C24" s="59" t="s">
+      <c r="C24" s="58" t="s">
         <v>26</v>
       </c>
       <c r="D24" s="7" t="s">
@@ -2153,10 +2155,10 @@
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B25" s="54">
+      <c r="B25" s="53">
         <v>46139</v>
       </c>
-      <c r="C25" s="55" t="s">
+      <c r="C25" s="54" t="s">
         <v>27</v>
       </c>
       <c r="D25" s="9" t="s">
@@ -2176,10 +2178,10 @@
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B26" s="52">
+      <c r="B26" s="51">
         <v>46140</v>
       </c>
-      <c r="C26" s="53" t="s">
+      <c r="C26" s="52" t="s">
         <v>28</v>
       </c>
       <c r="D26" s="5" t="s">
@@ -2199,10 +2201,10 @@
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B27" s="52">
+      <c r="B27" s="51">
         <v>46141</v>
       </c>
-      <c r="C27" s="53" t="s">
+      <c r="C27" s="52" t="s">
         <v>29</v>
       </c>
       <c r="D27" s="5" t="s">
@@ -2222,10 +2224,10 @@
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B28" s="52">
+      <c r="B28" s="51">
         <v>46142</v>
       </c>
-      <c r="C28" s="53" t="s">
+      <c r="C28" s="52" t="s">
         <v>25</v>
       </c>
       <c r="D28" s="5" t="s">
@@ -2253,7 +2255,9 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
+      <c r="G29" s="42" t="s">
+        <v>43</v>
+      </c>
       <c r="H29" s="2"/>
     </row>
   </sheetData>

--- a/daily.xml.xlsx
+++ b/daily.xml.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hyojung2\2026-AI-FULLSTACK-LevelUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46B40B8C-E12C-4F0D-862C-B23B5FC613AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6EA39DD-59D0-47DC-83C5-9253E70B6C24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1283" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1283" uniqueCount="46">
   <si>
     <t>출석일수 (Attendance Days)</t>
   </si>
@@ -213,10 +213,32 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
+    <r>
+      <t xml:space="preserve">복습문제
+협업마스터 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FF006100"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>임채연님 - 최윤정님추천</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
     <t xml:space="preserve"> 복습문제
 html - css-ckeck1
 java - 계산기1
-java - 성적처리</t>
+java - 성적처리
+협업마스터
+</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -227,7 +249,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -316,6 +338,15 @@
     <font>
       <b/>
       <sz val="9"/>
+      <color rgb="FF006100"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
       <color rgb="FF006100"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
@@ -1595,7 +1626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:17" ht="45" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="60">
         <v>46267</v>
       </c>
@@ -1612,7 +1643,7 @@
         <v>23</v>
       </c>
       <c r="G8" s="42" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>23</v>
@@ -1636,7 +1667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:17" ht="66.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:17" ht="99.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="57">
         <v>46268</v>
       </c>
@@ -1653,7 +1684,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="42" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>23</v>
@@ -1923,7 +1954,7 @@
         <v>1</v>
       </c>
       <c r="N15" s="31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O15" s="36">
         <v>0</v>

--- a/daily.xml.xlsx
+++ b/daily.xml.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sally03915\Desktop\2026.03-ing\2026-출석부\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hyojung2\2026-AI-FULLSTACK-LevelUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3404C01F-571C-45E4-B644-2EBE5472C9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026. 3~4월" sheetId="1" r:id="rId1"/>
@@ -20,7 +21,7 @@
     <sheet name="2026.9" sheetId="6" r:id="rId6"/>
     <sheet name="2026.10" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1283" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1283" uniqueCount="50">
   <si>
     <t>출석일수 (Attendance Days)</t>
   </si>
@@ -186,10 +187,13 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">복습문제
-협업마스터 
-</t>
+협업마스터 </t>
     </r>
     <r>
       <rPr>
@@ -201,14 +205,33 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>이일두님추천
+      <t xml:space="preserve">
 - 장영탁, 임채연
-최다영추천 - 정수정</t>
+- 정수정</t>
     </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <r>
+      <t xml:space="preserve"> 복습문제
+html - css-ckeck1
+java - 계산기1
+java - 성적처리
+협업마스터 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FF006100"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- 김보라-하혜원</t>
+    </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -227,16 +250,19 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>임채연님 - 최윤정님추천</t>
+      <t>최윤정</t>
     </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
+    <t xml:space="preserve">복습문제
+협업마스터
+</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
     <r>
-      <t xml:space="preserve"> 복습문제
-html - css-ckeck1
-java - 계산기1
-java - 성적처리
+      <t xml:space="preserve">복습문제
 협업마스터
 </t>
     </r>
@@ -250,8 +276,30 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>김욱진님추천 
-- 김보라-하혜원</t>
+      <t>- 김주엽- 최윤정</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>전원 출석</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>전원 출석
+-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF006100"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 최윤정 지각(상담)</t>
     </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -259,7 +307,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
@@ -1374,24 +1422,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:Q29"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="12.09765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.69921875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="18.8984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.69921875" customWidth="1"/>
-    <col min="6" max="6" width="14.19921875" customWidth="1"/>
-    <col min="7" max="7" width="16.19921875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.09765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.75" style="3" customWidth="1"/>
+    <col min="4" max="4" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.75" customWidth="1"/>
+    <col min="6" max="6" width="14.25" customWidth="1"/>
+    <col min="7" max="7" width="16.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="2:17" ht="49.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:17" ht="49.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="46" t="s">
         <v>30</v>
       </c>
@@ -1435,7 +1483,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B3" s="55">
         <v>46107</v>
       </c>
@@ -1476,7 +1524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="57">
         <v>46108</v>
       </c>
@@ -1517,7 +1565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B5" s="55">
         <v>46111</v>
       </c>
@@ -1558,7 +1606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B6" s="60">
         <v>46112</v>
       </c>
@@ -1599,9 +1647,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:17" ht="75" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:17" ht="57.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="60">
-        <v>46266</v>
+        <v>46113</v>
       </c>
       <c r="C7" s="52" t="s">
         <v>29</v>
@@ -1616,7 +1664,7 @@
         <v>23</v>
       </c>
       <c r="G7" s="42" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>23</v>
@@ -1640,9 +1688,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:17" ht="46.2" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:17" ht="45" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="60">
-        <v>46267</v>
+        <v>46114</v>
       </c>
       <c r="C8" s="52" t="s">
         <v>25</v>
@@ -1657,7 +1705,7 @@
         <v>23</v>
       </c>
       <c r="G8" s="42" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>23</v>
@@ -1681,9 +1729,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:17" ht="109.2" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B9" s="57">
-        <v>46268</v>
+    <row r="9" spans="2:17" ht="94.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="60">
+        <v>46115</v>
       </c>
       <c r="C9" s="58" t="s">
         <v>26</v>
@@ -1698,7 +1746,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="42" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>23</v>
@@ -1725,15 +1773,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:17" ht="45" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="55">
-        <v>46271</v>
+        <v>46118</v>
       </c>
       <c r="C10" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="44" t="s">
-        <v>23</v>
+      <c r="D10" s="43" t="s">
+        <v>48</v>
       </c>
       <c r="E10" s="44" t="s">
         <v>23</v>
@@ -1741,8 +1789,8 @@
       <c r="F10" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="44" t="s">
-        <v>23</v>
+      <c r="G10" s="43" t="s">
+        <v>47</v>
       </c>
       <c r="H10" s="45" t="s">
         <v>23</v>
@@ -1766,15 +1814,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.4">
-      <c r="B11" s="60">
-        <v>46272</v>
+    <row r="11" spans="2:17" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="55">
+        <v>46119</v>
       </c>
       <c r="C11" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>23</v>
+      <c r="D11" s="43" t="s">
+        <v>49</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>23</v>
@@ -1782,8 +1830,8 @@
       <c r="F11" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>23</v>
+      <c r="G11" s="42" t="s">
+        <v>46</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>23</v>
@@ -1807,9 +1855,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.4">
-      <c r="B12" s="60">
-        <v>46273</v>
+    <row r="12" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="55">
+        <v>46120</v>
       </c>
       <c r="C12" s="52" t="s">
         <v>29</v>
@@ -1848,9 +1896,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.4">
-      <c r="B13" s="60">
-        <v>46274</v>
+    <row r="13" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="55">
+        <v>46121</v>
       </c>
       <c r="C13" s="52" t="s">
         <v>25</v>
@@ -1889,9 +1937,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B14" s="57">
-        <v>46275</v>
+    <row r="14" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="55">
+        <v>46122</v>
       </c>
       <c r="C14" s="58" t="s">
         <v>26</v>
@@ -1933,9 +1981,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="55">
-        <v>46278</v>
+        <v>46125</v>
       </c>
       <c r="C15" s="56" t="s">
         <v>27</v>
@@ -1974,9 +2022,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B16" s="60">
-        <v>46284</v>
+    <row r="16" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="55">
+        <v>46126</v>
       </c>
       <c r="C16" s="52" t="s">
         <v>28</v>
@@ -2015,8 +2063,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B17" s="60">
+    <row r="17" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="55">
         <v>46127</v>
       </c>
       <c r="C17" s="52" t="s">
@@ -2038,8 +2086,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B18" s="60">
+    <row r="18" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="55">
         <v>46128</v>
       </c>
       <c r="C18" s="52" t="s">
@@ -2061,8 +2109,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B19" s="57">
+    <row r="19" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="55">
         <v>46129</v>
       </c>
       <c r="C19" s="58" t="s">
@@ -2084,7 +2132,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="55">
         <v>46132</v>
       </c>
@@ -2107,7 +2155,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="60">
         <v>46133</v>
       </c>
@@ -2130,7 +2178,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B22" s="60">
         <v>46134</v>
       </c>
@@ -2153,7 +2201,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="60">
         <v>46135</v>
       </c>
@@ -2176,7 +2224,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="57">
         <v>46136</v>
       </c>
@@ -2199,7 +2247,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B25" s="53">
         <v>46139</v>
       </c>
@@ -2222,7 +2270,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B26" s="51">
         <v>46140</v>
       </c>
@@ -2245,7 +2293,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B27" s="51">
         <v>46141</v>
       </c>
@@ -2268,7 +2316,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B28" s="51">
         <v>46142</v>
       </c>
@@ -2291,7 +2339,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="2"/>
       <c r="C29" s="4"/>
       <c r="D29" s="2">
@@ -2301,7 +2349,7 @@
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
       <c r="G29" s="42" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H29" s="2"/>
     </row>
@@ -2313,19 +2361,19 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:Q31"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.8984375" customWidth="1"/>
+    <col min="2" max="2" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="2:17" ht="87.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:17" ht="83.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="13" t="s">
         <v>30</v>
       </c>
@@ -2369,7 +2417,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:17" ht="33" x14ac:dyDescent="0.3">
       <c r="B3" s="14">
         <v>46107</v>
       </c>
@@ -2400,7 +2448,7 @@
       <c r="N3" s="31"/>
       <c r="O3" s="32"/>
     </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B4" s="15">
         <v>46108</v>
       </c>
@@ -2431,7 +2479,7 @@
       <c r="N4" s="35"/>
       <c r="O4" s="36"/>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B5" s="15">
         <v>46111</v>
       </c>
@@ -2462,7 +2510,7 @@
       <c r="N5" s="35"/>
       <c r="O5" s="36"/>
     </row>
-    <row r="6" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:17" ht="33" x14ac:dyDescent="0.3">
       <c r="B6" s="15">
         <v>46112</v>
       </c>
@@ -2493,7 +2541,7 @@
       <c r="N6" s="35"/>
       <c r="O6" s="36"/>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B7" s="15">
         <v>46113</v>
       </c>
@@ -2524,7 +2572,7 @@
       <c r="N7" s="35"/>
       <c r="O7" s="36"/>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B8" s="15">
         <v>46114</v>
       </c>
@@ -2555,7 +2603,7 @@
       <c r="N8" s="35"/>
       <c r="O8" s="36"/>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B9" s="15">
         <v>46115</v>
       </c>
@@ -2586,7 +2634,7 @@
       <c r="N9" s="35"/>
       <c r="O9" s="36"/>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B10" s="15">
         <v>46118</v>
       </c>
@@ -2617,7 +2665,7 @@
       <c r="N10" s="35"/>
       <c r="O10" s="36"/>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B11" s="15">
         <v>46119</v>
       </c>
@@ -2648,7 +2696,7 @@
       <c r="N11" s="35"/>
       <c r="O11" s="36"/>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B12" s="15">
         <v>46120</v>
       </c>
@@ -2679,7 +2727,7 @@
       <c r="N12" s="35"/>
       <c r="O12" s="36"/>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B13" s="15">
         <v>46121</v>
       </c>
@@ -2710,7 +2758,7 @@
       <c r="N13" s="35"/>
       <c r="O13" s="36"/>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B14" s="15">
         <v>46122</v>
       </c>
@@ -2741,7 +2789,7 @@
       <c r="N14" s="35"/>
       <c r="O14" s="36"/>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B15" s="15">
         <v>46125</v>
       </c>
@@ -2772,7 +2820,7 @@
       <c r="N15" s="35"/>
       <c r="O15" s="36"/>
     </row>
-    <row r="16" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="15">
         <v>46126</v>
       </c>
@@ -2803,7 +2851,7 @@
       <c r="N16" s="39"/>
       <c r="O16" s="40"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" s="15">
         <v>46127</v>
       </c>
@@ -2826,7 +2874,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B18" s="15">
         <v>46128</v>
       </c>
@@ -2849,7 +2897,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="15">
         <v>46129</v>
       </c>
@@ -2872,7 +2920,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="15">
         <v>46132</v>
       </c>
@@ -2895,7 +2943,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="15">
         <v>46133</v>
       </c>
@@ -2918,7 +2966,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B22" s="15">
         <v>46134</v>
       </c>
@@ -2941,7 +2989,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="15">
         <v>46135</v>
       </c>
@@ -2964,7 +3012,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="15">
         <v>46136</v>
       </c>
@@ -2987,7 +3035,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B25" s="15">
         <v>46139</v>
       </c>
@@ -3010,7 +3058,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B26" s="15">
         <v>46140</v>
       </c>
@@ -3033,7 +3081,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B27" s="15">
         <v>46141</v>
       </c>
@@ -3056,7 +3104,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B28" s="16">
         <v>46142</v>
       </c>
@@ -3079,7 +3127,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="2"/>
       <c r="C29" s="4"/>
       <c r="D29" s="2"/>
@@ -3088,10 +3136,10 @@
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C30" s="3"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C31" s="3"/>
     </row>
   </sheetData>
@@ -3101,15 +3149,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:Q31"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="2:17" ht="87.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:17" ht="83.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="13" t="s">
         <v>30</v>
       </c>
@@ -3153,7 +3201,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:17" ht="33" x14ac:dyDescent="0.3">
       <c r="B3" s="14">
         <v>46107</v>
       </c>
@@ -3194,7 +3242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:17" ht="33" x14ac:dyDescent="0.3">
       <c r="B4" s="15">
         <v>46108</v>
       </c>
@@ -3235,7 +3283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B5" s="15">
         <v>46111</v>
       </c>
@@ -3276,7 +3324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:17" ht="33" x14ac:dyDescent="0.3">
       <c r="B6" s="15">
         <v>46112</v>
       </c>
@@ -3317,7 +3365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B7" s="15">
         <v>46113</v>
       </c>
@@ -3358,7 +3406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B8" s="15">
         <v>46114</v>
       </c>
@@ -3399,7 +3447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B9" s="15">
         <v>46115</v>
       </c>
@@ -3440,7 +3488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B10" s="15">
         <v>46118</v>
       </c>
@@ -3481,7 +3529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B11" s="15">
         <v>46119</v>
       </c>
@@ -3522,7 +3570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B12" s="15">
         <v>46120</v>
       </c>
@@ -3563,7 +3611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B13" s="15">
         <v>46121</v>
       </c>
@@ -3604,7 +3652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B14" s="15">
         <v>46122</v>
       </c>
@@ -3645,7 +3693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B15" s="15">
         <v>46125</v>
       </c>
@@ -3686,7 +3734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="15">
         <v>46126</v>
       </c>
@@ -3727,7 +3775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" s="15">
         <v>46127</v>
       </c>
@@ -3750,7 +3798,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B18" s="15">
         <v>46128</v>
       </c>
@@ -3773,7 +3821,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="15">
         <v>46129</v>
       </c>
@@ -3796,7 +3844,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="15">
         <v>46132</v>
       </c>
@@ -3819,7 +3867,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="15">
         <v>46133</v>
       </c>
@@ -3842,7 +3890,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B22" s="15">
         <v>46134</v>
       </c>
@@ -3865,7 +3913,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="15">
         <v>46135</v>
       </c>
@@ -3888,7 +3936,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="15">
         <v>46136</v>
       </c>
@@ -3911,7 +3959,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B25" s="15">
         <v>46139</v>
       </c>
@@ -3934,7 +3982,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B26" s="15">
         <v>46140</v>
       </c>
@@ -3957,7 +4005,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B27" s="15">
         <v>46141</v>
       </c>
@@ -3980,7 +4028,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B28" s="16">
         <v>46142</v>
       </c>
@@ -4003,7 +4051,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="2"/>
       <c r="C29" s="4"/>
       <c r="D29" s="2"/>
@@ -4012,10 +4060,10 @@
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C30" s="3"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C31" s="3"/>
     </row>
   </sheetData>
@@ -4025,15 +4073,15 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B1:Q31"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="2:17" ht="87.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:17" ht="83.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="13" t="s">
         <v>30</v>
       </c>
@@ -4077,7 +4125,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:17" ht="33" x14ac:dyDescent="0.3">
       <c r="B3" s="14">
         <v>46107</v>
       </c>
@@ -4118,7 +4166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:17" ht="33" x14ac:dyDescent="0.3">
       <c r="B4" s="15">
         <v>46108</v>
       </c>
@@ -4159,7 +4207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B5" s="15">
         <v>46111</v>
       </c>
@@ -4200,7 +4248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:17" ht="33" x14ac:dyDescent="0.3">
       <c r="B6" s="15">
         <v>46112</v>
       </c>
@@ -4241,7 +4289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B7" s="15">
         <v>46113</v>
       </c>
@@ -4282,7 +4330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B8" s="15">
         <v>46114</v>
       </c>
@@ -4323,7 +4371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B9" s="15">
         <v>46115</v>
       </c>
@@ -4364,7 +4412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B10" s="15">
         <v>46118</v>
       </c>
@@ -4405,7 +4453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B11" s="15">
         <v>46119</v>
       </c>
@@ -4446,7 +4494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B12" s="15">
         <v>46120</v>
       </c>
@@ -4487,7 +4535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B13" s="15">
         <v>46121</v>
       </c>
@@ -4528,7 +4576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B14" s="15">
         <v>46122</v>
       </c>
@@ -4569,7 +4617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B15" s="15">
         <v>46125</v>
       </c>
@@ -4610,7 +4658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="15">
         <v>46126</v>
       </c>
@@ -4651,7 +4699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" s="15">
         <v>46127</v>
       </c>
@@ -4674,7 +4722,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B18" s="15">
         <v>46128</v>
       </c>
@@ -4697,7 +4745,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="15">
         <v>46129</v>
       </c>
@@ -4720,7 +4768,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="15">
         <v>46132</v>
       </c>
@@ -4743,7 +4791,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="15">
         <v>46133</v>
       </c>
@@ -4766,7 +4814,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B22" s="15">
         <v>46134</v>
       </c>
@@ -4789,7 +4837,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="15">
         <v>46135</v>
       </c>
@@ -4812,7 +4860,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="15">
         <v>46136</v>
       </c>
@@ -4835,7 +4883,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B25" s="15">
         <v>46139</v>
       </c>
@@ -4858,7 +4906,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B26" s="15">
         <v>46140</v>
       </c>
@@ -4881,7 +4929,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B27" s="15">
         <v>46141</v>
       </c>
@@ -4904,7 +4952,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B28" s="16">
         <v>46142</v>
       </c>
@@ -4927,7 +4975,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="2"/>
       <c r="C29" s="4"/>
       <c r="D29" s="2"/>
@@ -4936,10 +4984,10 @@
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C30" s="3"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C31" s="3"/>
     </row>
   </sheetData>
@@ -4949,15 +4997,15 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B1:Q31"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="2:17" ht="87.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:17" ht="83.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="13" t="s">
         <v>30</v>
       </c>
@@ -5001,7 +5049,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:17" ht="33" x14ac:dyDescent="0.3">
       <c r="B3" s="14">
         <v>46107</v>
       </c>
@@ -5042,7 +5090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:17" ht="33" x14ac:dyDescent="0.3">
       <c r="B4" s="15">
         <v>46108</v>
       </c>
@@ -5083,7 +5131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B5" s="15">
         <v>46111</v>
       </c>
@@ -5124,7 +5172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:17" ht="33" x14ac:dyDescent="0.3">
       <c r="B6" s="15">
         <v>46112</v>
       </c>
@@ -5165,7 +5213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B7" s="15">
         <v>46113</v>
       </c>
@@ -5206,7 +5254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B8" s="15">
         <v>46114</v>
       </c>
@@ -5247,7 +5295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B9" s="15">
         <v>46115</v>
       </c>
@@ -5288,7 +5336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B10" s="15">
         <v>46118</v>
       </c>
@@ -5329,7 +5377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B11" s="15">
         <v>46119</v>
       </c>
@@ -5370,7 +5418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B12" s="15">
         <v>46120</v>
       </c>
@@ -5411,7 +5459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B13" s="15">
         <v>46121</v>
       </c>
@@ -5452,7 +5500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B14" s="15">
         <v>46122</v>
       </c>
@@ -5493,7 +5541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B15" s="15">
         <v>46125</v>
       </c>
@@ -5534,7 +5582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="15">
         <v>46126</v>
       </c>
@@ -5575,7 +5623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" s="15">
         <v>46127</v>
       </c>
@@ -5598,7 +5646,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B18" s="15">
         <v>46128</v>
       </c>
@@ -5621,7 +5669,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="15">
         <v>46129</v>
       </c>
@@ -5644,7 +5692,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="15">
         <v>46132</v>
       </c>
@@ -5667,7 +5715,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="15">
         <v>46133</v>
       </c>
@@ -5690,7 +5738,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B22" s="15">
         <v>46134</v>
       </c>
@@ -5713,7 +5761,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="15">
         <v>46135</v>
       </c>
@@ -5736,7 +5784,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="15">
         <v>46136</v>
       </c>
@@ -5759,7 +5807,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B25" s="15">
         <v>46139</v>
       </c>
@@ -5782,7 +5830,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B26" s="15">
         <v>46140</v>
       </c>
@@ -5805,7 +5853,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B27" s="15">
         <v>46141</v>
       </c>
@@ -5828,7 +5876,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B28" s="16">
         <v>46142</v>
       </c>
@@ -5851,7 +5899,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="2"/>
       <c r="C29" s="4"/>
       <c r="D29" s="2"/>
@@ -5860,10 +5908,10 @@
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C30" s="3"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C31" s="3"/>
     </row>
   </sheetData>
@@ -5873,15 +5921,15 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B1:Q31"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="2:17" ht="87.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:17" ht="83.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="13" t="s">
         <v>30</v>
       </c>
@@ -5925,7 +5973,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:17" ht="33" x14ac:dyDescent="0.3">
       <c r="B3" s="14">
         <v>46107</v>
       </c>
@@ -5966,7 +6014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:17" ht="33" x14ac:dyDescent="0.3">
       <c r="B4" s="15">
         <v>46108</v>
       </c>
@@ -6007,7 +6055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B5" s="15">
         <v>46111</v>
       </c>
@@ -6048,7 +6096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:17" ht="33" x14ac:dyDescent="0.3">
       <c r="B6" s="15">
         <v>46112</v>
       </c>
@@ -6089,7 +6137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B7" s="15">
         <v>46113</v>
       </c>
@@ -6130,7 +6178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B8" s="15">
         <v>46114</v>
       </c>
@@ -6171,7 +6219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B9" s="15">
         <v>46115</v>
       </c>
@@ -6212,7 +6260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B10" s="15">
         <v>46118</v>
       </c>
@@ -6253,7 +6301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B11" s="15">
         <v>46119</v>
       </c>
@@ -6294,7 +6342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B12" s="15">
         <v>46120</v>
       </c>
@@ -6335,7 +6383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B13" s="15">
         <v>46121</v>
       </c>
@@ -6376,7 +6424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B14" s="15">
         <v>46122</v>
       </c>
@@ -6417,7 +6465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B15" s="15">
         <v>46125</v>
       </c>
@@ -6458,7 +6506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="15">
         <v>46126</v>
       </c>
@@ -6499,7 +6547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" s="15">
         <v>46127</v>
       </c>
@@ -6522,7 +6570,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B18" s="15">
         <v>46128</v>
       </c>
@@ -6545,7 +6593,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="15">
         <v>46129</v>
       </c>
@@ -6568,7 +6616,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="15">
         <v>46132</v>
       </c>
@@ -6591,7 +6639,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="15">
         <v>46133</v>
       </c>
@@ -6614,7 +6662,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B22" s="15">
         <v>46134</v>
       </c>
@@ -6637,7 +6685,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="15">
         <v>46135</v>
       </c>
@@ -6660,7 +6708,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="15">
         <v>46136</v>
       </c>
@@ -6683,7 +6731,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B25" s="15">
         <v>46139</v>
       </c>
@@ -6706,7 +6754,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B26" s="15">
         <v>46140</v>
       </c>
@@ -6729,7 +6777,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B27" s="15">
         <v>46141</v>
       </c>
@@ -6752,7 +6800,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B28" s="16">
         <v>46142</v>
       </c>
@@ -6775,7 +6823,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="2"/>
       <c r="C29" s="4"/>
       <c r="D29" s="2"/>
@@ -6784,10 +6832,10 @@
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C30" s="3"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C31" s="3"/>
     </row>
   </sheetData>
@@ -6797,15 +6845,15 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="B1:Q31"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="2:17" ht="87.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:17" ht="83.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="13" t="s">
         <v>30</v>
       </c>
@@ -6849,7 +6897,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:17" ht="33" x14ac:dyDescent="0.3">
       <c r="B3" s="14">
         <v>46107</v>
       </c>
@@ -6890,7 +6938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:17" ht="33" x14ac:dyDescent="0.3">
       <c r="B4" s="15">
         <v>46108</v>
       </c>
@@ -6931,7 +6979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B5" s="15">
         <v>46111</v>
       </c>
@@ -6972,7 +7020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:17" ht="33" x14ac:dyDescent="0.3">
       <c r="B6" s="15">
         <v>46112</v>
       </c>
@@ -7013,7 +7061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B7" s="15">
         <v>46113</v>
       </c>
@@ -7054,7 +7102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B8" s="15">
         <v>46114</v>
       </c>
@@ -7095,7 +7143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B9" s="15">
         <v>46115</v>
       </c>
@@ -7136,7 +7184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B10" s="15">
         <v>46118</v>
       </c>
@@ -7177,7 +7225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B11" s="15">
         <v>46119</v>
       </c>
@@ -7218,7 +7266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B12" s="15">
         <v>46120</v>
       </c>
@@ -7259,7 +7307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B13" s="15">
         <v>46121</v>
       </c>
@@ -7300,7 +7348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B14" s="15">
         <v>46122</v>
       </c>
@@ -7341,7 +7389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B15" s="15">
         <v>46125</v>
       </c>
@@ -7382,7 +7430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="15">
         <v>46126</v>
       </c>
@@ -7423,7 +7471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" s="15">
         <v>46127</v>
       </c>
@@ -7446,7 +7494,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B18" s="15">
         <v>46128</v>
       </c>
@@ -7469,7 +7517,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="15">
         <v>46129</v>
       </c>
@@ -7492,7 +7540,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="15">
         <v>46132</v>
       </c>
@@ -7515,7 +7563,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="15">
         <v>46133</v>
       </c>
@@ -7538,7 +7586,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B22" s="15">
         <v>46134</v>
       </c>
@@ -7561,7 +7609,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="15">
         <v>46135</v>
       </c>
@@ -7584,7 +7632,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="15">
         <v>46136</v>
       </c>
@@ -7607,7 +7655,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B25" s="15">
         <v>46139</v>
       </c>
@@ -7630,7 +7678,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B26" s="15">
         <v>46140</v>
       </c>
@@ -7653,7 +7701,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B27" s="15">
         <v>46141</v>
       </c>
@@ -7676,7 +7724,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B28" s="16">
         <v>46142</v>
       </c>
@@ -7699,7 +7747,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="2"/>
       <c r="C29" s="4"/>
       <c r="D29" s="2"/>
@@ -7708,10 +7756,10 @@
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C30" s="3"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C31" s="3"/>
     </row>
   </sheetData>

--- a/daily.xml.xlsx
+++ b/daily.xml.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hyojung2\2026-AI-FULLSTACK-LevelUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3404C01F-571C-45E4-B644-2EBE5472C9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3006F647-0730-4E14-8FA2-B6D2EB68B866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1283" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1284" uniqueCount="54">
   <si>
     <t>출석일수 (Attendance Days)</t>
   </si>
@@ -255,12 +255,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">복습문제
-협업마스터
-</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">복습문제
 협업마스터
@@ -300,6 +294,40 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 최윤정 지각(상담)</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">전원 출석 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-04-010</t>
+  </si>
+  <si>
+    <t>2026-04-210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">복습문제
+협업마스터 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">협업마스터
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF006100"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>욱진, 윤정, 보라, 주협</t>
     </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -440,7 +468,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="37">
+  <borders count="38">
     <border>
       <left/>
       <right/>
@@ -938,6 +966,17 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -953,7 +992,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1138,6 +1177,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1509,7 +1551,7 @@
         <v>5</v>
       </c>
       <c r="K3" s="30">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L3" s="31">
         <v>1</v>
@@ -1518,7 +1560,7 @@
         <v>1</v>
       </c>
       <c r="N3" s="31">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O3" s="32">
         <v>0</v>
@@ -1550,7 +1592,7 @@
         <v>6</v>
       </c>
       <c r="K4" s="30">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L4" s="35">
         <v>1</v>
@@ -1559,7 +1601,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="31">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O4" s="36">
         <v>0</v>
@@ -1591,7 +1633,7 @@
         <v>7</v>
       </c>
       <c r="K5" s="30">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L5" s="35">
         <v>1</v>
@@ -1600,7 +1642,7 @@
         <v>1</v>
       </c>
       <c r="N5" s="31">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O5" s="36">
         <v>0</v>
@@ -1632,7 +1674,7 @@
         <v>8</v>
       </c>
       <c r="K6" s="30">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L6" s="35">
         <v>1</v>
@@ -1641,7 +1683,7 @@
         <v>1</v>
       </c>
       <c r="N6" s="31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O6" s="36">
         <v>0</v>
@@ -1673,7 +1715,7 @@
         <v>9</v>
       </c>
       <c r="K7" s="30">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L7" s="35">
         <v>1</v>
@@ -1682,7 +1724,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O7" s="36">
         <v>0</v>
@@ -1714,7 +1756,7 @@
         <v>10</v>
       </c>
       <c r="K8" s="30">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L8" s="35">
         <v>1</v>
@@ -1723,7 +1765,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O8" s="36">
         <v>0</v>
@@ -1758,7 +1800,7 @@
         <v>11</v>
       </c>
       <c r="K9" s="30">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L9" s="35">
         <v>1</v>
@@ -1767,7 +1809,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O9" s="36">
         <v>0</v>
@@ -1781,7 +1823,7 @@
         <v>27</v>
       </c>
       <c r="D10" s="43" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E10" s="44" t="s">
         <v>23</v>
@@ -1790,7 +1832,7 @@
         <v>23</v>
       </c>
       <c r="G10" s="43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H10" s="45" t="s">
         <v>23</v>
@@ -1799,7 +1841,7 @@
         <v>12</v>
       </c>
       <c r="K10" s="30">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L10" s="35">
         <v>1</v>
@@ -1808,13 +1850,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O10" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:17" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:17" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="55">
         <v>46119</v>
       </c>
@@ -1822,7 +1864,7 @@
         <v>28</v>
       </c>
       <c r="D11" s="43" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>23</v>
@@ -1831,7 +1873,7 @@
         <v>23</v>
       </c>
       <c r="G11" s="42" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>23</v>
@@ -1840,7 +1882,7 @@
         <v>13</v>
       </c>
       <c r="K11" s="30">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L11" s="35">
         <v>1</v>
@@ -1849,21 +1891,21 @@
         <v>1</v>
       </c>
       <c r="N11" s="31">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O11" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:17" ht="29.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="55">
         <v>46120</v>
       </c>
       <c r="C12" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>23</v>
+      <c r="D12" s="43" t="s">
+        <v>49</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>23</v>
@@ -1871,8 +1913,8 @@
       <c r="F12" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G12" s="5" t="s">
-        <v>23</v>
+      <c r="G12" s="42" t="s">
+        <v>53</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>23</v>
@@ -1881,7 +1923,7 @@
         <v>14</v>
       </c>
       <c r="K12" s="30">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L12" s="35">
         <v>1</v>
@@ -1890,15 +1932,15 @@
         <v>1</v>
       </c>
       <c r="N12" s="31">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O12" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="55">
-        <v>46121</v>
+    <row r="13" spans="2:17" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="55" t="s">
+        <v>50</v>
       </c>
       <c r="C13" s="52" t="s">
         <v>25</v>
@@ -1912,9 +1954,6 @@
       <c r="F13" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>23</v>
-      </c>
       <c r="H13" s="6" t="s">
         <v>23</v>
       </c>
@@ -1922,7 +1961,7 @@
         <v>15</v>
       </c>
       <c r="K13" s="30">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L13" s="35">
         <v>1</v>
@@ -1931,7 +1970,7 @@
         <v>1</v>
       </c>
       <c r="N13" s="31">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O13" s="36">
         <v>0</v>
@@ -1939,7 +1978,7 @@
     </row>
     <row r="14" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="55">
-        <v>46122</v>
+        <v>46123</v>
       </c>
       <c r="C14" s="58" t="s">
         <v>26</v>
@@ -1966,7 +2005,7 @@
         <v>16</v>
       </c>
       <c r="K14" s="30">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L14" s="35">
         <v>1</v>
@@ -1975,7 +2014,7 @@
         <v>1</v>
       </c>
       <c r="N14" s="31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O14" s="36">
         <v>0</v>
@@ -2007,7 +2046,7 @@
         <v>17</v>
       </c>
       <c r="K15" s="30">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L15" s="35">
         <v>1</v>
@@ -2016,7 +2055,7 @@
         <v>1</v>
       </c>
       <c r="N15" s="31">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O15" s="36">
         <v>0</v>
@@ -2047,8 +2086,8 @@
       <c r="J16" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="K16" s="30">
-        <v>7</v>
+      <c r="K16" s="62">
+        <v>11</v>
       </c>
       <c r="L16" s="39">
         <v>1</v>
@@ -2057,7 +2096,7 @@
         <v>1</v>
       </c>
       <c r="N16" s="41">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O16" s="40">
         <v>0</v>
@@ -2293,9 +2332,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B27" s="51">
-        <v>46141</v>
+    <row r="27" spans="2:8" ht="33" x14ac:dyDescent="0.3">
+      <c r="B27" s="51" t="s">
+        <v>51</v>
       </c>
       <c r="C27" s="52" t="s">
         <v>29</v>

--- a/daily.xml.xlsx
+++ b/daily.xml.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hyojung2\2026-AI-FULLSTACK-LevelUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAE5C051-85CF-4ACF-9B53-7DF520A315DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DE195CE-18A9-491D-B0D5-3527D66C2B51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28665" yWindow="735" windowWidth="13650" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026. 3~4월" sheetId="1" r:id="rId1"/>
@@ -42,8 +42,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1285" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="60">
   <si>
     <t>출석일수 (Attendance Days)</t>
   </si>
@@ -167,10 +189,6 @@
   <si>
     <t>전원 출석
 - 최윤정 지각</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>7일</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -309,6 +327,9 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
+    <t>13일</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">협업마스터
 </t>
@@ -323,12 +344,41 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>욱진, 윤정, 보라, 주협</t>
+      <t>욱진, 윤정(2), 보라, 주협</t>
     </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>13일</t>
+    <t>복습문제
+협업마스터 
+- 장영탁, 손창기</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>장영탁, 임채연,정수정</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>최윤정</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>7일
+김보라-하혜원</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>김주엽- 최윤정</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>욱진, 윤정(2), 보라, 주협</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>장영탁, 손창기
+정수정, 이일두, 최윤정</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1472,9 +1522,9 @@
     <col min="4" max="4" width="18.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.75" customWidth="1"/>
     <col min="6" max="6" width="14.25" customWidth="1"/>
-    <col min="7" max="7" width="16.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.75" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="47.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1559,7 +1609,7 @@
         <v>1</v>
       </c>
       <c r="N3" s="31">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O3" s="32">
         <v>0</v>
@@ -1600,7 +1650,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="31">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O4" s="36">
         <v>0</v>
@@ -1641,7 +1691,7 @@
         <v>1</v>
       </c>
       <c r="N5" s="31">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O5" s="36">
         <v>0</v>
@@ -1682,7 +1732,7 @@
         <v>1</v>
       </c>
       <c r="N6" s="31">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O6" s="36">
         <v>0</v>
@@ -1705,10 +1755,13 @@
         <v>23</v>
       </c>
       <c r="G7" s="42" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>23</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="J7" s="33" t="s">
         <v>9</v>
@@ -1723,7 +1776,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="31">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O7" s="36">
         <v>0</v>
@@ -1746,10 +1799,13 @@
         <v>23</v>
       </c>
       <c r="G8" s="42" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>23</v>
+      </c>
+      <c r="I8" s="61" t="s">
+        <v>55</v>
       </c>
       <c r="J8" s="33" t="s">
         <v>10</v>
@@ -1764,13 +1820,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="31">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O8" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:17" ht="94.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:17" ht="111" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="60">
         <v>46115</v>
       </c>
@@ -1778,22 +1834,22 @@
         <v>26</v>
       </c>
       <c r="D9" s="43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F9" s="7">
         <v>1</v>
       </c>
       <c r="G9" s="42" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="61" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="J9" s="33" t="s">
         <v>11</v>
@@ -1808,7 +1864,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="31">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O9" s="36">
         <v>0</v>
@@ -1822,7 +1878,7 @@
         <v>27</v>
       </c>
       <c r="D10" s="43" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E10" s="44" t="s">
         <v>23</v>
@@ -1831,10 +1887,13 @@
         <v>23</v>
       </c>
       <c r="G10" s="43" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H10" s="45" t="s">
         <v>23</v>
+      </c>
+      <c r="I10" s="61" t="s">
+        <v>57</v>
       </c>
       <c r="J10" s="33" t="s">
         <v>12</v>
@@ -1849,7 +1908,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="31">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O10" s="36">
         <v>0</v>
@@ -1863,7 +1922,7 @@
         <v>28</v>
       </c>
       <c r="D11" s="43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>23</v>
@@ -1872,7 +1931,7 @@
         <v>23</v>
       </c>
       <c r="G11" s="42" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>23</v>
@@ -1890,13 +1949,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="31">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O11" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:17" ht="29.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:17" ht="41.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="55">
         <v>46120</v>
       </c>
@@ -1904,7 +1963,7 @@
         <v>29</v>
       </c>
       <c r="D12" s="43" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>23</v>
@@ -1918,6 +1977,9 @@
       <c r="H12" s="6" t="s">
         <v>23</v>
       </c>
+      <c r="I12" s="61" t="s">
+        <v>58</v>
+      </c>
       <c r="J12" s="33" t="s">
         <v>14</v>
       </c>
@@ -1931,21 +1993,21 @@
         <v>1</v>
       </c>
       <c r="N12" s="31">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O12" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:17" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:17" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="55" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C13" s="52" t="s">
         <v>25</v>
       </c>
       <c r="D13" s="43" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>23</v>
@@ -1954,10 +2016,13 @@
         <v>23</v>
       </c>
       <c r="G13" s="43" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>23</v>
+      </c>
+      <c r="I13" s="61" t="s">
+        <v>59</v>
       </c>
       <c r="J13" s="33" t="s">
         <v>15</v>
@@ -1972,7 +2037,7 @@
         <v>1</v>
       </c>
       <c r="N13" s="31">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O13" s="36">
         <v>0</v>
@@ -2001,7 +2066,7 @@
         <v>23</v>
       </c>
       <c r="I14" s="61" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J14" s="33" t="s">
         <v>16</v>
@@ -2016,7 +2081,7 @@
         <v>1</v>
       </c>
       <c r="N14" s="31">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O14" s="36">
         <v>0</v>
@@ -2057,7 +2122,7 @@
         <v>1</v>
       </c>
       <c r="N15" s="31">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="O15" s="36">
         <v>0</v>
@@ -2098,13 +2163,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="41">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O16" s="40">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="55">
         <v>46127</v>
       </c>
@@ -2127,7 +2192,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="55">
         <v>46128</v>
       </c>
@@ -2150,7 +2215,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19" s="55">
         <v>46129</v>
       </c>
@@ -2173,7 +2238,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B20" s="55">
         <v>46132</v>
       </c>
@@ -2196,7 +2261,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B21" s="60">
         <v>46133</v>
       </c>
@@ -2218,8 +2283,12 @@
       <c r="H21" s="6" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="P21" t="e" cm="1">
+        <f t="array" ref="P21">+B2A21:P21</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B22" s="60">
         <v>46134</v>
       </c>
@@ -2242,7 +2311,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B23" s="60">
         <v>46135</v>
       </c>
@@ -2265,7 +2334,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="57">
         <v>46136</v>
       </c>
@@ -2288,7 +2357,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B25" s="53">
         <v>46139</v>
       </c>
@@ -2311,7 +2380,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B26" s="51">
         <v>46140</v>
       </c>
@@ -2334,9 +2403,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="33" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:16" ht="33" x14ac:dyDescent="0.3">
       <c r="B27" s="51" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C27" s="52" t="s">
         <v>29</v>
@@ -2357,7 +2426,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B28" s="51">
         <v>46142</v>
       </c>
@@ -2380,7 +2449,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B29" s="2"/>
       <c r="C29" s="4"/>
       <c r="D29" s="2">
@@ -2390,7 +2459,7 @@
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
       <c r="G29" s="42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H29" s="2"/>
     </row>

--- a/daily.xml.xlsx
+++ b/daily.xml.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hyojung2\2026-AI-FULLSTACK-LevelUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DE195CE-18A9-491D-B0D5-3527D66C2B51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15E24753-CACC-4ED5-9CBD-38363A736854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,28 +40,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -327,9 +305,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>13일</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">협업마스터
 </t>
@@ -346,12 +321,6 @@
       </rPr>
       <t>욱진, 윤정(2), 보라, 주협</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>복습문제
-협업마스터 
-- 장영탁, 손창기</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -380,6 +349,40 @@
 정수정, 이일두, 최윤정</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <t>협업마스터</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>현미, 욱진, 수정, 예진</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>현미, 욱진, 수정, 예진</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -388,7 +391,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -492,6 +495,14 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -517,7 +528,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="38">
+  <borders count="37">
     <border>
       <left/>
       <right/>
@@ -1015,17 +1026,6 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1041,7 +1041,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1226,9 +1226,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1600,7 +1597,7 @@
         <v>5</v>
       </c>
       <c r="K3" s="30">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L3" s="31">
         <v>1</v>
@@ -1609,7 +1606,7 @@
         <v>1</v>
       </c>
       <c r="N3" s="31">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O3" s="32">
         <v>0</v>
@@ -1641,7 +1638,7 @@
         <v>6</v>
       </c>
       <c r="K4" s="30">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L4" s="35">
         <v>1</v>
@@ -1650,7 +1647,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="31">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O4" s="36">
         <v>0</v>
@@ -1682,7 +1679,7 @@
         <v>7</v>
       </c>
       <c r="K5" s="30">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L5" s="35">
         <v>1</v>
@@ -1691,7 +1688,7 @@
         <v>1</v>
       </c>
       <c r="N5" s="31">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O5" s="36">
         <v>0</v>
@@ -1723,7 +1720,7 @@
         <v>8</v>
       </c>
       <c r="K6" s="30">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L6" s="35">
         <v>1</v>
@@ -1732,7 +1729,7 @@
         <v>1</v>
       </c>
       <c r="N6" s="31">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O6" s="36">
         <v>0</v>
@@ -1761,13 +1758,13 @@
         <v>23</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J7" s="33" t="s">
         <v>9</v>
       </c>
       <c r="K7" s="30">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L7" s="35">
         <v>1</v>
@@ -1776,7 +1773,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="31">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O7" s="36">
         <v>0</v>
@@ -1805,7 +1802,7 @@
         <v>23</v>
       </c>
       <c r="I8" s="61" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J8" s="33" t="s">
         <v>10</v>
@@ -1820,7 +1817,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="31">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O8" s="36">
         <v>0</v>
@@ -1849,13 +1846,13 @@
         <v>23</v>
       </c>
       <c r="I9" s="61" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J9" s="33" t="s">
         <v>11</v>
       </c>
       <c r="K9" s="30">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L9" s="35">
         <v>1</v>
@@ -1864,7 +1861,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="31">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O9" s="36">
         <v>0</v>
@@ -1893,13 +1890,13 @@
         <v>23</v>
       </c>
       <c r="I10" s="61" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J10" s="33" t="s">
         <v>12</v>
       </c>
       <c r="K10" s="30">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L10" s="35">
         <v>1</v>
@@ -1908,7 +1905,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="31">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O10" s="36">
         <v>0</v>
@@ -1940,7 +1937,7 @@
         <v>13</v>
       </c>
       <c r="K11" s="30">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L11" s="35">
         <v>1</v>
@@ -1949,7 +1946,7 @@
         <v>1</v>
       </c>
       <c r="N11" s="31">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O11" s="36">
         <v>0</v>
@@ -1972,19 +1969,19 @@
         <v>23</v>
       </c>
       <c r="G12" s="42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="61" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="J12" s="33" t="s">
         <v>14</v>
       </c>
       <c r="K12" s="30">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L12" s="35">
         <v>1</v>
@@ -1993,13 +1990,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="31">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O12" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:17" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:17" ht="41.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="55" t="s">
         <v>48</v>
       </c>
@@ -2015,20 +2012,20 @@
       <c r="F13" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G13" s="43" t="s">
-        <v>53</v>
+      <c r="G13" s="42" t="s">
+        <v>51</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>23</v>
       </c>
       <c r="I13" s="61" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J13" s="33" t="s">
         <v>15</v>
       </c>
       <c r="K13" s="30">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L13" s="35">
         <v>1</v>
@@ -2037,21 +2034,21 @@
         <v>1</v>
       </c>
       <c r="N13" s="31">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O13" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:17" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="55">
         <v>46123</v>
       </c>
       <c r="C14" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="7" t="s">
-        <v>23</v>
+      <c r="D14" s="43" t="s">
+        <v>47</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>23</v>
@@ -2059,20 +2056,20 @@
       <c r="F14" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="G14" s="7" t="s">
-        <v>23</v>
+      <c r="G14" s="42" t="s">
+        <v>58</v>
       </c>
       <c r="H14" s="8" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="61" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="J14" s="33" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="30">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L14" s="35">
         <v>1</v>
@@ -2081,7 +2078,7 @@
         <v>1</v>
       </c>
       <c r="N14" s="31">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O14" s="36">
         <v>0</v>
@@ -2113,7 +2110,7 @@
         <v>17</v>
       </c>
       <c r="K15" s="30">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L15" s="35">
         <v>1</v>
@@ -2122,7 +2119,7 @@
         <v>1</v>
       </c>
       <c r="N15" s="31">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O15" s="36">
         <v>0</v>
@@ -2153,8 +2150,8 @@
       <c r="J16" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="K16" s="62">
-        <v>11</v>
+      <c r="K16" s="30">
+        <v>12</v>
       </c>
       <c r="L16" s="39">
         <v>1</v>
@@ -2163,13 +2160,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="41">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O16" s="40">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="55">
         <v>46127</v>
       </c>
@@ -2192,7 +2189,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="55">
         <v>46128</v>
       </c>
@@ -2215,7 +2212,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19" s="55">
         <v>46129</v>
       </c>
@@ -2238,7 +2235,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="55">
         <v>46132</v>
       </c>
@@ -2261,7 +2258,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="60">
         <v>46133</v>
       </c>
@@ -2283,12 +2280,8 @@
       <c r="H21" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="P21" t="e" cm="1">
-        <f t="array" ref="P21">+B2A21:P21</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B22" s="60">
         <v>46134</v>
       </c>
@@ -2311,7 +2304,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="60">
         <v>46135</v>
       </c>
@@ -2334,7 +2327,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="2:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="57">
         <v>46136</v>
       </c>
@@ -2357,7 +2350,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B25" s="53">
         <v>46139</v>
       </c>
@@ -2380,7 +2373,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B26" s="51">
         <v>46140</v>
       </c>
@@ -2403,7 +2396,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="2:16" ht="33" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:8" ht="33" x14ac:dyDescent="0.3">
       <c r="B27" s="51" t="s">
         <v>49</v>
       </c>
@@ -2426,7 +2419,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B28" s="51">
         <v>46142</v>
       </c>
@@ -2449,7 +2442,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="2"/>
       <c r="C29" s="4"/>
       <c r="D29" s="2">

--- a/daily.xml.xlsx
+++ b/daily.xml.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hyojung2\2026-AI-FULLSTACK-LevelUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15E24753-CACC-4ED5-9CBD-38363A736854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD2A84F-F23A-4B46-8328-EF25A2FE430D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28890" yWindow="0" windowWidth="14340" windowHeight="15795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026. 3~4월" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="61">
   <si>
     <t>출석일수 (Attendance Days)</t>
   </si>
@@ -381,6 +381,10 @@
   </si>
   <si>
     <t>현미, 욱진, 수정, 예진</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 복습문제 </t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1597,7 +1601,7 @@
         <v>5</v>
       </c>
       <c r="K3" s="30">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L3" s="31">
         <v>1</v>
@@ -1606,7 +1610,7 @@
         <v>1</v>
       </c>
       <c r="N3" s="31">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O3" s="32">
         <v>0</v>
@@ -1647,7 +1651,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="31">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O4" s="36">
         <v>0</v>
@@ -1688,7 +1692,7 @@
         <v>1</v>
       </c>
       <c r="N5" s="31">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O5" s="36">
         <v>0</v>
@@ -1729,7 +1733,7 @@
         <v>1</v>
       </c>
       <c r="N6" s="31">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O6" s="36">
         <v>0</v>
@@ -1773,7 +1777,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="31">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O7" s="36">
         <v>0</v>
@@ -1817,7 +1821,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="31">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O8" s="36">
         <v>0</v>
@@ -1861,7 +1865,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="31">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O9" s="36">
         <v>0</v>
@@ -1905,7 +1909,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="31">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O10" s="36">
         <v>0</v>
@@ -1946,7 +1950,7 @@
         <v>1</v>
       </c>
       <c r="N11" s="31">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O11" s="36">
         <v>0</v>
@@ -1990,7 +1994,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="31">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O12" s="36">
         <v>0</v>
@@ -2034,7 +2038,7 @@
         <v>1</v>
       </c>
       <c r="N13" s="31">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O13" s="36">
         <v>0</v>
@@ -2078,7 +2082,7 @@
         <v>1</v>
       </c>
       <c r="N14" s="31">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O14" s="36">
         <v>0</v>
@@ -2091,8 +2095,8 @@
       <c r="C15" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="44" t="s">
-        <v>23</v>
+      <c r="D15" s="43" t="s">
+        <v>47</v>
       </c>
       <c r="E15" s="44" t="s">
         <v>23</v>
@@ -2100,8 +2104,8 @@
       <c r="F15" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="G15" s="44" t="s">
-        <v>23</v>
+      <c r="G15" s="42" t="s">
+        <v>60</v>
       </c>
       <c r="H15" s="45" t="s">
         <v>23</v>
@@ -2119,7 +2123,7 @@
         <v>1</v>
       </c>
       <c r="N15" s="31">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O15" s="36">
         <v>0</v>
@@ -2160,7 +2164,7 @@
         <v>1</v>
       </c>
       <c r="N16" s="41">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O16" s="40">
         <v>0</v>

--- a/daily.xml.xlsx
+++ b/daily.xml.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hyojung2\2026-AI-FULLSTACK-LevelUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD2A84F-F23A-4B46-8328-EF25A2FE430D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6BB5336-B2EE-4A5E-8A91-DCE4212CA629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28890" yWindow="0" windowWidth="14340" windowHeight="15795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -384,7 +384,8 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 복습문제 </t>
+    <t xml:space="preserve"> 복습문제 
+협업마스터</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1642,7 +1643,7 @@
         <v>6</v>
       </c>
       <c r="K4" s="30">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L4" s="35">
         <v>1</v>
@@ -1683,7 +1684,7 @@
         <v>7</v>
       </c>
       <c r="K5" s="30">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L5" s="35">
         <v>1</v>
@@ -1724,7 +1725,7 @@
         <v>8</v>
       </c>
       <c r="K6" s="30">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L6" s="35">
         <v>1</v>
@@ -1768,7 +1769,7 @@
         <v>9</v>
       </c>
       <c r="K7" s="30">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L7" s="35">
         <v>1</v>
@@ -1812,7 +1813,7 @@
         <v>10</v>
       </c>
       <c r="K8" s="30">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L8" s="35">
         <v>1</v>
@@ -1856,7 +1857,7 @@
         <v>11</v>
       </c>
       <c r="K9" s="30">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L9" s="35">
         <v>1</v>
@@ -1900,7 +1901,7 @@
         <v>12</v>
       </c>
       <c r="K10" s="30">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L10" s="35">
         <v>1</v>
@@ -1941,7 +1942,7 @@
         <v>13</v>
       </c>
       <c r="K11" s="30">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L11" s="35">
         <v>1</v>
@@ -1985,7 +1986,7 @@
         <v>14</v>
       </c>
       <c r="K12" s="30">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L12" s="35">
         <v>1</v>
@@ -2029,7 +2030,7 @@
         <v>15</v>
       </c>
       <c r="K13" s="30">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L13" s="35">
         <v>1</v>
@@ -2073,7 +2074,7 @@
         <v>16</v>
       </c>
       <c r="K14" s="30">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L14" s="35">
         <v>1</v>
@@ -2088,7 +2089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:17" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="55">
         <v>46125</v>
       </c>
@@ -2114,7 +2115,7 @@
         <v>17</v>
       </c>
       <c r="K15" s="30">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L15" s="35">
         <v>1</v>
@@ -2155,7 +2156,7 @@
         <v>18</v>
       </c>
       <c r="K16" s="30">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L16" s="39">
         <v>1</v>

--- a/daily.xml.xlsx
+++ b/daily.xml.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hyojung2\2026-AI-FULLSTACK-LevelUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6BB5336-B2EE-4A5E-8A91-DCE4212CA629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB280CFA-7823-4FB5-B1BC-62401A2D713B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28890" yWindow="0" windowWidth="14340" windowHeight="15795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026. 3~4월" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1291" uniqueCount="62">
   <si>
     <t>출석일수 (Attendance Days)</t>
   </si>
@@ -385,7 +385,15 @@
   </si>
   <si>
     <t xml:space="preserve"> 복습문제 
-협업마스터</t>
+협업마스터
+채연, 예진</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>채연(transform-질문), 예진(html해결-2관왕), 
+대원 ,다영(정말로 열심히해요! 응원)
+욱진(java-복습)
+장영탁(마스터)</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -533,7 +541,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="37">
+  <borders count="42">
     <border>
       <left/>
       <right/>
@@ -1031,6 +1039,69 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1046,7 +1117,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1231,6 +1302,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1652,7 +1750,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="31">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O4" s="36">
         <v>0</v>
@@ -1778,7 +1876,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="31">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O7" s="36">
         <v>0</v>
@@ -1822,32 +1920,32 @@
         <v>1</v>
       </c>
       <c r="N8" s="31">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O8" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:17" ht="111" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="60">
+      <c r="B9" s="64">
         <v>46115</v>
       </c>
-      <c r="C9" s="58" t="s">
+      <c r="C9" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="43" t="s">
+      <c r="D9" s="66" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="67" t="s">
         <v>38</v>
       </c>
-      <c r="F9" s="7">
-        <v>1</v>
-      </c>
-      <c r="G9" s="42" t="s">
+      <c r="F9" s="67">
+        <v>1</v>
+      </c>
+      <c r="G9" s="68" t="s">
         <v>42</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="69" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="61" t="s">
@@ -1872,7 +1970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:17" ht="45" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:17" ht="44.25" x14ac:dyDescent="0.3">
       <c r="B10" s="55">
         <v>46118</v>
       </c>
@@ -1894,7 +1992,7 @@
       <c r="H10" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="I10" s="61" t="s">
+      <c r="I10" s="63" t="s">
         <v>55</v>
       </c>
       <c r="J10" s="33" t="s">
@@ -1916,14 +2014,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:17" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="55">
+    <row r="11" spans="2:17" ht="33" x14ac:dyDescent="0.3">
+      <c r="B11" s="60">
         <v>46119</v>
       </c>
       <c r="C11" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="43" t="s">
+      <c r="D11" s="42" t="s">
         <v>46</v>
       </c>
       <c r="E11" s="5" t="s">
@@ -1951,20 +2049,20 @@
         <v>1</v>
       </c>
       <c r="N11" s="31">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O11" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:17" ht="41.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="55">
+    <row r="12" spans="2:17" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="B12" s="60">
         <v>46120</v>
       </c>
       <c r="C12" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="43" t="s">
+      <c r="D12" s="42" t="s">
         <v>47</v>
       </c>
       <c r="E12" s="5" t="s">
@@ -1979,7 +2077,7 @@
       <c r="H12" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I12" s="61" t="s">
+      <c r="I12" s="63" t="s">
         <v>56</v>
       </c>
       <c r="J12" s="33" t="s">
@@ -1995,20 +2093,20 @@
         <v>1</v>
       </c>
       <c r="N12" s="31">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O12" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:17" ht="41.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="55" t="s">
+    <row r="13" spans="2:17" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="B13" s="60" t="s">
         <v>48</v>
       </c>
       <c r="C13" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="43" t="s">
+      <c r="D13" s="42" t="s">
         <v>47</v>
       </c>
       <c r="E13" s="5" t="s">
@@ -2023,7 +2121,7 @@
       <c r="H13" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I13" s="61" t="s">
+      <c r="I13" s="63" t="s">
         <v>57</v>
       </c>
       <c r="J13" s="33" t="s">
@@ -2046,28 +2144,28 @@
       </c>
     </row>
     <row r="14" spans="2:17" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="55">
+      <c r="B14" s="64">
         <v>46123</v>
       </c>
-      <c r="C14" s="58" t="s">
+      <c r="C14" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="43" t="s">
+      <c r="D14" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="42" t="s">
+      <c r="E14" s="67" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="67" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="H14" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I14" s="61" t="s">
+      <c r="H14" s="69" t="s">
+        <v>23</v>
+      </c>
+      <c r="I14" s="63" t="s">
         <v>59</v>
       </c>
       <c r="J14" s="33" t="s">
@@ -2083,13 +2181,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="31">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O14" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:17" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:17" ht="66" x14ac:dyDescent="0.3">
       <c r="B15" s="55">
         <v>46125</v>
       </c>
@@ -2105,11 +2203,14 @@
       <c r="F15" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="G15" s="42" t="s">
+      <c r="G15" s="43" t="s">
         <v>60</v>
       </c>
       <c r="H15" s="45" t="s">
         <v>23</v>
+      </c>
+      <c r="I15" s="63" t="s">
+        <v>61</v>
       </c>
       <c r="J15" s="33" t="s">
         <v>17</v>
@@ -2131,7 +2232,7 @@
       </c>
     </row>
     <row r="16" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="55">
+      <c r="B16" s="60">
         <v>46126</v>
       </c>
       <c r="C16" s="52" t="s">
@@ -2155,7 +2256,7 @@
       <c r="J16" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="K16" s="30">
+      <c r="K16" s="62">
         <v>13</v>
       </c>
       <c r="L16" s="39">
@@ -2171,8 +2272,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="55">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B17" s="60">
         <v>46127</v>
       </c>
       <c r="C17" s="52" t="s">
@@ -2194,8 +2295,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="55">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B18" s="60">
         <v>46128</v>
       </c>
       <c r="C18" s="52" t="s">
@@ -2218,7 +2319,7 @@
       </c>
     </row>
     <row r="19" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="55">
+      <c r="B19" s="57">
         <v>46129</v>
       </c>
       <c r="C19" s="58" t="s">
@@ -2241,25 +2342,25 @@
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B20" s="55">
+      <c r="B20" s="70">
         <v>46132</v>
       </c>
-      <c r="C20" s="56" t="s">
+      <c r="C20" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="E20" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="F20" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="G20" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="H20" s="45" t="s">
+      <c r="D20" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="10" t="s">
         <v>23</v>
       </c>
     </row>

--- a/daily.xml.xlsx
+++ b/daily.xml.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hyojung2\2026-AI-FULLSTACK-LevelUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CC38C5F-94C8-43D6-81D9-8CF8287BA302}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AD1B683-9AD8-4595-AFF0-A927A9A44287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="67">
   <si>
     <t>출석일수 (Attendance Days)</t>
   </si>
@@ -402,13 +402,22 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>전원 출석 
-- 이일두님 조퇴예정</t>
+    <t xml:space="preserve">  복습문제 손에 모터단 친구들( 수정, 윤정, 대원)
+</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">  복습문제 손에 모터단 친구들( 수정, 윤정, 대원)
-</t>
+    <t>전원 출석 
+- 이일두님 조퇴예정
+- 하혜원 결석</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">전원 출석  </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 복습문제 </t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -556,7 +565,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="41">
+  <borders count="42">
     <border>
       <left/>
       <right/>
@@ -1106,6 +1115,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1121,7 +1141,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1333,6 +1353,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1704,7 +1727,7 @@
         <v>5</v>
       </c>
       <c r="K3" s="30">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L3" s="31">
         <v>1</v>
@@ -1745,7 +1768,7 @@
         <v>6</v>
       </c>
       <c r="K4" s="30">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L4" s="35">
         <v>1</v>
@@ -1786,7 +1809,7 @@
         <v>7</v>
       </c>
       <c r="K5" s="30">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L5" s="35">
         <v>1</v>
@@ -1827,7 +1850,7 @@
         <v>8</v>
       </c>
       <c r="K6" s="30">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L6" s="35">
         <v>1</v>
@@ -1871,7 +1894,7 @@
         <v>9</v>
       </c>
       <c r="K7" s="30">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L7" s="35">
         <v>1</v>
@@ -1880,7 +1903,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="31">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O7" s="36">
         <v>0</v>
@@ -1915,7 +1938,7 @@
         <v>10</v>
       </c>
       <c r="K8" s="30">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L8" s="35">
         <v>1</v>
@@ -1959,7 +1982,7 @@
         <v>11</v>
       </c>
       <c r="K9" s="30">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L9" s="35">
         <v>1</v>
@@ -2003,7 +2026,7 @@
         <v>12</v>
       </c>
       <c r="K10" s="30">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L10" s="35">
         <v>1</v>
@@ -2044,7 +2067,7 @@
         <v>13</v>
       </c>
       <c r="K11" s="30">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L11" s="35">
         <v>1</v>
@@ -2088,7 +2111,7 @@
         <v>14</v>
       </c>
       <c r="K12" s="30">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L12" s="35">
         <v>1</v>
@@ -2132,7 +2155,7 @@
         <v>15</v>
       </c>
       <c r="K13" s="30">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L13" s="35">
         <v>1</v>
@@ -2141,7 +2164,7 @@
         <v>1</v>
       </c>
       <c r="N13" s="31">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O13" s="36">
         <v>0</v>
@@ -2176,7 +2199,7 @@
         <v>16</v>
       </c>
       <c r="K14" s="30">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L14" s="35">
         <v>1</v>
@@ -2220,7 +2243,7 @@
         <v>17</v>
       </c>
       <c r="K15" s="30">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L15" s="35">
         <v>1</v>
@@ -2229,13 +2252,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="31">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O15" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:17" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:17" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="60">
         <v>46126</v>
       </c>
@@ -2243,7 +2266,7 @@
         <v>28</v>
       </c>
       <c r="D16" s="43" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>23</v>
@@ -2258,13 +2281,13 @@
         <v>23</v>
       </c>
       <c r="I16" s="70" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J16" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="K16" s="30">
-        <v>13</v>
+      <c r="K16" s="71">
+        <v>14</v>
       </c>
       <c r="L16" s="39">
         <v>1</v>
@@ -2286,8 +2309,8 @@
       <c r="C17" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>23</v>
+      <c r="D17" s="43" t="s">
+        <v>65</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>23</v>
@@ -2295,8 +2318,8 @@
       <c r="F17" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G17" s="5" t="s">
-        <v>23</v>
+      <c r="G17" s="42" t="s">
+        <v>66</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>23</v>

--- a/daily.xml.xlsx
+++ b/daily.xml.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hyojung2\2026-AI-FULLSTACK-LevelUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC7DF5B2-B8A9-429E-99CB-3855F522C4B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0355555-7BEC-417B-90D0-A2E5BF86CAA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28725" yWindow="255" windowWidth="15720" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026. 3~4월" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1295" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1295" uniqueCount="70">
   <si>
     <t>출석일수 (Attendance Days)</t>
   </si>
@@ -403,12 +403,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>전원 출석 
-- 이일두님 조퇴예정
-- 하혜원 결석</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">전원 출석  </t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -423,14 +417,37 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 복습문제 
-협업마스터 
-</t>
+    <t>협업마스터 - 김주엽, 최윤정, 손예진, 김욱진, 
+김보라, 이일두</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>협업마스터 - 김주엽, 최윤정, 손예진, 김욱진, 
-김보라, 이일두</t>
+    <r>
+      <t xml:space="preserve">전원 출석 
+- 이일두님 조퇴예정
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- 하혜원 결석</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>손예진 결석</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 복습문제 
+협업마스터 </t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -520,15 +537,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="8" tint="-0.499984740745262"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF006100"/>
       <name val="맑은 고딕"/>
@@ -553,8 +561,17 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFF00"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -569,12 +586,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1332,9 +1343,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1369,6 +1377,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1740,7 +1751,7 @@
         <v>5</v>
       </c>
       <c r="K3" s="30">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L3" s="31">
         <v>1</v>
@@ -1749,7 +1760,7 @@
         <v>1</v>
       </c>
       <c r="N3" s="31">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O3" s="32">
         <v>0</v>
@@ -1762,8 +1773,8 @@
       <c r="C4" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="59" t="s">
-        <v>22</v>
+      <c r="D4" s="71" t="s">
+        <v>68</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>23</v>
@@ -1781,7 +1792,7 @@
         <v>6</v>
       </c>
       <c r="K4" s="30">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L4" s="35">
         <v>1</v>
@@ -1790,7 +1801,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="31">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="O4" s="36">
         <v>0</v>
@@ -1822,7 +1833,7 @@
         <v>7</v>
       </c>
       <c r="K5" s="30">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L5" s="35">
         <v>1</v>
@@ -1831,14 +1842,14 @@
         <v>1</v>
       </c>
       <c r="N5" s="31">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O5" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B6" s="60">
+      <c r="B6" s="59">
         <v>46112</v>
       </c>
       <c r="C6" s="52" t="s">
@@ -1863,7 +1874,7 @@
         <v>8</v>
       </c>
       <c r="K6" s="30">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L6" s="35">
         <v>1</v>
@@ -1872,14 +1883,14 @@
         <v>1</v>
       </c>
       <c r="N6" s="31">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O6" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:17" ht="57.75" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="60">
+      <c r="B7" s="59">
         <v>46113</v>
       </c>
       <c r="C7" s="52" t="s">
@@ -1907,7 +1918,7 @@
         <v>9</v>
       </c>
       <c r="K7" s="30">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L7" s="35">
         <v>1</v>
@@ -1916,14 +1927,14 @@
         <v>1</v>
       </c>
       <c r="N7" s="31">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O7" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:17" ht="45" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="60">
+      <c r="B8" s="59">
         <v>46114</v>
       </c>
       <c r="C8" s="52" t="s">
@@ -1944,14 +1955,14 @@
       <c r="H8" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I8" s="61" t="s">
+      <c r="I8" s="60" t="s">
         <v>52</v>
       </c>
       <c r="J8" s="33" t="s">
         <v>10</v>
       </c>
       <c r="K8" s="30">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L8" s="35">
         <v>1</v>
@@ -1960,20 +1971,20 @@
         <v>1</v>
       </c>
       <c r="N8" s="31">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O8" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:17" ht="111" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="63">
+      <c r="B9" s="62">
         <v>46115</v>
       </c>
-      <c r="C9" s="64" t="s">
+      <c r="C9" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="65" t="s">
+      <c r="D9" s="64" t="s">
         <v>38</v>
       </c>
       <c r="E9" s="5" t="s">
@@ -1982,20 +1993,20 @@
       <c r="F9" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G9" s="67" t="s">
+      <c r="G9" s="66" t="s">
         <v>41</v>
       </c>
-      <c r="H9" s="68" t="s">
-        <v>23</v>
-      </c>
-      <c r="I9" s="61" t="s">
+      <c r="H9" s="67" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" s="60" t="s">
         <v>53</v>
       </c>
       <c r="J9" s="33" t="s">
         <v>11</v>
       </c>
       <c r="K9" s="30">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L9" s="35">
         <v>1</v>
@@ -2004,7 +2015,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="31">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O9" s="36">
         <v>0</v>
@@ -2032,14 +2043,14 @@
       <c r="H10" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="I10" s="62" t="s">
+      <c r="I10" s="61" t="s">
         <v>54</v>
       </c>
       <c r="J10" s="33" t="s">
         <v>12</v>
       </c>
       <c r="K10" s="30">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L10" s="35">
         <v>1</v>
@@ -2048,14 +2059,14 @@
         <v>1</v>
       </c>
       <c r="N10" s="31">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O10" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="2:17" ht="33" x14ac:dyDescent="0.3">
-      <c r="B11" s="60">
+      <c r="B11" s="59">
         <v>46119</v>
       </c>
       <c r="C11" s="52" t="s">
@@ -2080,7 +2091,7 @@
         <v>13</v>
       </c>
       <c r="K11" s="30">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L11" s="35">
         <v>1</v>
@@ -2089,14 +2100,14 @@
         <v>1</v>
       </c>
       <c r="N11" s="31">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O11" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:17" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="B12" s="60">
+      <c r="B12" s="59">
         <v>46120</v>
       </c>
       <c r="C12" s="52" t="s">
@@ -2117,14 +2128,14 @@
       <c r="H12" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I12" s="62" t="s">
+      <c r="I12" s="61" t="s">
         <v>55</v>
       </c>
       <c r="J12" s="33" t="s">
         <v>14</v>
       </c>
       <c r="K12" s="30">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L12" s="35">
         <v>1</v>
@@ -2133,14 +2144,14 @@
         <v>1</v>
       </c>
       <c r="N12" s="31">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O12" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="2:17" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="B13" s="60" t="s">
+      <c r="B13" s="59" t="s">
         <v>47</v>
       </c>
       <c r="C13" s="52" t="s">
@@ -2161,14 +2172,14 @@
       <c r="H13" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I13" s="62" t="s">
+      <c r="I13" s="61" t="s">
         <v>56</v>
       </c>
       <c r="J13" s="33" t="s">
         <v>15</v>
       </c>
       <c r="K13" s="30">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L13" s="35">
         <v>1</v>
@@ -2177,42 +2188,42 @@
         <v>1</v>
       </c>
       <c r="N13" s="31">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="O13" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:17" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="63">
+      <c r="B14" s="62">
         <v>46123</v>
       </c>
-      <c r="C14" s="64" t="s">
+      <c r="C14" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="67" t="s">
+      <c r="D14" s="66" t="s">
         <v>46</v>
       </c>
-      <c r="E14" s="66" t="s">
-        <v>23</v>
-      </c>
-      <c r="F14" s="66" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="67" t="s">
+      <c r="E14" s="65" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="65" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="66" t="s">
         <v>57</v>
       </c>
-      <c r="H14" s="68" t="s">
-        <v>23</v>
-      </c>
-      <c r="I14" s="62" t="s">
+      <c r="H14" s="67" t="s">
+        <v>23</v>
+      </c>
+      <c r="I14" s="61" t="s">
         <v>58</v>
       </c>
       <c r="J14" s="33" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="30">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L14" s="35">
         <v>1</v>
@@ -2221,7 +2232,7 @@
         <v>1</v>
       </c>
       <c r="N14" s="31">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O14" s="36">
         <v>0</v>
@@ -2249,14 +2260,14 @@
       <c r="H15" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="I15" s="62" t="s">
+      <c r="I15" s="61" t="s">
         <v>60</v>
       </c>
       <c r="J15" s="33" t="s">
         <v>17</v>
       </c>
       <c r="K15" s="30">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L15" s="35">
         <v>1</v>
@@ -2265,21 +2276,21 @@
         <v>1</v>
       </c>
       <c r="N15" s="31">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="O15" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="2:17" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="60">
+      <c r="B16" s="59">
         <v>46126</v>
       </c>
       <c r="C16" s="52" t="s">
         <v>28</v>
       </c>
       <c r="D16" s="43" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>23</v>
@@ -2293,14 +2304,14 @@
       <c r="H16" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I16" s="70" t="s">
+      <c r="I16" s="69" t="s">
         <v>62</v>
       </c>
       <c r="J16" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="K16" s="71">
-        <v>15</v>
+      <c r="K16" s="70">
+        <v>18</v>
       </c>
       <c r="L16" s="39">
         <v>1</v>
@@ -2309,47 +2320,47 @@
         <v>1</v>
       </c>
       <c r="N16" s="41">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O16" s="40">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="60">
+      <c r="B17" s="59">
         <v>46127</v>
       </c>
       <c r="C17" s="52" t="s">
         <v>29</v>
       </c>
       <c r="D17" s="43" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I17" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="E17" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G17" s="42" t="s">
-        <v>66</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I17" s="70" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="B18" s="60">
+    </row>
+    <row r="18" spans="2:9" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="59">
         <v>46128</v>
       </c>
       <c r="C18" s="52" t="s">
         <v>25</v>
       </c>
       <c r="D18" s="43" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>23</v>
@@ -2358,13 +2369,13 @@
         <v>23</v>
       </c>
       <c r="G18" s="42" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I18" s="62" t="s">
-        <v>68</v>
+      <c r="I18" s="61" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -2374,8 +2385,8 @@
       <c r="C19" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="7" t="s">
-        <v>23</v>
+      <c r="D19" s="43" t="s">
+        <v>63</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>23</v>
@@ -2383,22 +2394,22 @@
       <c r="F19" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="G19" s="7" t="s">
-        <v>23</v>
+      <c r="G19" s="42" t="s">
+        <v>69</v>
       </c>
       <c r="H19" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B20" s="69">
+    <row r="20" spans="2:9" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="68">
         <v>46132</v>
       </c>
       <c r="C20" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="9" t="s">
-        <v>23</v>
+      <c r="D20" s="43" t="s">
+        <v>63</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>23</v>
@@ -2406,22 +2417,22 @@
       <c r="F20" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="G20" s="9" t="s">
-        <v>23</v>
+      <c r="G20" s="42" t="s">
+        <v>69</v>
       </c>
       <c r="H20" s="10" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B21" s="60">
+      <c r="B21" s="59">
         <v>46133</v>
       </c>
       <c r="C21" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="D21" s="5" t="s">
-        <v>23</v>
+      <c r="D21" s="43" t="s">
+        <v>63</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>23</v>
@@ -2437,7 +2448,7 @@
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B22" s="60">
+      <c r="B22" s="59">
         <v>46134</v>
       </c>
       <c r="C22" s="52" t="s">
@@ -2460,7 +2471,7 @@
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B23" s="60">
+      <c r="B23" s="59">
         <v>46135</v>
       </c>
       <c r="C23" s="52" t="s">

--- a/daily.xml.xlsx
+++ b/daily.xml.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hyojung2\2026-AI-FULLSTACK-LevelUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0355555-7BEC-417B-90D0-A2E5BF86CAA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E8B0E70-1973-421D-BD7B-724FA34A886E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28725" yWindow="255" windowWidth="15720" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026. 3~4월" sheetId="1" r:id="rId1"/>
@@ -2424,7 +2424,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:9" ht="33" x14ac:dyDescent="0.3">
       <c r="B21" s="59">
         <v>46133</v>
       </c>
@@ -2440,8 +2440,8 @@
       <c r="F21" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G21" s="5" t="s">
-        <v>23</v>
+      <c r="G21" s="42" t="s">
+        <v>69</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>23</v>

--- a/daily.xml.xlsx
+++ b/daily.xml.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hyojung2\2026-AI-FULLSTACK-LevelUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E8B0E70-1973-421D-BD7B-724FA34A886E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FD95D01-8C67-40B8-B9BB-414D54F87406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1295" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1296" uniqueCount="71">
   <si>
     <t>출석일수 (Attendance Days)</t>
   </si>
@@ -448,6 +448,10 @@
   <si>
     <t xml:space="preserve"> 복습문제 
 협업마스터 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>수정, 채연, 다영, 예진</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1971,7 +1975,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="31">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O8" s="36">
         <v>0</v>
@@ -2100,7 +2104,7 @@
         <v>1</v>
       </c>
       <c r="N11" s="31">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O11" s="36">
         <v>0</v>
@@ -2188,7 +2192,7 @@
         <v>1</v>
       </c>
       <c r="N13" s="31">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O13" s="36">
         <v>0</v>
@@ -2232,7 +2236,7 @@
         <v>1</v>
       </c>
       <c r="N14" s="31">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O14" s="36">
         <v>0</v>
@@ -2445,6 +2449,9 @@
       </c>
       <c r="H21" s="6" t="s">
         <v>23</v>
+      </c>
+      <c r="I21" s="61" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.3">

--- a/daily.xml.xlsx
+++ b/daily.xml.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hyojung2\2026-AI-FULLSTACK-LevelUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FD95D01-8C67-40B8-B9BB-414D54F87406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B55B0CBE-62C1-4109-8CCB-9FEC8F2C0D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1755,7 +1755,7 @@
         <v>5</v>
       </c>
       <c r="K3" s="30">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L3" s="31">
         <v>1</v>
@@ -1764,7 +1764,7 @@
         <v>1</v>
       </c>
       <c r="N3" s="31">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O3" s="32">
         <v>0</v>
@@ -1796,7 +1796,7 @@
         <v>6</v>
       </c>
       <c r="K4" s="30">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L4" s="35">
         <v>1</v>
@@ -1805,7 +1805,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="31">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O4" s="36">
         <v>0</v>
@@ -1837,7 +1837,7 @@
         <v>7</v>
       </c>
       <c r="K5" s="30">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L5" s="35">
         <v>1</v>
@@ -1846,7 +1846,7 @@
         <v>1</v>
       </c>
       <c r="N5" s="31">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O5" s="36">
         <v>0</v>
@@ -1878,7 +1878,7 @@
         <v>8</v>
       </c>
       <c r="K6" s="30">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L6" s="35">
         <v>1</v>
@@ -1887,7 +1887,7 @@
         <v>1</v>
       </c>
       <c r="N6" s="31">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O6" s="36">
         <v>0</v>
@@ -1922,7 +1922,7 @@
         <v>9</v>
       </c>
       <c r="K7" s="30">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L7" s="35">
         <v>1</v>
@@ -1931,7 +1931,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="31">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O7" s="36">
         <v>0</v>
@@ -1966,7 +1966,7 @@
         <v>10</v>
       </c>
       <c r="K8" s="30">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L8" s="35">
         <v>1</v>
@@ -1975,7 +1975,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="31">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O8" s="36">
         <v>0</v>
@@ -2010,7 +2010,7 @@
         <v>11</v>
       </c>
       <c r="K9" s="30">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L9" s="35">
         <v>1</v>
@@ -2019,7 +2019,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="31">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O9" s="36">
         <v>0</v>
@@ -2054,7 +2054,7 @@
         <v>12</v>
       </c>
       <c r="K10" s="30">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L10" s="35">
         <v>1</v>
@@ -2063,7 +2063,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="31">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O10" s="36">
         <v>0</v>
@@ -2095,7 +2095,7 @@
         <v>13</v>
       </c>
       <c r="K11" s="30">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L11" s="35">
         <v>1</v>
@@ -2104,7 +2104,7 @@
         <v>1</v>
       </c>
       <c r="N11" s="31">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O11" s="36">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>14</v>
       </c>
       <c r="K12" s="30">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L12" s="35">
         <v>1</v>
@@ -2148,7 +2148,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="31">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O12" s="36">
         <v>0</v>
@@ -2183,7 +2183,7 @@
         <v>15</v>
       </c>
       <c r="K13" s="30">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L13" s="35">
         <v>1</v>
@@ -2192,7 +2192,7 @@
         <v>1</v>
       </c>
       <c r="N13" s="31">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O13" s="36">
         <v>0</v>
@@ -2227,7 +2227,7 @@
         <v>16</v>
       </c>
       <c r="K14" s="30">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L14" s="35">
         <v>1</v>
@@ -2236,7 +2236,7 @@
         <v>1</v>
       </c>
       <c r="N14" s="31">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O14" s="36">
         <v>0</v>
@@ -2271,7 +2271,7 @@
         <v>17</v>
       </c>
       <c r="K15" s="30">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L15" s="35">
         <v>1</v>
@@ -2280,7 +2280,7 @@
         <v>1</v>
       </c>
       <c r="N15" s="31">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O15" s="36">
         <v>0</v>
@@ -2315,7 +2315,7 @@
         <v>18</v>
       </c>
       <c r="K16" s="70">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L16" s="39">
         <v>1</v>
@@ -2324,7 +2324,7 @@
         <v>1</v>
       </c>
       <c r="N16" s="41">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O16" s="40">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="2:9" ht="33" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:9" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="59">
         <v>46133</v>
       </c>
@@ -2461,8 +2461,8 @@
       <c r="C22" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="D22" s="5" t="s">
-        <v>23</v>
+      <c r="D22" s="43" t="s">
+        <v>63</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>23</v>

--- a/daily.xml.xlsx
+++ b/daily.xml.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hyojung2\2026-AI-FULLSTACK-LevelUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDBBDB0F-82FC-4498-ADF0-72C791FC4180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EF62C96-C40A-4FE3-9237-D3780BEB5A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,28 +40,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1700,7 +1678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:Q30"/>
+  <dimension ref="B1:Q29"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
@@ -2361,7 +2339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:16" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:9" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="59">
         <v>46127</v>
       </c>
@@ -2386,12 +2364,8 @@
       <c r="I17" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="P17" cm="1">
-        <f t="array" ref="P17:P30">N3:N16+1</f>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="2:16" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="2:9" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="59">
         <v>46128</v>
       </c>
@@ -2416,11 +2390,8 @@
       <c r="I18" s="61" t="s">
         <v>66</v>
       </c>
-      <c r="P18">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="19" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="19" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19" s="57">
         <v>46129</v>
       </c>
@@ -2442,11 +2413,8 @@
       <c r="H19" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="P19">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="20" spans="2:16" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="20" spans="2:9" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="68">
         <v>46132</v>
       </c>
@@ -2468,11 +2436,8 @@
       <c r="H20" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="P20">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="2:16" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="21" spans="2:9" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="59">
         <v>46133</v>
       </c>
@@ -2497,11 +2462,8 @@
       <c r="I21" s="61" t="s">
         <v>70</v>
       </c>
-      <c r="P21">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="22" spans="2:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="22" spans="2:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="59">
         <v>46134</v>
       </c>
@@ -2523,11 +2485,8 @@
       <c r="H22" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="P22">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="2:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="23" spans="2:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="59">
         <v>46135</v>
       </c>
@@ -2549,11 +2508,8 @@
       <c r="H23" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="P23">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="24" spans="2:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="24" spans="2:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="57">
         <v>46136</v>
       </c>
@@ -2575,11 +2531,8 @@
       <c r="H24" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="P24">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="25" spans="2:16" ht="33" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="2:9" ht="33" x14ac:dyDescent="0.3">
       <c r="B25" s="53">
         <v>46139</v>
       </c>
@@ -2601,11 +2554,8 @@
       <c r="H25" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="P25">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26" s="51">
         <v>46140</v>
       </c>
@@ -2627,11 +2577,8 @@
       <c r="H26" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="P26">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="27" spans="2:16" ht="33" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="2:9" ht="33" x14ac:dyDescent="0.3">
       <c r="B27" s="51" t="s">
         <v>48</v>
       </c>
@@ -2653,11 +2600,8 @@
       <c r="H27" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="P27">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B28" s="51">
         <v>46142</v>
       </c>
@@ -2679,11 +2623,8 @@
       <c r="H28" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="P28">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B29" s="2"/>
       <c r="C29" s="4"/>
       <c r="D29" s="2">
@@ -2696,14 +2637,6 @@
         <v>39</v>
       </c>
       <c r="H29" s="2"/>
-      <c r="P29">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="P30">
-        <v>26</v>
-      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>

--- a/daily.xml.xlsx
+++ b/daily.xml.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hyojung2\2026-AI-FULLSTACK-LevelUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EF62C96-C40A-4FE3-9237-D3780BEB5A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A35167AE-602F-4BEC-8681-7559D0746AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026. 3~4월" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1296" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="75">
   <si>
     <t>출석일수 (Attendance Days)</t>
   </si>
@@ -463,6 +463,14 @@
 -  장영탁 결석</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
+  <si>
+    <t>협업마스터 - 다영, 수정, 창기, 현미, 윤정(2)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 협업마스터- 현미, 창기, 윤정</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -602,7 +610,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="42">
+  <borders count="43">
     <border>
       <left/>
       <right/>
@@ -1163,6 +1171,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1178,7 +1197,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1393,6 +1412,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1764,7 +1786,7 @@
         <v>5</v>
       </c>
       <c r="K3" s="30">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L3" s="31">
         <v>1</v>
@@ -1773,7 +1795,7 @@
         <v>1</v>
       </c>
       <c r="N3" s="31">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O3" s="32">
         <v>0</v>
@@ -1805,7 +1827,7 @@
         <v>6</v>
       </c>
       <c r="K4" s="30">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L4" s="35">
         <v>1</v>
@@ -1814,7 +1836,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="31">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O4" s="36">
         <v>0</v>
@@ -1846,7 +1868,7 @@
         <v>7</v>
       </c>
       <c r="K5" s="30">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L5" s="35">
         <v>1</v>
@@ -1855,7 +1877,7 @@
         <v>1</v>
       </c>
       <c r="N5" s="31">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O5" s="36">
         <v>0</v>
@@ -1887,7 +1909,7 @@
         <v>8</v>
       </c>
       <c r="K6" s="30">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L6" s="35">
         <v>1</v>
@@ -1896,7 +1918,7 @@
         <v>1</v>
       </c>
       <c r="N6" s="31">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="O6" s="36">
         <v>0</v>
@@ -1931,7 +1953,7 @@
         <v>9</v>
       </c>
       <c r="K7" s="30">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L7" s="35">
         <v>1</v>
@@ -1940,7 +1962,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="31">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O7" s="36">
         <v>0</v>
@@ -1975,7 +1997,7 @@
         <v>10</v>
       </c>
       <c r="K8" s="30">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L8" s="35">
         <v>1</v>
@@ -1984,7 +2006,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="31">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O8" s="36">
         <v>0</v>
@@ -2019,7 +2041,7 @@
         <v>11</v>
       </c>
       <c r="K9" s="30">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L9" s="35">
         <v>1</v>
@@ -2028,7 +2050,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="31">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="O9" s="36">
         <v>0</v>
@@ -2063,7 +2085,7 @@
         <v>12</v>
       </c>
       <c r="K10" s="30">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L10" s="35">
         <v>1</v>
@@ -2072,7 +2094,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="31">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O10" s="36">
         <v>0</v>
@@ -2104,7 +2126,7 @@
         <v>13</v>
       </c>
       <c r="K11" s="30">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L11" s="35">
         <v>1</v>
@@ -2113,7 +2135,7 @@
         <v>1</v>
       </c>
       <c r="N11" s="31">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O11" s="36">
         <v>0</v>
@@ -2157,7 +2179,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="31">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O12" s="36">
         <v>0</v>
@@ -2192,7 +2214,7 @@
         <v>15</v>
       </c>
       <c r="K13" s="30">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L13" s="35">
         <v>1</v>
@@ -2201,7 +2223,7 @@
         <v>1</v>
       </c>
       <c r="N13" s="31">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O13" s="36">
         <v>0</v>
@@ -2236,7 +2258,7 @@
         <v>16</v>
       </c>
       <c r="K14" s="30">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L14" s="35">
         <v>1</v>
@@ -2245,7 +2267,7 @@
         <v>1</v>
       </c>
       <c r="N14" s="31">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="O14" s="36">
         <v>0</v>
@@ -2280,7 +2302,7 @@
         <v>17</v>
       </c>
       <c r="K15" s="30">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L15" s="35">
         <v>1</v>
@@ -2289,7 +2311,7 @@
         <v>1</v>
       </c>
       <c r="N15" s="31">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="O15" s="36">
         <v>0</v>
@@ -2324,7 +2346,7 @@
         <v>18</v>
       </c>
       <c r="K16" s="70">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L16" s="39">
         <v>1</v>
@@ -2333,7 +2355,7 @@
         <v>1</v>
       </c>
       <c r="N16" s="41">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O16" s="40">
         <v>0</v>
@@ -2548,22 +2570,25 @@
       <c r="F25" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="G25" s="9" t="s">
-        <v>23</v>
+      <c r="G25" s="42" t="s">
+        <v>71</v>
       </c>
       <c r="H25" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I25" s="72" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" ht="33" x14ac:dyDescent="0.3">
       <c r="B26" s="51">
         <v>46140</v>
       </c>
       <c r="C26" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="D26" s="5" t="s">
-        <v>23</v>
+      <c r="D26" s="42" t="s">
+        <v>72</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>23</v>
@@ -2571,11 +2596,14 @@
       <c r="F26" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G26" s="5" t="s">
-        <v>23</v>
+      <c r="G26" s="42" t="s">
+        <v>71</v>
       </c>
       <c r="H26" s="5" t="s">
         <v>23</v>
+      </c>
+      <c r="I26" s="72" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="33" x14ac:dyDescent="0.3">

--- a/daily.xml.xlsx
+++ b/daily.xml.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hyojung2\2026-AI-FULLSTACK-LevelUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A35167AE-602F-4BEC-8681-7559D0746AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA7E32F9-B335-4741-A08D-3A4B93368D6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026. 3~4월" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1299" uniqueCount="76">
   <si>
     <t>출석일수 (Attendance Days)</t>
   </si>
@@ -469,6 +469,11 @@
   </si>
   <si>
     <t xml:space="preserve"> 협업마스터- 현미, 창기, 윤정</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">복습문제 -2점
+</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1786,7 +1791,7 @@
         <v>5</v>
       </c>
       <c r="K3" s="30">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L3" s="31">
         <v>1</v>
@@ -1795,7 +1800,7 @@
         <v>1</v>
       </c>
       <c r="N3" s="31">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="O3" s="32">
         <v>0</v>
@@ -1827,7 +1832,7 @@
         <v>6</v>
       </c>
       <c r="K4" s="30">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L4" s="35">
         <v>1</v>
@@ -1836,7 +1841,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="31">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O4" s="36">
         <v>0</v>
@@ -1868,7 +1873,7 @@
         <v>7</v>
       </c>
       <c r="K5" s="30">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L5" s="35">
         <v>1</v>
@@ -1877,7 +1882,7 @@
         <v>1</v>
       </c>
       <c r="N5" s="31">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="O5" s="36">
         <v>0</v>
@@ -1909,7 +1914,7 @@
         <v>8</v>
       </c>
       <c r="K6" s="30">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L6" s="35">
         <v>1</v>
@@ -1918,7 +1923,7 @@
         <v>1</v>
       </c>
       <c r="N6" s="31">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="O6" s="36">
         <v>0</v>
@@ -1953,7 +1958,7 @@
         <v>9</v>
       </c>
       <c r="K7" s="30">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L7" s="35">
         <v>1</v>
@@ -1962,7 +1967,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="31">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="O7" s="36">
         <v>0</v>
@@ -1997,7 +2002,7 @@
         <v>10</v>
       </c>
       <c r="K8" s="30">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L8" s="35">
         <v>1</v>
@@ -2006,7 +2011,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="31">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="O8" s="36">
         <v>0</v>
@@ -2041,7 +2046,7 @@
         <v>11</v>
       </c>
       <c r="K9" s="30">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L9" s="35">
         <v>1</v>
@@ -2050,7 +2055,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="31">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="O9" s="36">
         <v>0</v>
@@ -2085,7 +2090,7 @@
         <v>12</v>
       </c>
       <c r="K10" s="30">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L10" s="35">
         <v>1</v>
@@ -2094,7 +2099,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="31">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="O10" s="36">
         <v>0</v>
@@ -2126,7 +2131,7 @@
         <v>13</v>
       </c>
       <c r="K11" s="30">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L11" s="35">
         <v>1</v>
@@ -2135,7 +2140,7 @@
         <v>1</v>
       </c>
       <c r="N11" s="31">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="O11" s="36">
         <v>0</v>
@@ -2179,7 +2184,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="31">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="O12" s="36">
         <v>0</v>
@@ -2214,7 +2219,7 @@
         <v>15</v>
       </c>
       <c r="K13" s="30">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L13" s="35">
         <v>1</v>
@@ -2223,7 +2228,7 @@
         <v>1</v>
       </c>
       <c r="N13" s="31">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="O13" s="36">
         <v>0</v>
@@ -2258,7 +2263,7 @@
         <v>16</v>
       </c>
       <c r="K14" s="30">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L14" s="35">
         <v>1</v>
@@ -2267,7 +2272,7 @@
         <v>1</v>
       </c>
       <c r="N14" s="31">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O14" s="36">
         <v>0</v>
@@ -2302,7 +2307,7 @@
         <v>17</v>
       </c>
       <c r="K15" s="30">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L15" s="35">
         <v>1</v>
@@ -2311,7 +2316,7 @@
         <v>1</v>
       </c>
       <c r="N15" s="31">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O15" s="36">
         <v>0</v>
@@ -2346,7 +2351,7 @@
         <v>18</v>
       </c>
       <c r="K16" s="70">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L16" s="39">
         <v>1</v>
@@ -2355,7 +2360,7 @@
         <v>1</v>
       </c>
       <c r="N16" s="41">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O16" s="40">
         <v>0</v>
@@ -2613,8 +2618,8 @@
       <c r="C27" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="D27" s="5" t="s">
-        <v>23</v>
+      <c r="D27" s="42" t="s">
+        <v>72</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>23</v>
@@ -2622,11 +2627,14 @@
       <c r="F27" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G27" s="5" t="s">
-        <v>23</v>
+      <c r="G27" s="42" t="s">
+        <v>71</v>
       </c>
       <c r="H27" s="5" t="s">
         <v>23</v>
+      </c>
+      <c r="I27" s="72" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.3">

--- a/daily.xml.xlsx
+++ b/daily.xml.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hyojung2\2026-AI-FULLSTACK-LevelUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA7E32F9-B335-4741-A08D-3A4B93368D6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFAC7661-6010-4D7E-9CEB-3EA37655D5EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -473,7 +473,8 @@
   </si>
   <si>
     <t xml:space="preserve">복습문제 -2점
-</t>
+협업마스터 -  손예진(2), 김주엽(2), 
+보라, 혜원, 수정, 욱진 </t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1715,7 +1716,7 @@
     <col min="6" max="6" width="14.25" customWidth="1"/>
     <col min="7" max="7" width="15.75" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="47.375" customWidth="1"/>
+    <col min="9" max="9" width="48.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1800,7 +1801,7 @@
         <v>1</v>
       </c>
       <c r="N3" s="31">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O3" s="32">
         <v>0</v>
@@ -1841,7 +1842,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="31">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O4" s="36">
         <v>0</v>
@@ -1882,7 +1883,7 @@
         <v>1</v>
       </c>
       <c r="N5" s="31">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O5" s="36">
         <v>0</v>
@@ -2011,7 +2012,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="31">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O8" s="36">
         <v>0</v>
@@ -2228,7 +2229,7 @@
         <v>1</v>
       </c>
       <c r="N13" s="31">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O13" s="36">
         <v>0</v>
@@ -2360,7 +2361,7 @@
         <v>1</v>
       </c>
       <c r="N16" s="41">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O16" s="40">
         <v>0</v>
@@ -2611,7 +2612,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="27" spans="2:9" ht="33" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:9" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B27" s="51" t="s">
         <v>48</v>
       </c>

--- a/daily.xml.xlsx
+++ b/daily.xml.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hyojung2\2026-AI-FULLSTACK-LevelUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFAC7661-6010-4D7E-9CEB-3EA37655D5EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58BC0ADB-0F53-42AB-AA93-00AE12A849A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026. 3~4월" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1299" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1254" uniqueCount="80">
   <si>
     <t>출석일수 (Attendance Days)</t>
   </si>
@@ -477,6 +477,29 @@
 보라, 혜원, 수정, 욱진 </t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
+  <si>
+    <t>전원 출석
+-  장영탁 조퇴</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>하혜원</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>욱진, 다영</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>수정
+보라
+예진1
+채연
+욱진
+혜원2
+윤정6</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -485,7 +508,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -597,8 +620,17 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="2"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -615,8 +647,14 @@
         <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="43">
+  <borders count="48">
     <border>
       <left/>
       <right/>
@@ -1188,6 +1226,69 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1203,7 +1304,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1414,13 +1515,61 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1792,7 +1941,7 @@
         <v>5</v>
       </c>
       <c r="K3" s="30">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L3" s="31">
         <v>1</v>
@@ -1801,7 +1950,7 @@
         <v>1</v>
       </c>
       <c r="N3" s="31">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O3" s="32">
         <v>0</v>
@@ -1814,7 +1963,7 @@
       <c r="C4" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="71" t="s">
+      <c r="D4" s="70" t="s">
         <v>68</v>
       </c>
       <c r="E4" s="7" t="s">
@@ -1833,7 +1982,7 @@
         <v>6</v>
       </c>
       <c r="K4" s="30">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L4" s="35">
         <v>1</v>
@@ -1842,7 +1991,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="31">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O4" s="36">
         <v>0</v>
@@ -1874,7 +2023,7 @@
         <v>7</v>
       </c>
       <c r="K5" s="30">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L5" s="35">
         <v>1</v>
@@ -1915,7 +2064,7 @@
         <v>8</v>
       </c>
       <c r="K6" s="30">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L6" s="35">
         <v>1</v>
@@ -1959,7 +2108,7 @@
         <v>9</v>
       </c>
       <c r="K7" s="30">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L7" s="35">
         <v>1</v>
@@ -2003,7 +2152,7 @@
         <v>10</v>
       </c>
       <c r="K8" s="30">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L8" s="35">
         <v>1</v>
@@ -2012,7 +2161,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="31">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O8" s="36">
         <v>0</v>
@@ -2047,7 +2196,7 @@
         <v>11</v>
       </c>
       <c r="K9" s="30">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L9" s="35">
         <v>1</v>
@@ -2091,7 +2240,7 @@
         <v>12</v>
       </c>
       <c r="K10" s="30">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L10" s="35">
         <v>1</v>
@@ -2132,7 +2281,7 @@
         <v>13</v>
       </c>
       <c r="K11" s="30">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L11" s="35">
         <v>1</v>
@@ -2141,7 +2290,7 @@
         <v>1</v>
       </c>
       <c r="N11" s="31">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O11" s="36">
         <v>0</v>
@@ -2176,7 +2325,7 @@
         <v>14</v>
       </c>
       <c r="K12" s="30">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L12" s="35">
         <v>1</v>
@@ -2220,7 +2369,7 @@
         <v>15</v>
       </c>
       <c r="K13" s="30">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L13" s="35">
         <v>1</v>
@@ -2229,7 +2378,7 @@
         <v>1</v>
       </c>
       <c r="N13" s="31">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O13" s="36">
         <v>0</v>
@@ -2264,7 +2413,7 @@
         <v>16</v>
       </c>
       <c r="K14" s="30">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L14" s="35">
         <v>1</v>
@@ -2308,7 +2457,7 @@
         <v>17</v>
       </c>
       <c r="K15" s="30">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L15" s="35">
         <v>1</v>
@@ -2317,7 +2466,7 @@
         <v>1</v>
       </c>
       <c r="N15" s="31">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O15" s="36">
         <v>0</v>
@@ -2349,10 +2498,10 @@
         <v>62</v>
       </c>
       <c r="J16" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="K16" s="70">
-        <v>24</v>
+        <v>77</v>
+      </c>
+      <c r="K16" s="30">
+        <v>26</v>
       </c>
       <c r="L16" s="39">
         <v>1</v>
@@ -2361,7 +2510,7 @@
         <v>1</v>
       </c>
       <c r="N16" s="41">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O16" s="40">
         <v>0</v>
@@ -2582,7 +2731,7 @@
       <c r="H25" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="I25" s="72" t="s">
+      <c r="I25" s="71" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2608,7 +2757,7 @@
       <c r="H26" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="I26" s="72" t="s">
+      <c r="I26" s="71" t="s">
         <v>74</v>
       </c>
     </row>
@@ -2634,19 +2783,19 @@
       <c r="H27" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="I27" s="72" t="s">
+      <c r="I27" s="71" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:9" ht="132" x14ac:dyDescent="0.3">
       <c r="B28" s="51">
         <v>46142</v>
       </c>
       <c r="C28" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="D28" s="5" t="s">
-        <v>23</v>
+      <c r="D28" s="42" t="s">
+        <v>76</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>23</v>
@@ -2654,11 +2803,14 @@
       <c r="F28" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G28" s="5" t="s">
-        <v>23</v>
+      <c r="G28" s="42" t="s">
+        <v>71</v>
       </c>
       <c r="H28" s="5" t="s">
         <v>23</v>
+      </c>
+      <c r="I28" s="72" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.3">
@@ -2689,6 +2841,7 @@
   <cols>
     <col min="2" max="2" width="10.625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.875" customWidth="1"/>
+    <col min="9" max="9" width="16.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2739,46 +2892,59 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="2:17" ht="33" x14ac:dyDescent="0.3">
-      <c r="B3" s="14">
-        <v>46107</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" s="18" t="s">
+    <row r="3" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="73">
+        <v>46148</v>
+      </c>
+      <c r="C3" s="74" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="9">
-        <v>1</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>23</v>
+      <c r="E3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="61" t="s">
+        <v>78</v>
       </c>
       <c r="J3" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="30"/>
-      <c r="L3" s="31"/>
-      <c r="M3" s="31"/>
-      <c r="N3" s="31"/>
-      <c r="O3" s="32"/>
-    </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B4" s="15">
-        <v>46108</v>
+      <c r="K3" s="30">
+        <v>27</v>
+      </c>
+      <c r="L3" s="31">
+        <v>1</v>
+      </c>
+      <c r="M3" s="31">
+        <v>1</v>
+      </c>
+      <c r="N3" s="31">
+        <v>34</v>
+      </c>
+      <c r="O3" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="14">
+        <v>46149</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>22</v>
+        <v>25</v>
+      </c>
+      <c r="D4" s="75" t="s">
+        <v>21</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>23</v>
@@ -2795,83 +2961,113 @@
       <c r="J4" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="K4" s="34"/>
-      <c r="L4" s="35"/>
-      <c r="M4" s="35"/>
-      <c r="N4" s="35"/>
-      <c r="O4" s="36"/>
-    </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B5" s="15">
-        <v>46111</v>
-      </c>
-      <c r="C5" s="23" t="s">
+      <c r="K4" s="30">
         <v>27</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="L4" s="35">
+        <v>1</v>
+      </c>
+      <c r="M4" s="35">
+        <v>1</v>
+      </c>
+      <c r="N4" s="31">
+        <v>36</v>
+      </c>
+      <c r="O4" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="76">
+        <v>46150</v>
+      </c>
+      <c r="C5" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="6" t="s">
+      <c r="E5" s="65" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="65" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="65" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="67" t="s">
         <v>23</v>
       </c>
       <c r="J5" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="34"/>
-      <c r="L5" s="35"/>
-      <c r="M5" s="35"/>
-      <c r="N5" s="35"/>
-      <c r="O5" s="36"/>
-    </row>
-    <row r="6" spans="2:17" ht="33" x14ac:dyDescent="0.3">
-      <c r="B6" s="15">
-        <v>46112</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="20" t="s">
+      <c r="K5" s="30">
+        <v>27</v>
+      </c>
+      <c r="L5" s="35">
+        <v>1</v>
+      </c>
+      <c r="M5" s="35">
+        <v>1</v>
+      </c>
+      <c r="N5" s="31">
+        <v>33</v>
+      </c>
+      <c r="O5" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="79">
+        <v>46153</v>
+      </c>
+      <c r="C6" s="74" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H6" s="6" t="s">
+      <c r="E6" s="80" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="80" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="80" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="81" t="s">
         <v>23</v>
       </c>
       <c r="J6" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="K6" s="34"/>
-      <c r="L6" s="35"/>
-      <c r="M6" s="35"/>
-      <c r="N6" s="35"/>
-      <c r="O6" s="36"/>
-    </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B7" s="15">
-        <v>46113</v>
+      <c r="K6" s="30">
+        <v>27</v>
+      </c>
+      <c r="L6" s="35">
+        <v>1</v>
+      </c>
+      <c r="M6" s="35">
+        <v>1</v>
+      </c>
+      <c r="N6" s="31">
+        <v>31</v>
+      </c>
+      <c r="O6" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="79">
+        <v>46154</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>23</v>
+        <v>28</v>
+      </c>
+      <c r="D7" s="75" t="s">
+        <v>21</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>23</v>
@@ -2888,21 +3084,31 @@
       <c r="J7" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="34"/>
-      <c r="L7" s="35"/>
-      <c r="M7" s="35"/>
-      <c r="N7" s="35"/>
-      <c r="O7" s="36"/>
-    </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B8" s="15">
-        <v>46114</v>
+      <c r="K7" s="30">
+        <v>27</v>
+      </c>
+      <c r="L7" s="35">
+        <v>1</v>
+      </c>
+      <c r="M7" s="35">
+        <v>1</v>
+      </c>
+      <c r="N7" s="31">
+        <v>30</v>
+      </c>
+      <c r="O7" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="79">
+        <v>46155</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>23</v>
+        <v>29</v>
+      </c>
+      <c r="D8" s="75" t="s">
+        <v>21</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>23</v>
@@ -2919,21 +3125,31 @@
       <c r="J8" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="K8" s="34"/>
-      <c r="L8" s="35"/>
-      <c r="M8" s="35"/>
-      <c r="N8" s="35"/>
-      <c r="O8" s="36"/>
-    </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B9" s="15">
-        <v>46115</v>
+      <c r="K8" s="30">
+        <v>26</v>
+      </c>
+      <c r="L8" s="35">
+        <v>1</v>
+      </c>
+      <c r="M8" s="35">
+        <v>1</v>
+      </c>
+      <c r="N8" s="31">
+        <v>35</v>
+      </c>
+      <c r="O8" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="79">
+        <v>46156</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="D9" s="75" t="s">
+        <v>21</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>23</v>
@@ -2950,83 +3166,113 @@
       <c r="J9" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="K9" s="34"/>
-      <c r="L9" s="35"/>
-      <c r="M9" s="35"/>
-      <c r="N9" s="35"/>
-      <c r="O9" s="36"/>
-    </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B10" s="15">
-        <v>46118</v>
-      </c>
-      <c r="C10" s="23" t="s">
+      <c r="K9" s="30">
         <v>27</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" s="6" t="s">
+      <c r="L9" s="35">
+        <v>1</v>
+      </c>
+      <c r="M9" s="35">
+        <v>1</v>
+      </c>
+      <c r="N9" s="31">
+        <v>30</v>
+      </c>
+      <c r="O9" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="79">
+        <v>46157</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="82" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="8" t="s">
         <v>23</v>
       </c>
       <c r="J10" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="K10" s="34"/>
-      <c r="L10" s="35"/>
-      <c r="M10" s="35"/>
-      <c r="N10" s="35"/>
-      <c r="O10" s="36"/>
-    </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B11" s="15">
-        <v>46119</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H11" s="6" t="s">
+      <c r="K10" s="30">
+        <v>27</v>
+      </c>
+      <c r="L10" s="35">
+        <v>1</v>
+      </c>
+      <c r="M10" s="35">
+        <v>1</v>
+      </c>
+      <c r="N10" s="31">
+        <v>30</v>
+      </c>
+      <c r="O10" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="79">
+        <v>46160</v>
+      </c>
+      <c r="C11" s="74" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="75" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="45" t="s">
         <v>23</v>
       </c>
       <c r="J11" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="K11" s="34"/>
-      <c r="L11" s="35"/>
-      <c r="M11" s="35"/>
-      <c r="N11" s="35"/>
-      <c r="O11" s="36"/>
-    </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B12" s="15">
-        <v>46120</v>
+      <c r="K11" s="30">
+        <v>27</v>
+      </c>
+      <c r="L11" s="35">
+        <v>1</v>
+      </c>
+      <c r="M11" s="35">
+        <v>1</v>
+      </c>
+      <c r="N11" s="31">
+        <v>32</v>
+      </c>
+      <c r="O11" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="79">
+        <v>46161</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>23</v>
+        <v>28</v>
+      </c>
+      <c r="D12" s="75" t="s">
+        <v>21</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>23</v>
@@ -3043,21 +3289,31 @@
       <c r="J12" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="K12" s="34"/>
-      <c r="L12" s="35"/>
-      <c r="M12" s="35"/>
-      <c r="N12" s="35"/>
-      <c r="O12" s="36"/>
-    </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B13" s="15">
-        <v>46121</v>
+      <c r="K12" s="30">
+        <v>24</v>
+      </c>
+      <c r="L12" s="35">
+        <v>1</v>
+      </c>
+      <c r="M12" s="35">
+        <v>1</v>
+      </c>
+      <c r="N12" s="31">
+        <v>31</v>
+      </c>
+      <c r="O12" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="79">
+        <v>46162</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>23</v>
+        <v>29</v>
+      </c>
+      <c r="D13" s="75" t="s">
+        <v>21</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>23</v>
@@ -3074,21 +3330,31 @@
       <c r="J13" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="K13" s="34"/>
-      <c r="L13" s="35"/>
-      <c r="M13" s="35"/>
-      <c r="N13" s="35"/>
-      <c r="O13" s="36"/>
-    </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B14" s="15">
-        <v>46122</v>
+      <c r="K13" s="30">
+        <v>27</v>
+      </c>
+      <c r="L13" s="35">
+        <v>1</v>
+      </c>
+      <c r="M13" s="35">
+        <v>1</v>
+      </c>
+      <c r="N13" s="31">
+        <v>37</v>
+      </c>
+      <c r="O13" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="79">
+        <v>46163</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>21</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>23</v>
@@ -3105,152 +3371,182 @@
       <c r="J14" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="K14" s="34"/>
-      <c r="L14" s="35"/>
-      <c r="M14" s="35"/>
-      <c r="N14" s="35"/>
-      <c r="O14" s="36"/>
-    </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B15" s="15">
-        <v>46125</v>
-      </c>
-      <c r="C15" s="23" t="s">
+      <c r="K14" s="30">
         <v>27</v>
       </c>
-      <c r="D15" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H15" s="6" t="s">
+      <c r="L14" s="35">
+        <v>1</v>
+      </c>
+      <c r="M14" s="35">
+        <v>1</v>
+      </c>
+      <c r="N14" s="31">
+        <v>34</v>
+      </c>
+      <c r="O14" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="79">
+        <v>46164</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="83" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" s="8" t="s">
         <v>23</v>
       </c>
       <c r="J15" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="K15" s="34"/>
-      <c r="L15" s="35"/>
-      <c r="M15" s="35"/>
-      <c r="N15" s="35"/>
-      <c r="O15" s="36"/>
+      <c r="K15" s="30">
+        <v>27</v>
+      </c>
+      <c r="L15" s="35">
+        <v>1</v>
+      </c>
+      <c r="M15" s="35">
+        <v>1</v>
+      </c>
+      <c r="N15" s="31">
+        <v>41</v>
+      </c>
+      <c r="O15" s="36">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="15">
-        <v>46126</v>
-      </c>
-      <c r="C16" s="23" t="s">
+      <c r="B16" s="84">
+        <v>46167</v>
+      </c>
+      <c r="C16" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="86" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" s="87" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" s="87" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="87" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="88" t="s">
+        <v>23</v>
+      </c>
+      <c r="J16" s="37" t="s">
+        <v>77</v>
+      </c>
+      <c r="K16" s="30">
+        <v>26</v>
+      </c>
+      <c r="L16" s="39">
+        <v>1</v>
+      </c>
+      <c r="M16" s="39">
+        <v>1</v>
+      </c>
+      <c r="N16" s="41">
+        <v>30</v>
+      </c>
+      <c r="O16" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="79">
+        <v>46168</v>
+      </c>
+      <c r="C17" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J16" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="K16" s="38"/>
-      <c r="L16" s="39"/>
-      <c r="M16" s="39"/>
-      <c r="N16" s="39"/>
-      <c r="O16" s="40"/>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B17" s="15">
-        <v>46127</v>
-      </c>
-      <c r="C17" s="23" t="s">
+      <c r="D17" s="75" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="79">
+        <v>46169</v>
+      </c>
+      <c r="C18" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B18" s="15">
-        <v>46128</v>
-      </c>
-      <c r="C18" s="23" t="s">
+      <c r="D18" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="79">
+        <v>46170</v>
+      </c>
+      <c r="C19" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="D18" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B19" s="15">
-        <v>46129</v>
-      </c>
-      <c r="C19" s="23" t="s">
+      <c r="D19" s="75" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="79">
+        <v>46171</v>
+      </c>
+      <c r="C20" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B20" s="15">
-        <v>46132</v>
-      </c>
-      <c r="C20" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>23</v>
+      <c r="D20" s="75" t="s">
+        <v>21</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>23</v>
@@ -3266,188 +3562,76 @@
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B21" s="15">
-        <v>46133</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B22" s="15">
-        <v>46134</v>
-      </c>
-      <c r="C22" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B23" s="15">
-        <v>46135</v>
-      </c>
-      <c r="C23" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B24" s="15">
-        <v>46136</v>
-      </c>
-      <c r="C24" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>23</v>
-      </c>
+      <c r="B21" s="15"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="75"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="6"/>
+    </row>
+    <row r="22" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="15"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="6"/>
+    </row>
+    <row r="23" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="15"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="75"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="6"/>
+    </row>
+    <row r="24" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="15"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="75"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="6"/>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B25" s="15">
-        <v>46139</v>
-      </c>
-      <c r="C25" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B26" s="15">
-        <v>46140</v>
-      </c>
-      <c r="C26" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B27" s="15">
-        <v>46141</v>
-      </c>
-      <c r="C27" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>23</v>
-      </c>
+      <c r="B25" s="15"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="75"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="6"/>
+    </row>
+    <row r="26" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B26" s="15"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="6"/>
+    </row>
+    <row r="27" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B27" s="15"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="75"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="6"/>
     </row>
     <row r="28" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="16">
-        <v>46142</v>
-      </c>
-      <c r="C28" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>23</v>
-      </c>
+      <c r="B28" s="16"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="75"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="8"/>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="2"/>
@@ -3467,6 +3651,7 @@
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/daily.xml.xlsx
+++ b/daily.xml.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hyojung2\2026-AI-FULLSTACK-LevelUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0678BEE-4CC9-41ED-8B8F-0BB59E47B180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E83DF8D5-5EC4-403B-ABE2-5437AA71ABE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026. 3~4월" sheetId="1" r:id="rId1"/>

--- a/daily.xml.xlsx
+++ b/daily.xml.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hyojung2\2026-AI-FULLSTACK-LevelUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E83DF8D5-5EC4-403B-ABE2-5437AA71ABE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C193ECC3-210B-4D5B-8488-40EDD84E2571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026. 3~4월" sheetId="1" r:id="rId1"/>
     <sheet name="2026.5" sheetId="2" r:id="rId2"/>
-    <sheet name="2026.6" sheetId="3" r:id="rId3"/>
-    <sheet name="2026.7" sheetId="4" r:id="rId4"/>
-    <sheet name="2026.8" sheetId="5" r:id="rId5"/>
-    <sheet name="2026.9" sheetId="6" r:id="rId6"/>
-    <sheet name="2026.10" sheetId="7" r:id="rId7"/>
+    <sheet name="Sheet1" sheetId="8" r:id="rId3"/>
+    <sheet name="2026.6" sheetId="3" r:id="rId4"/>
+    <sheet name="2026.7" sheetId="4" r:id="rId5"/>
+    <sheet name="2026.8" sheetId="5" r:id="rId6"/>
+    <sheet name="2026.9" sheetId="6" r:id="rId7"/>
+    <sheet name="2026.10" sheetId="7" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1255" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1282" uniqueCount="109">
   <si>
     <t>출석일수 (Attendance Days)</t>
   </si>
@@ -512,6 +513,255 @@
 대원,   보라, 예진,윤정</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
+  <si>
+    <t xml:space="preserve">  {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "attendanceDays": 28,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "assignmentsCompleted": 1,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "totalAssignments": 1,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "contributions": 37,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "presentations": 0,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "blogsWritten": 6,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "tutorialsShared": 2,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "bugsFixed": 7,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "studySessions": 3,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "ideasProposed": 4,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "likesReceived": 55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  }</t>
+  </si>
+  <si>
+    <t>📌 필드별 의미</t>
+  </si>
+  <si>
+    <r>
+      <t>name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 학생 이름</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>attendanceDays</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 출석한 일수 (예: 28일 출석)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assignmentsCompleted</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 제출한 과제 수 (예: 1개 제출)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>totalAssignments</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 전체 과제 수 (예: 총 1개 과제 있음)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>contributions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 코드 기여 횟수 (예: 37회)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>presentations</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 발표 횟수 (예: 0회 발표)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>blogsWritten</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 작성한 학습 블로그 글 수 (예: 6개 → 블로그왕 조건 충족)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>tutorialsShared</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 공유한 튜토리얼/가이드 수 (예: 2개 → 튜토리얼 제작자 조건 충족)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>bugsFixed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 다른 학습자의 코드 버그 해결 횟수 (예: 7회 → 디버깅 마스터 조건 충족)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>studySessions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 스터디 그룹 운영 횟수 (예: 3회 → 스터디 리더 조건 충족)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ideasProposed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 새로운 프로젝트 아이디어 제안 횟수 (예: 4회 → 아이디어 메이커 조건 충족)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>likesReceived</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 커뮤니티 내 좋아요/응원 받은 횟수 (예: 55회 → 커뮤니티 스타 조건 충족)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    "name": "홍길동</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>",</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -520,7 +770,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -641,6 +891,36 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1316,7 +1596,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1589,6 +1869,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1874,7 +2169,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:Q29"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.75" style="3" customWidth="1"/>
@@ -1886,10 +2181,10 @@
     <col min="9" max="9" width="48.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:17" ht="17.25" thickBot="1">
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="2:17" ht="49.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:17" ht="49.15" customHeight="1" thickBot="1">
       <c r="B2" s="46" t="s">
         <v>30</v>
       </c>
@@ -1933,7 +2228,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:17">
       <c r="B3" s="55">
         <v>46107</v>
       </c>
@@ -1974,7 +2269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:17" ht="17.25" thickBot="1">
       <c r="B4" s="57">
         <v>46108</v>
       </c>
@@ -2015,7 +2310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:17">
       <c r="B5" s="55">
         <v>46111</v>
       </c>
@@ -2056,7 +2351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:17">
       <c r="B6" s="59">
         <v>46112</v>
       </c>
@@ -2097,7 +2392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:17" ht="57.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:17" ht="57.75" thickBot="1">
       <c r="B7" s="59">
         <v>46113</v>
       </c>
@@ -2141,7 +2436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:17" ht="45" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:17" ht="45" thickBot="1">
       <c r="B8" s="59">
         <v>46114</v>
       </c>
@@ -2185,7 +2480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:17" ht="111" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:17" ht="111" thickBot="1">
       <c r="B9" s="62">
         <v>46115</v>
       </c>
@@ -2229,7 +2524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:17" ht="44.25" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:17" ht="44.25">
       <c r="B10" s="55">
         <v>46118</v>
       </c>
@@ -2273,7 +2568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:17" ht="33">
       <c r="B11" s="59">
         <v>46119</v>
       </c>
@@ -2314,7 +2609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:17" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:17" ht="40.5">
       <c r="B12" s="59">
         <v>46120</v>
       </c>
@@ -2358,7 +2653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:17" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:17" ht="40.5">
       <c r="B13" s="59" t="s">
         <v>47</v>
       </c>
@@ -2402,7 +2697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:17" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:17" ht="50.25" thickBot="1">
       <c r="B14" s="62">
         <v>46123</v>
       </c>
@@ -2446,7 +2741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:17" ht="66.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:17" ht="66.75" thickBot="1">
       <c r="B15" s="55">
         <v>46125</v>
       </c>
@@ -2490,7 +2785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:17" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:17" ht="50.25" thickBot="1">
       <c r="B16" s="59">
         <v>46126</v>
       </c>
@@ -2534,7 +2829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:9" ht="50.25" thickBot="1">
       <c r="B17" s="59">
         <v>46127</v>
       </c>
@@ -2560,7 +2855,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="2:9" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:9" ht="33.75" thickBot="1">
       <c r="B18" s="59">
         <v>46128</v>
       </c>
@@ -2586,7 +2881,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="19" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:9" ht="15" customHeight="1" thickBot="1">
       <c r="B19" s="57">
         <v>46129</v>
       </c>
@@ -2609,7 +2904,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="2:9" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:9" ht="33.75" thickBot="1">
       <c r="B20" s="68">
         <v>46132</v>
       </c>
@@ -2632,7 +2927,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="2:9" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:9" ht="33.75" thickBot="1">
       <c r="B21" s="59">
         <v>46133</v>
       </c>
@@ -2658,7 +2953,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="2:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:9" ht="17.25" thickBot="1">
       <c r="B22" s="59">
         <v>46134</v>
       </c>
@@ -2681,7 +2976,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:9" ht="17.25" thickBot="1">
       <c r="B23" s="59">
         <v>46135</v>
       </c>
@@ -2704,7 +2999,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="2:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:9" ht="17.25" thickBot="1">
       <c r="B24" s="57">
         <v>46136</v>
       </c>
@@ -2727,7 +3022,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="2:9" ht="33" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:9" ht="33">
       <c r="B25" s="53">
         <v>46139</v>
       </c>
@@ -2753,7 +3048,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="26" spans="2:9" ht="33" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:9" ht="33">
       <c r="B26" s="51">
         <v>46140</v>
       </c>
@@ -2779,7 +3074,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="27" spans="2:9" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:9" ht="49.5">
       <c r="B27" s="51" t="s">
         <v>48</v>
       </c>
@@ -2805,7 +3100,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="28" spans="2:9" ht="132" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:9" ht="132">
       <c r="B28" s="51">
         <v>46142</v>
       </c>
@@ -2831,7 +3126,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:9">
       <c r="B29" s="2"/>
       <c r="C29" s="4"/>
       <c r="D29" s="2">
@@ -2855,18 +3150,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:Q31"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="10.625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.875" customWidth="1"/>
     <col min="9" max="9" width="17.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:17" ht="17.25" thickBot="1">
       <c r="B1" s="1"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="2:17" ht="83.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:17" ht="83.25" thickBot="1">
       <c r="B2" s="13" t="s">
         <v>30</v>
       </c>
@@ -2910,7 +3205,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:17" ht="17.25" thickBot="1">
       <c r="B3" s="73">
         <v>46148</v>
       </c>
@@ -2954,7 +3249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:17" ht="99.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:17" ht="99.75" thickBot="1">
       <c r="B4" s="14">
         <v>46149</v>
       </c>
@@ -2998,7 +3293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:17" ht="17.25" thickBot="1">
       <c r="B5" s="76">
         <v>46150</v>
       </c>
@@ -3039,7 +3334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:17" ht="17.25" thickBot="1">
       <c r="B6" s="78">
         <v>46153</v>
       </c>
@@ -3080,7 +3375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:17" ht="17.25" thickBot="1">
       <c r="B7" s="78">
         <v>46154</v>
       </c>
@@ -3121,7 +3416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:17" ht="17.25" thickBot="1">
       <c r="B8" s="78">
         <v>46155</v>
       </c>
@@ -3162,7 +3457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:17" ht="17.25" thickBot="1">
       <c r="B9" s="78">
         <v>46156</v>
       </c>
@@ -3203,7 +3498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:17" ht="17.25" thickBot="1">
       <c r="B10" s="78">
         <v>46157</v>
       </c>
@@ -3244,7 +3539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:17" ht="17.25" thickBot="1">
       <c r="B11" s="78">
         <v>46160</v>
       </c>
@@ -3285,7 +3580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:17" ht="17.25" thickBot="1">
       <c r="B12" s="78">
         <v>46161</v>
       </c>
@@ -3326,7 +3621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:17" ht="17.25" thickBot="1">
       <c r="B13" s="78">
         <v>46162</v>
       </c>
@@ -3367,7 +3662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:17" ht="17.25" thickBot="1">
       <c r="B14" s="78">
         <v>46163</v>
       </c>
@@ -3408,7 +3703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:17" ht="17.25" thickBot="1">
       <c r="B15" s="78">
         <v>46164</v>
       </c>
@@ -3449,7 +3744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:17" ht="17.25" thickBot="1">
       <c r="B16" s="81">
         <v>46167</v>
       </c>
@@ -3490,7 +3785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:8" ht="17.25" thickBot="1">
       <c r="B17" s="78">
         <v>46168</v>
       </c>
@@ -3513,7 +3808,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:8" ht="17.25" thickBot="1">
       <c r="B18" s="78">
         <v>46169</v>
       </c>
@@ -3536,7 +3831,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:8" ht="17.25" thickBot="1">
       <c r="B19" s="78">
         <v>46170</v>
       </c>
@@ -3559,7 +3854,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:8" ht="17.25" thickBot="1">
       <c r="B20" s="78">
         <v>46171</v>
       </c>
@@ -3582,7 +3877,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:8">
       <c r="B21" s="15"/>
       <c r="C21" s="23"/>
       <c r="D21" s="75"/>
@@ -3591,7 +3886,7 @@
       <c r="G21" s="5"/>
       <c r="H21" s="6"/>
     </row>
-    <row r="22" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:8" ht="17.25" thickBot="1">
       <c r="B22" s="15"/>
       <c r="C22" s="23"/>
       <c r="D22" s="18"/>
@@ -3600,7 +3895,7 @@
       <c r="G22" s="5"/>
       <c r="H22" s="6"/>
     </row>
-    <row r="23" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:8" ht="17.25" thickBot="1">
       <c r="B23" s="15"/>
       <c r="C23" s="23"/>
       <c r="D23" s="75"/>
@@ -3609,7 +3904,7 @@
       <c r="G23" s="5"/>
       <c r="H23" s="6"/>
     </row>
-    <row r="24" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:8" ht="17.25" thickBot="1">
       <c r="B24" s="15"/>
       <c r="C24" s="23"/>
       <c r="D24" s="75"/>
@@ -3618,7 +3913,7 @@
       <c r="G24" s="5"/>
       <c r="H24" s="6"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:8">
       <c r="B25" s="15"/>
       <c r="C25" s="23"/>
       <c r="D25" s="75"/>
@@ -3627,7 +3922,7 @@
       <c r="G25" s="5"/>
       <c r="H25" s="6"/>
     </row>
-    <row r="26" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:8" ht="17.25" thickBot="1">
       <c r="B26" s="15"/>
       <c r="C26" s="23"/>
       <c r="D26" s="18"/>
@@ -3636,7 +3931,7 @@
       <c r="G26" s="5"/>
       <c r="H26" s="6"/>
     </row>
-    <row r="27" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:8" ht="17.25" thickBot="1">
       <c r="B27" s="15"/>
       <c r="C27" s="23"/>
       <c r="D27" s="75"/>
@@ -3645,7 +3940,7 @@
       <c r="G27" s="5"/>
       <c r="H27" s="6"/>
     </row>
-    <row r="28" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:8" ht="17.25" thickBot="1">
       <c r="B28" s="16"/>
       <c r="C28" s="24"/>
       <c r="D28" s="75"/>
@@ -3654,7 +3949,7 @@
       <c r="G28" s="7"/>
       <c r="H28" s="8"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:8">
       <c r="B29" s="2"/>
       <c r="C29" s="4"/>
       <c r="D29" s="2"/>
@@ -3663,10 +3958,10 @@
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:8">
       <c r="C30" s="3"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:8">
       <c r="C31" s="3"/>
     </row>
   </sheetData>
@@ -3677,15 +3972,158 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5311FA83-4A96-4545-9E60-5FB40A21CCD1}">
+  <dimension ref="A2:E27"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetData>
+    <row r="2" spans="1:5" ht="26.25">
+      <c r="E2" s="92" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="91" t="s">
+        <v>82</v>
+      </c>
+      <c r="E3" s="93"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="91" t="s">
+        <v>108</v>
+      </c>
+      <c r="E4" s="94" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="91" t="s">
+        <v>83</v>
+      </c>
+      <c r="E5" s="94" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="91" t="s">
+        <v>84</v>
+      </c>
+      <c r="E6" s="94" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="91" t="s">
+        <v>85</v>
+      </c>
+      <c r="E7" s="94" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="91" t="s">
+        <v>86</v>
+      </c>
+      <c r="E8" s="94" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="91" t="s">
+        <v>87</v>
+      </c>
+      <c r="E9" s="94" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="91" t="s">
+        <v>88</v>
+      </c>
+      <c r="E10" s="94" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="91" t="s">
+        <v>89</v>
+      </c>
+      <c r="E11" s="94" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="91" t="s">
+        <v>90</v>
+      </c>
+      <c r="E12" s="94" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="91" t="s">
+        <v>91</v>
+      </c>
+      <c r="E13" s="94" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="91" t="s">
+        <v>92</v>
+      </c>
+      <c r="E14" s="94" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="91" t="s">
+        <v>93</v>
+      </c>
+      <c r="E15" s="94" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="21.75">
+      <c r="A16" s="91" t="s">
+        <v>94</v>
+      </c>
+      <c r="E16" s="95"/>
+    </row>
+    <row r="17" spans="5:5">
+      <c r="E17" s="93"/>
+    </row>
+    <row r="19" spans="5:5">
+      <c r="E19" s="93"/>
+    </row>
+    <row r="21" spans="5:5">
+      <c r="E21" s="93"/>
+    </row>
+    <row r="23" spans="5:5">
+      <c r="E23" s="93"/>
+    </row>
+    <row r="25" spans="5:5">
+      <c r="E25" s="93"/>
+    </row>
+    <row r="27" spans="5:5">
+      <c r="E27" s="93"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:Q31"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData>
-    <row r="1" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:17" ht="17.25" thickBot="1">
       <c r="B1" s="1"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="2:17" ht="83.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:17" ht="83.25" thickBot="1">
       <c r="B2" s="13" t="s">
         <v>30</v>
       </c>
@@ -3729,7 +4167,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="2:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:17" ht="33">
       <c r="B3" s="14">
         <v>46107</v>
       </c>
@@ -3770,7 +4208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:17" ht="33">
       <c r="B4" s="15">
         <v>46108</v>
       </c>
@@ -3811,7 +4249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:17">
       <c r="B5" s="15">
         <v>46111</v>
       </c>
@@ -3852,7 +4290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:17" ht="33">
       <c r="B6" s="15">
         <v>46112</v>
       </c>
@@ -3893,7 +4331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:17">
       <c r="B7" s="15">
         <v>46113</v>
       </c>
@@ -3934,7 +4372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:17">
       <c r="B8" s="15">
         <v>46114</v>
       </c>
@@ -3975,7 +4413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:17">
       <c r="B9" s="15">
         <v>46115</v>
       </c>
@@ -4016,7 +4454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:17">
       <c r="B10" s="15">
         <v>46118</v>
       </c>
@@ -4057,7 +4495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:17">
       <c r="B11" s="15">
         <v>46119</v>
       </c>
@@ -4098,7 +4536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:17">
       <c r="B12" s="15">
         <v>46120</v>
       </c>
@@ -4139,7 +4577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:17">
       <c r="B13" s="15">
         <v>46121</v>
       </c>
@@ -4180,7 +4618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:17">
       <c r="B14" s="15">
         <v>46122</v>
       </c>
@@ -4221,7 +4659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:17">
       <c r="B15" s="15">
         <v>46125</v>
       </c>
@@ -4262,7 +4700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:17" ht="17.25" thickBot="1">
       <c r="B16" s="15">
         <v>46126</v>
       </c>
@@ -4303,7 +4741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:8">
       <c r="B17" s="15">
         <v>46127</v>
       </c>
@@ -4326,7 +4764,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:8">
       <c r="B18" s="15">
         <v>46128</v>
       </c>
@@ -4349,7 +4787,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:8">
       <c r="B19" s="15">
         <v>46129</v>
       </c>
@@ -4372,7 +4810,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:8">
       <c r="B20" s="15">
         <v>46132</v>
       </c>
@@ -4395,7 +4833,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:8">
       <c r="B21" s="15">
         <v>46133</v>
       </c>
@@ -4418,7 +4856,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:8">
       <c r="B22" s="15">
         <v>46134</v>
       </c>
@@ -4441,7 +4879,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:8">
       <c r="B23" s="15">
         <v>46135</v>
       </c>
@@ -4464,7 +4902,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:8">
       <c r="B24" s="15">
         <v>46136</v>
       </c>
@@ -4487,7 +4925,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:8">
       <c r="B25" s="15">
         <v>46139</v>
       </c>
@@ -4510,7 +4948,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:8">
       <c r="B26" s="15">
         <v>46140</v>
       </c>
@@ -4533,7 +4971,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:8">
       <c r="B27" s="15">
         <v>46141</v>
       </c>
@@ -4556,7 +4994,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:8" ht="17.25" thickBot="1">
       <c r="B28" s="16">
         <v>46142</v>
       </c>
@@ -4579,7 +5017,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:8">
       <c r="B29" s="2"/>
       <c r="C29" s="4"/>
       <c r="D29" s="2"/>
@@ -4588,10 +5026,10 @@
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:8">
       <c r="C30" s="3"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:8">
       <c r="C31" s="3"/>
     </row>
   </sheetData>
@@ -4600,16 +5038,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B1:Q31"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData>
-    <row r="1" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:17" ht="17.25" thickBot="1">
       <c r="B1" s="1"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="2:17" ht="83.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:17" ht="83.25" thickBot="1">
       <c r="B2" s="13" t="s">
         <v>30</v>
       </c>
@@ -4653,7 +5091,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="2:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:17" ht="33">
       <c r="B3" s="14">
         <v>46107</v>
       </c>
@@ -4694,7 +5132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:17" ht="33">
       <c r="B4" s="15">
         <v>46108</v>
       </c>
@@ -4735,7 +5173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:17">
       <c r="B5" s="15">
         <v>46111</v>
       </c>
@@ -4776,7 +5214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:17" ht="33">
       <c r="B6" s="15">
         <v>46112</v>
       </c>
@@ -4817,7 +5255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:17">
       <c r="B7" s="15">
         <v>46113</v>
       </c>
@@ -4858,7 +5296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:17">
       <c r="B8" s="15">
         <v>46114</v>
       </c>
@@ -4899,7 +5337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:17">
       <c r="B9" s="15">
         <v>46115</v>
       </c>
@@ -4940,7 +5378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:17">
       <c r="B10" s="15">
         <v>46118</v>
       </c>
@@ -4981,7 +5419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:17">
       <c r="B11" s="15">
         <v>46119</v>
       </c>
@@ -5022,7 +5460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:17">
       <c r="B12" s="15">
         <v>46120</v>
       </c>
@@ -5063,7 +5501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:17">
       <c r="B13" s="15">
         <v>46121</v>
       </c>
@@ -5104,7 +5542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:17">
       <c r="B14" s="15">
         <v>46122</v>
       </c>
@@ -5145,7 +5583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:17">
       <c r="B15" s="15">
         <v>46125</v>
       </c>
@@ -5186,7 +5624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:17" ht="17.25" thickBot="1">
       <c r="B16" s="15">
         <v>46126</v>
       </c>
@@ -5227,7 +5665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:8">
       <c r="B17" s="15">
         <v>46127</v>
       </c>
@@ -5250,7 +5688,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:8">
       <c r="B18" s="15">
         <v>46128</v>
       </c>
@@ -5273,7 +5711,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:8">
       <c r="B19" s="15">
         <v>46129</v>
       </c>
@@ -5296,7 +5734,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:8">
       <c r="B20" s="15">
         <v>46132</v>
       </c>
@@ -5319,7 +5757,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:8">
       <c r="B21" s="15">
         <v>46133</v>
       </c>
@@ -5342,7 +5780,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:8">
       <c r="B22" s="15">
         <v>46134</v>
       </c>
@@ -5365,7 +5803,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:8">
       <c r="B23" s="15">
         <v>46135</v>
       </c>
@@ -5388,7 +5826,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:8">
       <c r="B24" s="15">
         <v>46136</v>
       </c>
@@ -5411,7 +5849,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:8">
       <c r="B25" s="15">
         <v>46139</v>
       </c>
@@ -5434,7 +5872,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:8">
       <c r="B26" s="15">
         <v>46140</v>
       </c>
@@ -5457,7 +5895,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:8">
       <c r="B27" s="15">
         <v>46141</v>
       </c>
@@ -5480,7 +5918,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:8" ht="17.25" thickBot="1">
       <c r="B28" s="16">
         <v>46142</v>
       </c>
@@ -5503,7 +5941,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:8">
       <c r="B29" s="2"/>
       <c r="C29" s="4"/>
       <c r="D29" s="2"/>
@@ -5512,10 +5950,10 @@
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:8">
       <c r="C30" s="3"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:8">
       <c r="C31" s="3"/>
     </row>
   </sheetData>
@@ -5524,16 +5962,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B1:Q31"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData>
-    <row r="1" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:17" ht="17.25" thickBot="1">
       <c r="B1" s="1"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="2:17" ht="83.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:17" ht="83.25" thickBot="1">
       <c r="B2" s="13" t="s">
         <v>30</v>
       </c>
@@ -5577,7 +6015,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="2:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:17" ht="33">
       <c r="B3" s="14">
         <v>46107</v>
       </c>
@@ -5618,7 +6056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:17" ht="33">
       <c r="B4" s="15">
         <v>46108</v>
       </c>
@@ -5659,7 +6097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:17">
       <c r="B5" s="15">
         <v>46111</v>
       </c>
@@ -5700,7 +6138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:17" ht="33">
       <c r="B6" s="15">
         <v>46112</v>
       </c>
@@ -5741,7 +6179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:17">
       <c r="B7" s="15">
         <v>46113</v>
       </c>
@@ -5782,7 +6220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:17">
       <c r="B8" s="15">
         <v>46114</v>
       </c>
@@ -5823,7 +6261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:17">
       <c r="B9" s="15">
         <v>46115</v>
       </c>
@@ -5864,7 +6302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:17">
       <c r="B10" s="15">
         <v>46118</v>
       </c>
@@ -5905,7 +6343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:17">
       <c r="B11" s="15">
         <v>46119</v>
       </c>
@@ -5946,7 +6384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:17">
       <c r="B12" s="15">
         <v>46120</v>
       </c>
@@ -5987,7 +6425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:17">
       <c r="B13" s="15">
         <v>46121</v>
       </c>
@@ -6028,7 +6466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:17">
       <c r="B14" s="15">
         <v>46122</v>
       </c>
@@ -6069,7 +6507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:17">
       <c r="B15" s="15">
         <v>46125</v>
       </c>
@@ -6110,7 +6548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:17" ht="17.25" thickBot="1">
       <c r="B16" s="15">
         <v>46126</v>
       </c>
@@ -6151,7 +6589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:8">
       <c r="B17" s="15">
         <v>46127</v>
       </c>
@@ -6174,7 +6612,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:8">
       <c r="B18" s="15">
         <v>46128</v>
       </c>
@@ -6197,7 +6635,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:8">
       <c r="B19" s="15">
         <v>46129</v>
       </c>
@@ -6220,7 +6658,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:8">
       <c r="B20" s="15">
         <v>46132</v>
       </c>
@@ -6243,7 +6681,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:8">
       <c r="B21" s="15">
         <v>46133</v>
       </c>
@@ -6266,7 +6704,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:8">
       <c r="B22" s="15">
         <v>46134</v>
       </c>
@@ -6289,7 +6727,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:8">
       <c r="B23" s="15">
         <v>46135</v>
       </c>
@@ -6312,7 +6750,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:8">
       <c r="B24" s="15">
         <v>46136</v>
       </c>
@@ -6335,7 +6773,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:8">
       <c r="B25" s="15">
         <v>46139</v>
       </c>
@@ -6358,7 +6796,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:8">
       <c r="B26" s="15">
         <v>46140</v>
       </c>
@@ -6381,7 +6819,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:8">
       <c r="B27" s="15">
         <v>46141</v>
       </c>
@@ -6404,7 +6842,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:8" ht="17.25" thickBot="1">
       <c r="B28" s="16">
         <v>46142</v>
       </c>
@@ -6427,7 +6865,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:8">
       <c r="B29" s="2"/>
       <c r="C29" s="4"/>
       <c r="D29" s="2"/>
@@ -6436,10 +6874,10 @@
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:8">
       <c r="C30" s="3"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:8">
       <c r="C31" s="3"/>
     </row>
   </sheetData>
@@ -6448,16 +6886,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B1:Q31"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData>
-    <row r="1" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:17" ht="17.25" thickBot="1">
       <c r="B1" s="1"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="2:17" ht="83.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:17" ht="83.25" thickBot="1">
       <c r="B2" s="13" t="s">
         <v>30</v>
       </c>
@@ -6501,7 +6939,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="2:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:17" ht="33">
       <c r="B3" s="14">
         <v>46107</v>
       </c>
@@ -6542,7 +6980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:17" ht="33">
       <c r="B4" s="15">
         <v>46108</v>
       </c>
@@ -6583,7 +7021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:17">
       <c r="B5" s="15">
         <v>46111</v>
       </c>
@@ -6624,7 +7062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:17" ht="33">
       <c r="B6" s="15">
         <v>46112</v>
       </c>
@@ -6665,7 +7103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:17">
       <c r="B7" s="15">
         <v>46113</v>
       </c>
@@ -6706,7 +7144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:17">
       <c r="B8" s="15">
         <v>46114</v>
       </c>
@@ -6747,7 +7185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:17">
       <c r="B9" s="15">
         <v>46115</v>
       </c>
@@ -6788,7 +7226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:17">
       <c r="B10" s="15">
         <v>46118</v>
       </c>
@@ -6829,7 +7267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:17">
       <c r="B11" s="15">
         <v>46119</v>
       </c>
@@ -6870,7 +7308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:17">
       <c r="B12" s="15">
         <v>46120</v>
       </c>
@@ -6911,7 +7349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:17">
       <c r="B13" s="15">
         <v>46121</v>
       </c>
@@ -6952,7 +7390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:17">
       <c r="B14" s="15">
         <v>46122</v>
       </c>
@@ -6993,7 +7431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:17">
       <c r="B15" s="15">
         <v>46125</v>
       </c>
@@ -7034,7 +7472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:17" ht="17.25" thickBot="1">
       <c r="B16" s="15">
         <v>46126</v>
       </c>
@@ -7075,7 +7513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:8">
       <c r="B17" s="15">
         <v>46127</v>
       </c>
@@ -7098,7 +7536,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:8">
       <c r="B18" s="15">
         <v>46128</v>
       </c>
@@ -7121,7 +7559,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:8">
       <c r="B19" s="15">
         <v>46129</v>
       </c>
@@ -7144,7 +7582,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:8">
       <c r="B20" s="15">
         <v>46132</v>
       </c>
@@ -7167,7 +7605,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:8">
       <c r="B21" s="15">
         <v>46133</v>
       </c>
@@ -7190,7 +7628,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:8">
       <c r="B22" s="15">
         <v>46134</v>
       </c>
@@ -7213,7 +7651,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:8">
       <c r="B23" s="15">
         <v>46135</v>
       </c>
@@ -7236,7 +7674,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:8">
       <c r="B24" s="15">
         <v>46136</v>
       </c>
@@ -7259,7 +7697,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:8">
       <c r="B25" s="15">
         <v>46139</v>
       </c>
@@ -7282,7 +7720,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:8">
       <c r="B26" s="15">
         <v>46140</v>
       </c>
@@ -7305,7 +7743,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:8">
       <c r="B27" s="15">
         <v>46141</v>
       </c>
@@ -7328,7 +7766,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:8" ht="17.25" thickBot="1">
       <c r="B28" s="16">
         <v>46142</v>
       </c>
@@ -7351,7 +7789,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:8">
       <c r="B29" s="2"/>
       <c r="C29" s="4"/>
       <c r="D29" s="2"/>
@@ -7360,10 +7798,10 @@
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:8">
       <c r="C30" s="3"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:8">
       <c r="C31" s="3"/>
     </row>
   </sheetData>
@@ -7372,16 +7810,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="B1:Q31"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData>
-    <row r="1" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:17" ht="17.25" thickBot="1">
       <c r="B1" s="1"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="2:17" ht="83.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:17" ht="83.25" thickBot="1">
       <c r="B2" s="13" t="s">
         <v>30</v>
       </c>
@@ -7425,7 +7863,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="2:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:17" ht="33">
       <c r="B3" s="14">
         <v>46107</v>
       </c>
@@ -7466,7 +7904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:17" ht="33">
       <c r="B4" s="15">
         <v>46108</v>
       </c>
@@ -7507,7 +7945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:17">
       <c r="B5" s="15">
         <v>46111</v>
       </c>
@@ -7548,7 +7986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:17" ht="33">
       <c r="B6" s="15">
         <v>46112</v>
       </c>
@@ -7589,7 +8027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:17">
       <c r="B7" s="15">
         <v>46113</v>
       </c>
@@ -7630,7 +8068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:17">
       <c r="B8" s="15">
         <v>46114</v>
       </c>
@@ -7671,7 +8109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:17">
       <c r="B9" s="15">
         <v>46115</v>
       </c>
@@ -7712,7 +8150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:17">
       <c r="B10" s="15">
         <v>46118</v>
       </c>
@@ -7753,7 +8191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:17">
       <c r="B11" s="15">
         <v>46119</v>
       </c>
@@ -7794,7 +8232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:17">
       <c r="B12" s="15">
         <v>46120</v>
       </c>
@@ -7835,7 +8273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:17">
       <c r="B13" s="15">
         <v>46121</v>
       </c>
@@ -7876,7 +8314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:17">
       <c r="B14" s="15">
         <v>46122</v>
       </c>
@@ -7917,7 +8355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:17">
       <c r="B15" s="15">
         <v>46125</v>
       </c>
@@ -7958,7 +8396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:17" ht="17.25" thickBot="1">
       <c r="B16" s="15">
         <v>46126</v>
       </c>
@@ -7999,7 +8437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:8">
       <c r="B17" s="15">
         <v>46127</v>
       </c>
@@ -8022,7 +8460,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:8">
       <c r="B18" s="15">
         <v>46128</v>
       </c>
@@ -8045,7 +8483,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:8">
       <c r="B19" s="15">
         <v>46129</v>
       </c>
@@ -8068,7 +8506,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:8">
       <c r="B20" s="15">
         <v>46132</v>
       </c>
@@ -8091,7 +8529,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:8">
       <c r="B21" s="15">
         <v>46133</v>
       </c>
@@ -8114,7 +8552,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:8">
       <c r="B22" s="15">
         <v>46134</v>
       </c>
@@ -8137,7 +8575,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:8">
       <c r="B23" s="15">
         <v>46135</v>
       </c>
@@ -8160,7 +8598,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:8">
       <c r="B24" s="15">
         <v>46136</v>
       </c>
@@ -8183,7 +8621,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:8">
       <c r="B25" s="15">
         <v>46139</v>
       </c>
@@ -8206,7 +8644,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:8">
       <c r="B26" s="15">
         <v>46140</v>
       </c>
@@ -8229,7 +8667,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:8">
       <c r="B27" s="15">
         <v>46141</v>
       </c>
@@ -8252,7 +8690,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:8" ht="17.25" thickBot="1">
       <c r="B28" s="16">
         <v>46142</v>
       </c>
@@ -8275,7 +8713,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:8">
       <c r="B29" s="2"/>
       <c r="C29" s="4"/>
       <c r="D29" s="2"/>
@@ -8284,10 +8722,10 @@
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:8">
       <c r="C30" s="3"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:8">
       <c r="C31" s="3"/>
     </row>
   </sheetData>

--- a/daily.xml.xlsx
+++ b/daily.xml.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hyojung2\2026-AI-FULLSTACK-LevelUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E22995A-C9EC-4436-A53F-473FE5770DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D4FCE10-1F88-498D-B80E-FC522C1D8545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28815" yWindow="45" windowWidth="11160" windowHeight="15600" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="2026. 3~4월" sheetId="1" r:id="rId1"/>
-    <sheet name="2026.5" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="8" r:id="rId3"/>
+    <sheet name="full stack" sheetId="8" r:id="rId1"/>
+    <sheet name="2026. 3~4월" sheetId="1" r:id="rId2"/>
+    <sheet name="2026.5" sheetId="2" r:id="rId3"/>
     <sheet name="2026.6" sheetId="3" r:id="rId4"/>
     <sheet name="2026.7" sheetId="4" r:id="rId5"/>
     <sheet name="2026.8" sheetId="5" r:id="rId6"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1287" uniqueCount="114">
   <si>
     <t>출석일수 (Attendance Days)</t>
   </si>
@@ -1012,6 +1012,10 @@
     <t xml:space="preserve">   codeReviews: 다른 학습자에게 코드 리뷰/멘토링을 해준 횟수 (예: 0회 → 커뮤니티 챌린지 조건 미충족)</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
+  <si>
+    <t>ctrl + alt + v</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1209,7 +1213,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="48">
+  <borders count="53">
     <border>
       <left/>
       <right/>
@@ -1834,14 +1838,77 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF7F7F7F"/>
       </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -1859,7 +1926,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2130,9 +2197,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -2147,6 +2211,33 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="50" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="51" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="52" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2430,6 +2521,162 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5311FA83-4A96-4545-9E60-5FB40A21CCD1}">
+  <dimension ref="A2:G27"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetData>
+    <row r="2" spans="1:4" ht="26.25">
+      <c r="D2" s="91" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="90" t="s">
+        <v>82</v>
+      </c>
+      <c r="D3" s="92"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="90" t="s">
+        <v>107</v>
+      </c>
+      <c r="D4" s="93" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="90" t="s">
+        <v>83</v>
+      </c>
+      <c r="D5" s="93" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="90" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" s="93" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="90" t="s">
+        <v>85</v>
+      </c>
+      <c r="D7" s="93" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="90" t="s">
+        <v>86</v>
+      </c>
+      <c r="D8" s="93" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="90" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" s="93" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="90" t="s">
+        <v>88</v>
+      </c>
+      <c r="D10" s="93" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="90" t="s">
+        <v>89</v>
+      </c>
+      <c r="D11" s="93" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="90" t="s">
+        <v>90</v>
+      </c>
+      <c r="D12" s="93" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="90" t="s">
+        <v>91</v>
+      </c>
+      <c r="D13" s="93" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="90" t="s">
+        <v>92</v>
+      </c>
+      <c r="D14" s="93" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="90" t="s">
+        <v>109</v>
+      </c>
+      <c r="D15" s="93" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="90" t="s">
+        <v>108</v>
+      </c>
+      <c r="D16" s="94" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="90" t="s">
+        <v>110</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="90" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="E19" s="92"/>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="E21" s="92"/>
+      <c r="G21" s="90"/>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="E23" s="92"/>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="E25" s="92"/>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="E27" s="92"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:Q29"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
@@ -3410,21 +3657,22 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B1:Q31"/>
+  <dimension ref="B1:R31"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="10.625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.875" customWidth="1"/>
-    <col min="9" max="9" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" ht="17.25" thickBot="1">
+    <row r="1" spans="2:18" ht="17.25" thickBot="1">
       <c r="B1" s="1"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="2:17" ht="83.25" thickBot="1">
+    <row r="2" spans="2:18" ht="83.25" thickBot="1">
       <c r="B2" s="13" t="s">
         <v>30</v>
       </c>
@@ -3446,29 +3694,29 @@
       <c r="H2" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="28" t="s">
+      <c r="K2" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="K2" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="L2" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="M2" s="25" t="s">
+      <c r="L2" s="99" t="s">
+        <v>0</v>
+      </c>
+      <c r="M2" s="100" t="s">
+        <v>1</v>
+      </c>
+      <c r="N2" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="N2" s="25" t="s">
+      <c r="O2" s="100" t="s">
         <v>3</v>
       </c>
-      <c r="O2" s="26" t="s">
+      <c r="P2" s="101" t="s">
         <v>4</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="2:17" ht="17.25" thickBot="1">
+    <row r="3" spans="2:18" ht="17.25" thickBot="1">
       <c r="B3" s="73">
         <v>46148</v>
       </c>
@@ -3493,26 +3741,27 @@
       <c r="I3" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="J3" s="29" t="s">
+      <c r="J3" s="61"/>
+      <c r="K3" s="96" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="30">
-        <v>28</v>
-      </c>
-      <c r="L3" s="31">
-        <v>1</v>
-      </c>
-      <c r="M3" s="31">
-        <v>1</v>
-      </c>
-      <c r="N3" s="31">
-        <v>37</v>
-      </c>
-      <c r="O3" s="32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="2:17" ht="99.75" thickBot="1">
+      <c r="L3" s="35">
+        <v>30</v>
+      </c>
+      <c r="M3" s="35">
+        <v>1</v>
+      </c>
+      <c r="N3" s="35">
+        <v>1</v>
+      </c>
+      <c r="O3" s="102">
+        <v>38</v>
+      </c>
+      <c r="P3" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:18" ht="99.75" thickBot="1">
       <c r="B4" s="14">
         <v>46149</v>
       </c>
@@ -3537,26 +3786,27 @@
       <c r="I4" s="89" t="s">
         <v>81</v>
       </c>
-      <c r="J4" s="33" t="s">
+      <c r="J4" s="89"/>
+      <c r="K4" s="97" t="s">
         <v>6</v>
       </c>
-      <c r="K4" s="30">
-        <v>28</v>
-      </c>
       <c r="L4" s="35">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="M4" s="35">
         <v>1</v>
       </c>
-      <c r="N4" s="31">
-        <v>37</v>
-      </c>
-      <c r="O4" s="36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="2:17" ht="17.25" thickBot="1">
+      <c r="N4" s="35">
+        <v>1</v>
+      </c>
+      <c r="O4" s="102">
+        <v>38</v>
+      </c>
+      <c r="P4" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:18" ht="17.25" thickBot="1">
       <c r="B5" s="76">
         <v>46150</v>
       </c>
@@ -3578,26 +3828,26 @@
       <c r="H5" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="33" t="s">
+      <c r="K5" s="97" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="30">
-        <v>28</v>
-      </c>
       <c r="L5" s="35">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="M5" s="35">
         <v>1</v>
       </c>
-      <c r="N5" s="31">
-        <v>35</v>
-      </c>
-      <c r="O5" s="36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="2:17" ht="17.25" thickBot="1">
+      <c r="N5" s="35">
+        <v>1</v>
+      </c>
+      <c r="O5" s="102">
+        <v>36</v>
+      </c>
+      <c r="P5" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:18" ht="17.25" thickBot="1">
       <c r="B6" s="78">
         <v>46153</v>
       </c>
@@ -3619,26 +3869,26 @@
       <c r="H6" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="J6" s="33" t="s">
+      <c r="K6" s="97" t="s">
         <v>8</v>
       </c>
-      <c r="K6" s="30">
-        <v>28</v>
-      </c>
       <c r="L6" s="35">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="M6" s="35">
         <v>1</v>
       </c>
-      <c r="N6" s="31">
-        <v>33</v>
-      </c>
-      <c r="O6" s="36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:17" ht="17.25" thickBot="1">
+      <c r="N6" s="35">
+        <v>1</v>
+      </c>
+      <c r="O6" s="102">
+        <v>34</v>
+      </c>
+      <c r="P6" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:18" ht="17.25" thickBot="1">
       <c r="B7" s="78">
         <v>46154</v>
       </c>
@@ -3660,26 +3910,26 @@
       <c r="H7" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="J7" s="33" t="s">
+      <c r="K7" s="97" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="30">
-        <v>28</v>
-      </c>
       <c r="L7" s="35">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="M7" s="35">
         <v>1</v>
       </c>
-      <c r="N7" s="31">
-        <v>32</v>
-      </c>
-      <c r="O7" s="36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="2:17" ht="17.25" thickBot="1">
+      <c r="N7" s="35">
+        <v>1</v>
+      </c>
+      <c r="O7" s="102">
+        <v>33</v>
+      </c>
+      <c r="P7" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:18" ht="17.25" thickBot="1">
       <c r="B8" s="78">
         <v>46155</v>
       </c>
@@ -3701,26 +3951,26 @@
       <c r="H8" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="J8" s="33" t="s">
+      <c r="K8" s="97" t="s">
         <v>10</v>
       </c>
-      <c r="K8" s="30">
-        <v>27</v>
-      </c>
       <c r="L8" s="35">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="M8" s="35">
         <v>1</v>
       </c>
-      <c r="N8" s="31">
-        <v>38</v>
-      </c>
-      <c r="O8" s="36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="2:17" ht="17.25" thickBot="1">
+      <c r="N8" s="35">
+        <v>1</v>
+      </c>
+      <c r="O8" s="102">
+        <v>39</v>
+      </c>
+      <c r="P8" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:18" ht="17.25" thickBot="1">
       <c r="B9" s="78">
         <v>46156</v>
       </c>
@@ -3742,26 +3992,26 @@
       <c r="H9" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="J9" s="33" t="s">
+      <c r="K9" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="K9" s="30">
-        <v>28</v>
-      </c>
       <c r="L9" s="35">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="M9" s="35">
         <v>1</v>
       </c>
-      <c r="N9" s="31">
-        <v>31</v>
-      </c>
-      <c r="O9" s="36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="2:17" ht="17.25" thickBot="1">
+      <c r="N9" s="35">
+        <v>1</v>
+      </c>
+      <c r="O9" s="102">
+        <v>32</v>
+      </c>
+      <c r="P9" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:18" ht="17.25" thickBot="1">
       <c r="B10" s="78">
         <v>46157</v>
       </c>
@@ -3783,26 +4033,26 @@
       <c r="H10" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="J10" s="33" t="s">
+      <c r="K10" s="97" t="s">
         <v>12</v>
       </c>
-      <c r="K10" s="30">
-        <v>28</v>
-      </c>
       <c r="L10" s="35">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="M10" s="35">
         <v>1</v>
       </c>
-      <c r="N10" s="31">
-        <v>32</v>
-      </c>
-      <c r="O10" s="36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="2:17" ht="17.25" thickBot="1">
+      <c r="N10" s="35">
+        <v>1</v>
+      </c>
+      <c r="O10" s="102">
+        <v>33</v>
+      </c>
+      <c r="P10" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:18" ht="17.25" thickBot="1">
       <c r="B11" s="78">
         <v>46160</v>
       </c>
@@ -3824,26 +4074,26 @@
       <c r="H11" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="J11" s="33" t="s">
+      <c r="K11" s="97" t="s">
         <v>13</v>
       </c>
-      <c r="K11" s="30">
-        <v>28</v>
-      </c>
       <c r="L11" s="35">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="M11" s="35">
         <v>1</v>
       </c>
-      <c r="N11" s="31">
-        <v>33</v>
-      </c>
-      <c r="O11" s="36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="2:17" ht="17.25" thickBot="1">
+      <c r="N11" s="35">
+        <v>1</v>
+      </c>
+      <c r="O11" s="102">
+        <v>34</v>
+      </c>
+      <c r="P11" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:18" ht="17.25" thickBot="1">
       <c r="B12" s="78">
         <v>46161</v>
       </c>
@@ -3865,26 +4115,26 @@
       <c r="H12" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="J12" s="33" t="s">
+      <c r="K12" s="97" t="s">
         <v>14</v>
       </c>
-      <c r="K12" s="30">
-        <v>25</v>
-      </c>
       <c r="L12" s="35">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="M12" s="35">
         <v>1</v>
       </c>
-      <c r="N12" s="31">
-        <v>32</v>
-      </c>
-      <c r="O12" s="36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="2:17" ht="17.25" thickBot="1">
+      <c r="N12" s="35">
+        <v>1</v>
+      </c>
+      <c r="O12" s="102">
+        <v>33</v>
+      </c>
+      <c r="P12" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:18" ht="17.25" thickBot="1">
       <c r="B13" s="78">
         <v>46162</v>
       </c>
@@ -3906,26 +4156,26 @@
       <c r="H13" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="J13" s="33" t="s">
+      <c r="K13" s="97" t="s">
         <v>15</v>
       </c>
-      <c r="K13" s="30">
-        <v>28</v>
-      </c>
       <c r="L13" s="35">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="M13" s="35">
         <v>1</v>
       </c>
-      <c r="N13" s="31">
-        <v>38</v>
-      </c>
-      <c r="O13" s="36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="2:17" ht="17.25" thickBot="1">
+      <c r="N13" s="35">
+        <v>1</v>
+      </c>
+      <c r="O13" s="102">
+        <v>39</v>
+      </c>
+      <c r="P13" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:18" ht="17.25" thickBot="1">
       <c r="B14" s="78">
         <v>46163</v>
       </c>
@@ -3947,26 +4197,26 @@
       <c r="H14" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="J14" s="33" t="s">
+      <c r="K14" s="97" t="s">
         <v>16</v>
       </c>
-      <c r="K14" s="30">
-        <v>28</v>
-      </c>
       <c r="L14" s="35">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="M14" s="35">
         <v>1</v>
       </c>
-      <c r="N14" s="31">
-        <v>35</v>
-      </c>
-      <c r="O14" s="36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="2:17" ht="17.25" thickBot="1">
+      <c r="N14" s="35">
+        <v>1</v>
+      </c>
+      <c r="O14" s="102">
+        <v>36</v>
+      </c>
+      <c r="P14" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:18" ht="17.25" thickBot="1">
       <c r="B15" s="78">
         <v>46164</v>
       </c>
@@ -3988,26 +4238,26 @@
       <c r="H15" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="J15" s="33" t="s">
+      <c r="K15" s="97" t="s">
         <v>17</v>
       </c>
-      <c r="K15" s="30">
-        <v>28</v>
-      </c>
       <c r="L15" s="35">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="M15" s="35">
         <v>1</v>
       </c>
-      <c r="N15" s="31">
-        <v>44</v>
-      </c>
-      <c r="O15" s="36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="2:17" ht="17.25" thickBot="1">
+      <c r="N15" s="35">
+        <v>1</v>
+      </c>
+      <c r="O15" s="102">
+        <v>45</v>
+      </c>
+      <c r="P15" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:18" ht="17.25" thickBot="1">
       <c r="B16" s="81">
         <v>46167</v>
       </c>
@@ -4029,26 +4279,26 @@
       <c r="H16" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="J16" s="37" t="s">
+      <c r="K16" s="98" t="s">
         <v>77</v>
       </c>
-      <c r="K16" s="90">
-        <v>27</v>
-      </c>
       <c r="L16" s="39">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="M16" s="39">
         <v>1</v>
       </c>
-      <c r="N16" s="41">
-        <v>32</v>
-      </c>
-      <c r="O16" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8" ht="17.25" thickBot="1">
+      <c r="N16" s="39">
+        <v>1</v>
+      </c>
+      <c r="O16" s="103">
+        <v>33</v>
+      </c>
+      <c r="P16" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14" ht="17.25" thickBot="1">
       <c r="B17" s="78">
         <v>46168</v>
       </c>
@@ -4071,7 +4321,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="17.25" thickBot="1">
+    <row r="18" spans="2:14" ht="17.25" thickBot="1">
       <c r="B18" s="78">
         <v>46169</v>
       </c>
@@ -4093,8 +4343,14 @@
       <c r="H18" s="6" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="19" spans="2:8" ht="17.25" thickBot="1">
+      <c r="M18" s="95">
+        <v>1</v>
+      </c>
+      <c r="N18" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14" ht="17.25" thickBot="1">
       <c r="B19" s="78">
         <v>46170</v>
       </c>
@@ -4117,7 +4373,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="17.25" thickBot="1">
+    <row r="20" spans="2:14" ht="17.25" thickBot="1">
       <c r="B20" s="78">
         <v>46171</v>
       </c>
@@ -4140,7 +4396,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="2:14">
       <c r="B21" s="15"/>
       <c r="C21" s="23"/>
       <c r="D21" s="75"/>
@@ -4149,7 +4405,7 @@
       <c r="G21" s="5"/>
       <c r="H21" s="6"/>
     </row>
-    <row r="22" spans="2:8" ht="17.25" thickBot="1">
+    <row r="22" spans="2:14" ht="17.25" thickBot="1">
       <c r="B22" s="15"/>
       <c r="C22" s="23"/>
       <c r="D22" s="18"/>
@@ -4158,7 +4414,7 @@
       <c r="G22" s="5"/>
       <c r="H22" s="6"/>
     </row>
-    <row r="23" spans="2:8" ht="17.25" thickBot="1">
+    <row r="23" spans="2:14" ht="17.25" thickBot="1">
       <c r="B23" s="15"/>
       <c r="C23" s="23"/>
       <c r="D23" s="75"/>
@@ -4167,7 +4423,7 @@
       <c r="G23" s="5"/>
       <c r="H23" s="6"/>
     </row>
-    <row r="24" spans="2:8" ht="17.25" thickBot="1">
+    <row r="24" spans="2:14" ht="17.25" thickBot="1">
       <c r="B24" s="15"/>
       <c r="C24" s="23"/>
       <c r="D24" s="75"/>
@@ -4176,7 +4432,7 @@
       <c r="G24" s="5"/>
       <c r="H24" s="6"/>
     </row>
-    <row r="25" spans="2:8">
+    <row r="25" spans="2:14">
       <c r="B25" s="15"/>
       <c r="C25" s="23"/>
       <c r="D25" s="75"/>
@@ -4185,7 +4441,7 @@
       <c r="G25" s="5"/>
       <c r="H25" s="6"/>
     </row>
-    <row r="26" spans="2:8" ht="17.25" thickBot="1">
+    <row r="26" spans="2:14" ht="17.25" thickBot="1">
       <c r="B26" s="15"/>
       <c r="C26" s="23"/>
       <c r="D26" s="18"/>
@@ -4194,7 +4450,7 @@
       <c r="G26" s="5"/>
       <c r="H26" s="6"/>
     </row>
-    <row r="27" spans="2:8" ht="17.25" thickBot="1">
+    <row r="27" spans="2:14" ht="17.25" thickBot="1">
       <c r="B27" s="15"/>
       <c r="C27" s="23"/>
       <c r="D27" s="75"/>
@@ -4203,7 +4459,7 @@
       <c r="G27" s="5"/>
       <c r="H27" s="6"/>
     </row>
-    <row r="28" spans="2:8" ht="17.25" thickBot="1">
+    <row r="28" spans="2:14" ht="17.25" thickBot="1">
       <c r="B28" s="16"/>
       <c r="C28" s="24"/>
       <c r="D28" s="75"/>
@@ -4212,7 +4468,7 @@
       <c r="G28" s="7"/>
       <c r="H28" s="8"/>
     </row>
-    <row r="29" spans="2:8">
+    <row r="29" spans="2:14">
       <c r="B29" s="2"/>
       <c r="C29" s="4"/>
       <c r="D29" s="2"/>
@@ -4221,167 +4477,11 @@
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
     </row>
-    <row r="30" spans="2:8">
+    <row r="30" spans="2:14">
       <c r="C30" s="3"/>
     </row>
-    <row r="31" spans="2:8">
+    <row r="31" spans="2:14">
       <c r="C31" s="3"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5311FA83-4A96-4545-9E60-5FB40A21CCD1}">
-  <dimension ref="A2:G27"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
-  <sheetData>
-    <row r="2" spans="1:4" ht="26.25">
-      <c r="D2" s="92" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="91" t="s">
-        <v>82</v>
-      </c>
-      <c r="D3" s="93"/>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="91" t="s">
-        <v>107</v>
-      </c>
-      <c r="D4" s="94" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="91" t="s">
-        <v>83</v>
-      </c>
-      <c r="D5" s="94" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="91" t="s">
-        <v>84</v>
-      </c>
-      <c r="D6" s="94" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="91" t="s">
-        <v>85</v>
-      </c>
-      <c r="D7" s="94" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="91" t="s">
-        <v>86</v>
-      </c>
-      <c r="D8" s="94" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="91" t="s">
-        <v>87</v>
-      </c>
-      <c r="D9" s="94" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="91" t="s">
-        <v>88</v>
-      </c>
-      <c r="D10" s="94" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="91" t="s">
-        <v>89</v>
-      </c>
-      <c r="D11" s="94" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="91" t="s">
-        <v>90</v>
-      </c>
-      <c r="D12" s="94" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="91" t="s">
-        <v>91</v>
-      </c>
-      <c r="D13" s="94" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="91" t="s">
-        <v>92</v>
-      </c>
-      <c r="D14" s="94" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="91" t="s">
-        <v>109</v>
-      </c>
-      <c r="D15" s="94" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="91" t="s">
-        <v>108</v>
-      </c>
-      <c r="D16" s="95" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="91" t="s">
-        <v>110</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="91" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="E19" s="93"/>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="E21" s="93"/>
-      <c r="G21" s="91"/>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="E23" s="93"/>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="E25" s="93"/>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="E27" s="93"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>

--- a/daily.xml.xlsx
+++ b/daily.xml.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hyojung2\2026-AI-FULLSTACK-LevelUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D4FCE10-1F88-498D-B80E-FC522C1D8545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{713C20F5-3F7A-47EC-B8DF-59007A3C0066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28815" yWindow="45" windowWidth="11160" windowHeight="15600" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="full stack" sheetId="8" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1287" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="118">
   <si>
     <t>출석일수 (Attendance Days)</t>
   </si>
@@ -650,22 +650,6 @@
   </si>
   <si>
     <r>
-      <t>blogsWritten</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: 작성한 학습 블로그 글 수 (예: 6개 → 블로그왕 조건 충족)</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>tutorialsShared</t>
     </r>
     <r>
@@ -678,22 +662,6 @@
         <scheme val="minor"/>
       </rPr>
       <t>: 공유한 튜토리얼/가이드 수 (예: 2개 → 튜토리얼 제작자 조건 충족)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>bugsFixed</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: 다른 학습자의 코드 버그 해결 횟수 (예: 7회 → 디버깅 마스터 조건 충족)</t>
     </r>
   </si>
   <si>
@@ -1014,6 +982,58 @@
   </si>
   <si>
     <t>ctrl + alt + v</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>bugsFixed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 다른 학습자의 코드 버그 해결 횟수 (예: 7회 → 디버깅 마스터 조건 충족)</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>blogsWritten</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 작성한 학습 블로그 글 수 (예: 6개 → 블로그왕 조건 충족)</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">신의손 획득~!  
+수정 , 보라, 주엽,욱진, 윤정 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>대원, 현미님, 욱진님, 채연, 창기</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>전원 출석
+-장영탁외</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>윤정, 주엽, 채연, 보라</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -2538,7 +2558,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="90" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D4" s="93" t="s">
         <v>95</v>
@@ -2589,7 +2609,7 @@
         <v>88</v>
       </c>
       <c r="D10" s="93" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2597,7 +2617,7 @@
         <v>89</v>
       </c>
       <c r="D11" s="93" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2605,7 +2625,7 @@
         <v>90</v>
       </c>
       <c r="D12" s="93" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2613,7 +2633,7 @@
         <v>91</v>
       </c>
       <c r="D13" s="93" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2621,31 +2641,31 @@
         <v>92</v>
       </c>
       <c r="D14" s="93" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="90" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D15" s="93" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="90" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D16" s="94" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="90" t="s">
+        <v>108</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -3659,20 +3679,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B1:R31"/>
+  <dimension ref="A1:R31"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="10.625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.875" customWidth="1"/>
-    <col min="9" max="9" width="18.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" ht="17.25" thickBot="1">
+    <row r="1" spans="1:18" ht="17.25" thickBot="1">
       <c r="B1" s="1"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="2:18" ht="83.25" thickBot="1">
+    <row r="2" spans="1:18" ht="83.25" thickBot="1">
       <c r="B2" s="13" t="s">
         <v>30</v>
       </c>
@@ -3716,7 +3736,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="2:18" ht="17.25" thickBot="1">
+    <row r="3" spans="1:18" ht="17.25" thickBot="1">
       <c r="B3" s="73">
         <v>46148</v>
       </c>
@@ -3746,7 +3766,7 @@
         <v>5</v>
       </c>
       <c r="L3" s="35">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M3" s="35">
         <v>1</v>
@@ -3755,13 +3775,13 @@
         <v>1</v>
       </c>
       <c r="O3" s="102">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="P3" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="99.75" thickBot="1">
+    <row r="4" spans="1:18" ht="99.75" thickBot="1">
       <c r="B4" s="14">
         <v>46149</v>
       </c>
@@ -3791,7 +3811,7 @@
         <v>6</v>
       </c>
       <c r="L4" s="35">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M4" s="35">
         <v>1</v>
@@ -3800,13 +3820,13 @@
         <v>1</v>
       </c>
       <c r="O4" s="102">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="P4" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:18" ht="17.25" thickBot="1">
+    <row r="5" spans="1:18" ht="50.25" thickBot="1">
       <c r="B5" s="76">
         <v>46150</v>
       </c>
@@ -3828,11 +3848,14 @@
       <c r="H5" s="67" t="s">
         <v>23</v>
       </c>
+      <c r="I5" s="89" t="s">
+        <v>114</v>
+      </c>
       <c r="K5" s="97" t="s">
         <v>7</v>
       </c>
       <c r="L5" s="35">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M5" s="35">
         <v>1</v>
@@ -3841,13 +3864,13 @@
         <v>1</v>
       </c>
       <c r="O5" s="102">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P5" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:18" ht="17.25" thickBot="1">
+    <row r="6" spans="1:18" ht="33.75" thickBot="1">
       <c r="B6" s="78">
         <v>46153</v>
       </c>
@@ -3855,7 +3878,7 @@
         <v>27</v>
       </c>
       <c r="D6" s="86" t="s">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="E6" s="79" t="s">
         <v>23</v>
@@ -3868,12 +3891,15 @@
       </c>
       <c r="H6" s="80" t="s">
         <v>23</v>
+      </c>
+      <c r="I6" s="61" t="s">
+        <v>115</v>
       </c>
       <c r="K6" s="97" t="s">
         <v>8</v>
       </c>
       <c r="L6" s="35">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M6" s="35">
         <v>1</v>
@@ -3882,13 +3908,16 @@
         <v>1</v>
       </c>
       <c r="O6" s="102">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P6" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:18" ht="17.25" thickBot="1">
+    <row r="7" spans="1:18" ht="33.75" thickBot="1">
+      <c r="A7" s="1">
+        <v>31</v>
+      </c>
       <c r="B7" s="78">
         <v>46154</v>
       </c>
@@ -3910,11 +3939,14 @@
       <c r="H7" s="6" t="s">
         <v>23</v>
       </c>
+      <c r="I7" s="61" t="s">
+        <v>117</v>
+      </c>
       <c r="K7" s="97" t="s">
         <v>9</v>
       </c>
       <c r="L7" s="35">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M7" s="35">
         <v>1</v>
@@ -3923,13 +3955,13 @@
         <v>1</v>
       </c>
       <c r="O7" s="102">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P7" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:18" ht="17.25" thickBot="1">
+    <row r="8" spans="1:18" ht="17.25" thickBot="1">
       <c r="B8" s="78">
         <v>46155</v>
       </c>
@@ -3955,7 +3987,7 @@
         <v>10</v>
       </c>
       <c r="L8" s="35">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M8" s="35">
         <v>1</v>
@@ -3970,7 +4002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:18" ht="17.25" thickBot="1">
+    <row r="9" spans="1:18" ht="17.25" thickBot="1">
       <c r="B9" s="78">
         <v>46156</v>
       </c>
@@ -3996,7 +4028,7 @@
         <v>11</v>
       </c>
       <c r="L9" s="35">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M9" s="35">
         <v>1</v>
@@ -4005,13 +4037,13 @@
         <v>1</v>
       </c>
       <c r="O9" s="102">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P9" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:18" ht="17.25" thickBot="1">
+    <row r="10" spans="1:18" ht="17.25" thickBot="1">
       <c r="B10" s="78">
         <v>46157</v>
       </c>
@@ -4037,7 +4069,7 @@
         <v>12</v>
       </c>
       <c r="L10" s="35">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M10" s="35">
         <v>1</v>
@@ -4052,7 +4084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:18" ht="17.25" thickBot="1">
+    <row r="11" spans="1:18" ht="17.25" thickBot="1">
       <c r="B11" s="78">
         <v>46160</v>
       </c>
@@ -4078,7 +4110,7 @@
         <v>13</v>
       </c>
       <c r="L11" s="35">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M11" s="35">
         <v>1</v>
@@ -4087,13 +4119,13 @@
         <v>1</v>
       </c>
       <c r="O11" s="102">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P11" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:18" ht="17.25" thickBot="1">
+    <row r="12" spans="1:18" ht="17.25" thickBot="1">
       <c r="B12" s="78">
         <v>46161</v>
       </c>
@@ -4134,7 +4166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:18" ht="17.25" thickBot="1">
+    <row r="13" spans="1:18" ht="17.25" thickBot="1">
       <c r="B13" s="78">
         <v>46162</v>
       </c>
@@ -4160,7 +4192,7 @@
         <v>15</v>
       </c>
       <c r="L13" s="35">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M13" s="35">
         <v>1</v>
@@ -4175,7 +4207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:18" ht="17.25" thickBot="1">
+    <row r="14" spans="1:18" ht="17.25" thickBot="1">
       <c r="B14" s="78">
         <v>46163</v>
       </c>
@@ -4201,7 +4233,7 @@
         <v>16</v>
       </c>
       <c r="L14" s="35">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M14" s="35">
         <v>1</v>
@@ -4216,7 +4248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:18" ht="17.25" thickBot="1">
+    <row r="15" spans="1:18" ht="17.25" thickBot="1">
       <c r="B15" s="78">
         <v>46164</v>
       </c>
@@ -4242,7 +4274,7 @@
         <v>17</v>
       </c>
       <c r="L15" s="35">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M15" s="35">
         <v>1</v>
@@ -4251,13 +4283,13 @@
         <v>1</v>
       </c>
       <c r="O15" s="102">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P15" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:18" ht="17.25" thickBot="1">
+    <row r="16" spans="1:18" ht="17.25" thickBot="1">
       <c r="B16" s="81">
         <v>46167</v>
       </c>
@@ -4283,7 +4315,7 @@
         <v>77</v>
       </c>
       <c r="L16" s="39">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M16" s="39">
         <v>1</v>
@@ -4347,7 +4379,7 @@
         <v>1</v>
       </c>
       <c r="N18" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="2:14" ht="17.25" thickBot="1">

--- a/daily.xml.xlsx
+++ b/daily.xml.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hyojung2\2026-AI-FULLSTACK-LevelUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9676A949-0AE8-4687-B4D0-1367B503DA74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD454F9-D4AD-4CDA-81E2-C6EE6F54EF56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3765,7 +3765,7 @@
         <v>5</v>
       </c>
       <c r="L3" s="95">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M3" s="35">
         <v>1</v>
@@ -3774,7 +3774,7 @@
         <v>1</v>
       </c>
       <c r="O3" s="95">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="P3" s="36">
         <v>0</v>
@@ -3813,7 +3813,7 @@
         <v>6</v>
       </c>
       <c r="L4" s="95">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M4" s="35">
         <v>1</v>
@@ -3822,7 +3822,7 @@
         <v>1</v>
       </c>
       <c r="O4" s="95">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="P4" s="36">
         <v>0</v>
@@ -3857,7 +3857,7 @@
         <v>7</v>
       </c>
       <c r="L5" s="95">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M5" s="35">
         <v>1</v>
@@ -3866,7 +3866,7 @@
         <v>1</v>
       </c>
       <c r="O5" s="95">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="P5" s="36">
         <v>0</v>
@@ -3901,7 +3901,7 @@
         <v>8</v>
       </c>
       <c r="L6" s="95">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M6" s="35">
         <v>1</v>
@@ -3910,7 +3910,7 @@
         <v>1</v>
       </c>
       <c r="O6" s="95">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P6" s="36">
         <v>0</v>
@@ -3948,7 +3948,7 @@
         <v>9</v>
       </c>
       <c r="L7" s="95">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M7" s="35">
         <v>1</v>
@@ -3957,7 +3957,7 @@
         <v>1</v>
       </c>
       <c r="O7" s="95">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="P7" s="36">
         <v>0</v>
@@ -3989,7 +3989,7 @@
         <v>10</v>
       </c>
       <c r="L8" s="95">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="M8" s="35">
         <v>1</v>
@@ -3998,7 +3998,7 @@
         <v>1</v>
       </c>
       <c r="O8" s="95">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="P8" s="36">
         <v>0</v>
@@ -4030,7 +4030,7 @@
         <v>11</v>
       </c>
       <c r="L9" s="95">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="M9" s="35">
         <v>1</v>
@@ -4039,7 +4039,7 @@
         <v>1</v>
       </c>
       <c r="O9" s="95">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="P9" s="36">
         <v>0</v>
@@ -4071,7 +4071,7 @@
         <v>12</v>
       </c>
       <c r="L10" s="95">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M10" s="35">
         <v>1</v>
@@ -4080,14 +4080,14 @@
         <v>1</v>
       </c>
       <c r="O10" s="95">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="P10" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="33.75" thickBot="1">
-      <c r="A11">
+      <c r="A11" s="1">
         <v>35</v>
       </c>
       <c r="B11" s="78">
@@ -4115,7 +4115,7 @@
         <v>13</v>
       </c>
       <c r="L11" s="95">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M11" s="35">
         <v>1</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="O11" s="95">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P11" s="36">
         <v>0</v>
@@ -4156,7 +4156,7 @@
         <v>14</v>
       </c>
       <c r="L12" s="95">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="M12" s="35">
         <v>1</v>
@@ -4165,7 +4165,7 @@
         <v>1</v>
       </c>
       <c r="O12" s="95">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="P12" s="36">
         <v>0</v>
@@ -4197,7 +4197,7 @@
         <v>15</v>
       </c>
       <c r="L13" s="95">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M13" s="35">
         <v>1</v>
@@ -4206,7 +4206,7 @@
         <v>1</v>
       </c>
       <c r="O13" s="95">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="P13" s="36">
         <v>0</v>
@@ -4238,7 +4238,7 @@
         <v>16</v>
       </c>
       <c r="L14" s="95">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M14" s="35">
         <v>1</v>
@@ -4247,13 +4247,16 @@
         <v>1</v>
       </c>
       <c r="O14" s="95">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P14" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:19" ht="17.25" thickBot="1">
+      <c r="A15" s="1">
+        <v>39</v>
+      </c>
       <c r="B15" s="78">
         <v>46164</v>
       </c>
@@ -4279,7 +4282,7 @@
         <v>17</v>
       </c>
       <c r="L15" s="95">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M15" s="35">
         <v>1</v>
@@ -4288,7 +4291,7 @@
         <v>1</v>
       </c>
       <c r="O15" s="95">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="P15" s="36">
         <v>0</v>
@@ -4320,7 +4323,7 @@
         <v>77</v>
       </c>
       <c r="L16" s="95">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M16" s="39">
         <v>1</v>
@@ -4329,7 +4332,7 @@
         <v>1</v>
       </c>
       <c r="O16" s="95">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="P16" s="40">
         <v>0</v>
@@ -4381,7 +4384,7 @@
         <v>23</v>
       </c>
       <c r="M18" s="95">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N18" t="s">
         <v>111</v>

--- a/daily.xml.xlsx
+++ b/daily.xml.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hyojung2\2026-AI-FULLSTACK-LevelUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD454F9-D4AD-4CDA-81E2-C6EE6F54EF56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3880194D-06D4-48D1-99BB-13C73AFF5EE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1291" uniqueCount="120">
   <si>
     <t>출석일수 (Attendance Days)</t>
   </si>
@@ -1039,6 +1039,10 @@
   <si>
     <t>전원 출석
 -손창기외</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>예진, 수정, 욱진, 윤정 , 다영, 보라</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -3774,7 +3778,7 @@
         <v>1</v>
       </c>
       <c r="O3" s="95">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P3" s="36">
         <v>0</v>
@@ -3822,7 +3826,7 @@
         <v>1</v>
       </c>
       <c r="O4" s="95">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P4" s="36">
         <v>0</v>
@@ -3998,7 +4002,7 @@
         <v>1</v>
       </c>
       <c r="O8" s="95">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P8" s="36">
         <v>0</v>
@@ -4206,7 +4210,7 @@
         <v>1</v>
       </c>
       <c r="O13" s="95">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P13" s="36">
         <v>0</v>
@@ -4247,13 +4251,13 @@
         <v>1</v>
       </c>
       <c r="O14" s="95">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P14" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="17.25" thickBot="1">
+    <row r="15" spans="1:19" ht="33.75" thickBot="1">
       <c r="A15" s="1">
         <v>39</v>
       </c>
@@ -4278,6 +4282,9 @@
       <c r="H15" s="8" t="s">
         <v>23</v>
       </c>
+      <c r="I15" s="61" t="s">
+        <v>119</v>
+      </c>
       <c r="K15" s="97" t="s">
         <v>17</v>
       </c>
@@ -4291,7 +4298,7 @@
         <v>1</v>
       </c>
       <c r="O15" s="95">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P15" s="36">
         <v>0</v>
